--- a/2025/CUBE MAGASIN.xlsx
+++ b/2025/CUBE MAGASIN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE0664A3-54B5-4DA6-A67D-1A215ADF5A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{DE0664A3-54B5-4DA6-A67D-1A215ADF5A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B47DB642-521A-491A-9E5B-0070D8F91B3E}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F5AAD21E-1102-4A59-AB9D-914D9F36506A}"/>
   </bookViews>
@@ -17,8 +17,9 @@
   </sheets>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="53" r:id="rId2"/>
+    <pivotCache cacheId="27" r:id="rId2"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -55,14 +56,15 @@
   <metadataTypes count="1">
     <metadataType name="XLMDX" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <metadataStrings count="5">
+  <metadataStrings count="6">
     <s v="SMGTAB VENTES"/>
     <s v="{[DIM_ARTICLE].[RAYON].[All]}"/>
     <s v="{[DIM_ARTICLE].[SECTEUR].&amp;[4 - EM]}"/>
     <s v="{[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-01T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-02T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-03T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-04T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-05T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-06T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-07T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-08T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-09T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-10T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-01T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-02T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-03T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-04T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-05T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-06T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-07T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-08T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-09T00:00:00],[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2026].&amp;[Trimestre2].&amp;[Mai].&amp;[2026-05-10T00:00:00]}"/>
     <s v="{[DIM_TEMPS].[ANNEE].&amp;[2024],[DIM_TEMPS].[ANNEE].&amp;[2025],[DIM_TEMPS].[ANNEE].&amp;[2026]}"/>
+    <s v="{[DIM_MAGASIN].[ENSEIGNE].&amp;[SMG],[DIM_MAGASIN].[ENSEIGNE].&amp;[BATAM]}"/>
   </metadataStrings>
-  <mdxMetadata count="4">
+  <mdxMetadata count="5">
     <mdx n="0" f="s">
       <ms ns="1" c="0"/>
     </mdx>
@@ -75,8 +77,11 @@
     <mdx n="0" f="s">
       <ms ns="4" c="0"/>
     </mdx>
+    <mdx n="0" f="s">
+      <ms ns="5" c="0"/>
+    </mdx>
   </mdxMetadata>
-  <valueMetadata count="4">
+  <valueMetadata count="5">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -89,12 +94,15 @@
     <bk>
       <rc t="1" v="3"/>
     </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
   <si>
     <t>RAYON</t>
   </si>
@@ -384,67 +392,70 @@
     <t>BATAM E-COMMERCE</t>
   </si>
   <si>
-    <t>01-05-2025</t>
+    <t>ANNEE</t>
   </si>
   <si>
-    <t>01-05-2026</t>
+    <t>ENSEIGNE</t>
   </si>
   <si>
-    <t>02-05-2025</t>
+    <t>2025-05-01</t>
   </si>
   <si>
-    <t>02-05-2026</t>
+    <t>2025-05-02</t>
   </si>
   <si>
-    <t>03-05-2025</t>
+    <t>2025-05-03</t>
   </si>
   <si>
-    <t>03-05-2026</t>
+    <t>2025-05-04</t>
   </si>
   <si>
-    <t>04-05-2025</t>
+    <t>2025-05-05</t>
   </si>
   <si>
-    <t>04-05-2026</t>
+    <t>2025-05-06</t>
   </si>
   <si>
-    <t>05-05-2025</t>
+    <t>2025-05-07</t>
   </si>
   <si>
-    <t>05-05-2026</t>
+    <t>2025-05-08</t>
   </si>
   <si>
-    <t>06-05-2025</t>
+    <t>2025-05-09</t>
   </si>
   <si>
-    <t>06-05-2026</t>
+    <t>2025-05-10</t>
   </si>
   <si>
-    <t>07-05-2025</t>
+    <t>2026-05-01</t>
   </si>
   <si>
-    <t>07-05-2026</t>
+    <t>2026-05-02</t>
   </si>
   <si>
-    <t>08-05-2025</t>
+    <t>2026-05-03</t>
   </si>
   <si>
-    <t>08-05-2026</t>
+    <t>2026-05-04</t>
   </si>
   <si>
-    <t>09-05-2025</t>
+    <t>2026-05-05</t>
   </si>
   <si>
-    <t>09-05-2026</t>
+    <t>2026-05-06</t>
   </si>
   <si>
-    <t>10-05-2025</t>
+    <t>2026-05-07</t>
   </si>
   <si>
-    <t>10-05-2026</t>
+    <t>2026-05-08</t>
   </si>
   <si>
-    <t>ANNEE</t>
+    <t>2026-05-09</t>
+  </si>
+  <si>
+    <t>2026-05-10</t>
   </si>
 </sst>
 </file>
@@ -532,7 +543,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="413">
+  <dxfs count="140">
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
@@ -1070,6 +1081,74 @@
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
     <dxf>
@@ -1077,78 +1156,8 @@
     </dxf>
     <dxf>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1253,14 +1262,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
+          <bgColor theme="4" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1282,1692 +1284,6 @@
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
     </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2982,7 +1298,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Hamadi Chkondali" refreshedDate="46154.389120254629" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{061FF52A-CE99-41E3-A6CF-40CDC5FBB247}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Hamadi Chkondali" refreshedDate="46171.383533449072" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{061FF52A-CE99-41E3-A6CF-40CDC5FBB247}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="18">
     <cacheField name="[DIM_TEMPS].[TEMPS ATMD].[ANNEE]" caption="ANNEE" numFmtId="0" hierarchy="64" level="1">
@@ -3130,32 +1446,32 @@
         <s v="[DIM_MAGASIN].[MAGASIN].&amp;[BATAM E-COMMERCE]" c="BATAM E-COMMERCE"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[DIM_TEMPS].[NOM_JOUR].[NOM_JOUR]" caption="NOM_JOUR" numFmtId="0" hierarchy="55" level="1">
-      <sharedItems count="20">
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[01-05-2025]" c="01-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[01-05-2026]" c="01-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[02-05-2025]" c="02-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[02-05-2026]" c="02-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[03-05-2025]" c="03-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[03-05-2026]" c="03-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[04-05-2025]" c="04-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[04-05-2026]" c="04-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[05-05-2025]" c="05-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[05-05-2026]" c="05-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[06-05-2025]" c="06-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[06-05-2026]" c="06-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[07-05-2025]" c="07-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[07-05-2026]" c="07-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[08-05-2025]" c="08-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[08-05-2026]" c="08-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[09-05-2025]" c="09-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[09-05-2026]" c="09-05-2026"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[10-05-2025]" c="10-05-2025"/>
-        <s v="[DIM_TEMPS].[NOM_JOUR].&amp;[10-05-2026]" c="10-05-2026"/>
-      </sharedItems>
-    </cacheField>
     <cacheField name="[DIM_TEMPS].[ANNEE].[ANNEE]" caption="ANNEE" numFmtId="0" hierarchy="52" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[DIM_TEMPS].[JOUR].[JOUR]" caption="JOUR" numFmtId="0" hierarchy="53" level="1">
+      <sharedItems count="20">
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-01T00:00:00]" c="2025-05-01"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-02T00:00:00]" c="2025-05-02"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-03T00:00:00]" c="2025-05-03"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-04T00:00:00]" c="2025-05-04"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-05T00:00:00]" c="2025-05-05"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-06T00:00:00]" c="2025-05-06"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-07T00:00:00]" c="2025-05-07"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-08T00:00:00]" c="2025-05-08"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-09T00:00:00]" c="2025-05-09"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2025-05-10T00:00:00]" c="2025-05-10"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-01T00:00:00]" c="2026-05-01"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-02T00:00:00]" c="2026-05-02"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-03T00:00:00]" c="2026-05-03"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-04T00:00:00]" c="2026-05-04"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-05T00:00:00]" c="2026-05-05"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-06T00:00:00]" c="2026-05-06"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-07T00:00:00]" c="2026-05-07"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-08T00:00:00]" c="2026-05-08"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-09T00:00:00]" c="2026-05-09"/>
+        <s v="[DIM_TEMPS].[JOUR].&amp;[2026-05-10T00:00:00]" c="2026-05-10"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <cacheHierarchies count="311">
@@ -3249,17 +1565,17 @@
     <cacheHierarchy uniqueName="[DIM_TEMPS].[ANNEE]" caption="ANNEE" attribute="1" time="1" defaultMemberUniqueName="[DIM_TEMPS].[ANNEE].[All]" allUniqueName="[DIM_TEMPS].[ANNEE].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
+        <fieldUsage x="16"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[DIM_TEMPS].[JOUR]" caption="JOUR" attribute="1" time="1" keyAttribute="1" defaultMemberUniqueName="[DIM_TEMPS].[JOUR].[All]" allUniqueName="[DIM_TEMPS].[JOUR].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
         <fieldUsage x="17"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[DIM_TEMPS].[JOUR]" caption="JOUR" attribute="1" time="1" keyAttribute="1" defaultMemberUniqueName="[DIM_TEMPS].[JOUR].[All]" allUniqueName="[DIM_TEMPS].[JOUR].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
     <cacheHierarchy uniqueName="[DIM_TEMPS].[MOIS]" caption="MOIS" attribute="1" time="1" defaultMemberUniqueName="[DIM_TEMPS].[MOIS].[All]" allUniqueName="[DIM_TEMPS].[MOIS].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[DIM_TEMPS].[NOM_JOUR]" caption="NOM_JOUR" attribute="1" time="1" defaultMemberUniqueName="[DIM_TEMPS].[NOM_JOUR].[All]" allUniqueName="[DIM_TEMPS].[NOM_JOUR].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="16"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[DIM_TEMPS].[NOM_JOUR]" caption="NOM_JOUR" attribute="1" time="1" defaultMemberUniqueName="[DIM_TEMPS].[NOM_JOUR].[All]" allUniqueName="[DIM_TEMPS].[NOM_JOUR].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="2" unbalanced="0"/>
     <cacheHierarchy uniqueName="[DIM_TEMPS].[NUM_JOUR]" caption="NUM_JOUR" attribute="1" time="1" defaultMemberUniqueName="[DIM_TEMPS].[NUM_JOUR].[All]" allUniqueName="[DIM_TEMPS].[NUM_JOUR].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[DIM_TEMPS].[NUM_SEMAINE]" caption="NUM_SEMAINE" attribute="1" time="1" defaultMemberUniqueName="[DIM_TEMPS].[NUM_SEMAINE].[All]" allUniqueName="[DIM_TEMPS].[NUM_SEMAINE].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[DIM_TEMPS].[NUM_TRIMESTRE]" caption="NUM_TRIMESTRE" attribute="1" time="1" defaultMemberUniqueName="[DIM_TEMPS].[NUM_TRIMESTRE].[All]" allUniqueName="[DIM_TEMPS].[NUM_TRIMESTRE].[All]" dimensionUniqueName="[DIM_TEMPS]" displayFolder="" count="0" unbalanced="0"/>
@@ -3626,8 +1942,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD6F70B3-4626-4ED7-8412-48E139314EA4}" name="Tableau croisé dynamique1" cacheId="53" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
-  <location ref="A6:CJ27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="4" colPageCount="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BD6F70B3-4626-4ED7-8412-48E139314EA4}" name="Tableau croisé dynamique1" cacheId="27" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valeurs" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A7:CJ28" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="5" colPageCount="1"/>
   <pivotFields count="18">
     <pivotField axis="axisPage" allDrilled="1" showAll="0" dataSourceSort="1" defaultSubtotal="0">
       <items count="3">
@@ -3658,7 +1974,7 @@
     <pivotField showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
     <pivotField showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
     <pivotField axis="axisPage" allDrilled="1" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField allDrilled="1" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+    <pivotField axis="axisPage" allDrilled="1" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="1">
         <item s="1" x="0"/>
       </items>
@@ -3754,6 +2070,7 @@
         <item x="86"/>
       </items>
     </pivotField>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="20">
         <item x="0"/>
@@ -3778,10 +2095,9 @@
         <item x="19"/>
       </items>
     </pivotField>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="16"/>
+    <field x="17"/>
   </rowFields>
   <rowItems count="20">
     <i>
@@ -4111,65 +2427,66 @@
       <x v="86"/>
     </i>
   </colItems>
-  <pageFields count="4">
+  <pageFields count="5">
+    <pageField fld="14" hier="37" name="[DIM_MAGASIN].[ENSEIGNE].&amp;[SMG]" cap="SMG"/>
     <pageField fld="13" hier="20" name="[DIM_ARTICLE].[RAYON].[All]" cap="All"/>
-    <pageField fld="17" hier="52" name="[DIM_TEMPS].[ANNEE].&amp;[2024]" cap="2024"/>
+    <pageField fld="16" hier="52" name="[DIM_TEMPS].[ANNEE].&amp;[2024]" cap="2024"/>
     <pageField fld="7" hier="22" name="[DIM_ARTICLE].[SECTEUR].&amp;[4 - EM]" cap="4 - EM"/>
-    <pageField fld="0" hier="64" name="[DIM_TEMPS].[TEMPS ATMD].[All]" cap="All"/>
+    <pageField fld="0" hier="64" name="[DIM_TEMPS].[TEMPS ATMD].[ANNEE].&amp;[2025].&amp;[Trimestre2].&amp;[Mai].&amp;[2025-05-01T00:00:00]" cap="2025-05-01"/>
   </pageFields>
   <dataFields count="1">
     <dataField fld="4" baseField="0" baseItem="0" numFmtId="3"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="84">
+    <format dxfId="139">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="85">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="3"/>
+    <format dxfId="138">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="4"/>
     </format>
-    <format dxfId="86">
+    <format dxfId="137">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="87">
+    <format dxfId="136">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="88">
+    <format dxfId="135">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="89">
+    <format dxfId="134">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="90">
+    <format dxfId="133">
       <pivotArea type="origin" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="91">
-      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="3"/>
+    <format dxfId="132">
+      <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="4"/>
     </format>
-    <format dxfId="92">
+    <format dxfId="131">
       <pivotArea field="5" type="button" dataOnly="0" labelOnly="1" outline="0"/>
     </format>
-    <format dxfId="93">
+    <format dxfId="130">
       <pivotArea field="-2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="94">
+    <format dxfId="129">
       <pivotArea type="topRight" dataOnly="0" labelOnly="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="95">
-      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="2"/>
+    <format dxfId="128">
+      <pivotArea field="7" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisPage" fieldPosition="3"/>
     </format>
-    <format dxfId="96">
+    <format dxfId="127">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="97">
-      <pivotArea field="0" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisPage" fieldPosition="3">
+    <format dxfId="126">
+      <pivotArea field="0" dataOnly="0" labelOnly="1" grandCol="1" outline="0" axis="axisPage" fieldPosition="4">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
             <x v="0"/>
@@ -4203,7 +2520,7 @@
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
-    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1"/>
     <pivotHierarchy/>
     <pivotHierarchy multipleItemSelectionAllowed="1"/>
     <pivotHierarchy/>
@@ -4220,7 +2537,12 @@
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
-    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="2" level="1">
+        <member name=""/>
+        <member name="[DIM_MAGASIN].[ENSEIGNE].&amp;[BATAM]"/>
+      </members>
+    </pivotHierarchy>
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -4557,7 +2879,7 @@
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="55"/>
+    <rowHierarchyUsage hierarchyUsage="53"/>
   </rowHierarchiesUsage>
   <colHierarchiesUsage count="1">
     <colHierarchyUsage hierarchyUsage="45"/>
@@ -4985,10 +3307,10 @@
   <sheetData>
     <row r="1" spans="1:88" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" vm="1">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="B1" t="s" vm="5">
+        <v>94</v>
       </c>
       <c r="C1"/>
       <c r="D1"/>
@@ -5002,10 +3324,10 @@
     </row>
     <row r="2" spans="1:88" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" t="s" vm="4">
-        <v>94</v>
+        <v>0</v>
+      </c>
+      <c r="B2" t="s" vm="1">
+        <v>1</v>
       </c>
       <c r="C2"/>
       <c r="D2"/>
@@ -5018,11 +3340,11 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:88" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s" vm="2">
-        <v>3</v>
+      <c r="A3" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" t="s" vm="4">
+        <v>94</v>
       </c>
       <c r="C3"/>
       <c r="D3"/>
@@ -5035,11 +3357,11 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:88" s="2" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="3" t="s" vm="3">
-        <v>94</v>
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s" vm="2">
+        <v>3</v>
       </c>
       <c r="C4"/>
       <c r="D4"/>
@@ -5052,7 +3374,12 @@
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:88" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B5"/>
+      <c r="A5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="3" t="s" vm="3">
+        <v>94</v>
+      </c>
       <c r="C5"/>
       <c r="D5"/>
       <c r="E5"/>
@@ -5064,882 +3391,640 @@
       <c r="K5"/>
     </row>
     <row r="6" spans="1:88" x14ac:dyDescent="0.35">
-      <c r="A6" s="2" t="s">
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6"/>
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+    </row>
+    <row r="7" spans="1:88" x14ac:dyDescent="0.35">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
-      <c r="S6" s="3"/>
-      <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-      <c r="AA6" s="3"/>
-      <c r="AB6" s="3"/>
-      <c r="AC6" s="3"/>
-      <c r="AD6" s="3"/>
-      <c r="AE6" s="3"/>
-      <c r="AF6" s="3"/>
-      <c r="AG6" s="3"/>
-      <c r="AH6" s="3"/>
-      <c r="AI6" s="3"/>
-      <c r="AJ6" s="3"/>
-      <c r="AK6" s="3"/>
-      <c r="AL6" s="3"/>
-      <c r="AM6" s="3"/>
-      <c r="AN6" s="3"/>
-      <c r="AO6" s="3"/>
-      <c r="AP6" s="3"/>
-      <c r="AQ6" s="3"/>
-      <c r="AR6" s="3"/>
-      <c r="AS6" s="3"/>
-      <c r="AT6" s="3"/>
-      <c r="AU6" s="3"/>
-      <c r="AV6" s="3"/>
-      <c r="AW6" s="3"/>
-      <c r="AX6" s="3"/>
-      <c r="AY6" s="3"/>
-      <c r="AZ6" s="3"/>
-      <c r="BA6" s="3"/>
-      <c r="BB6" s="3"/>
-      <c r="BC6" s="3"/>
-      <c r="BD6" s="3"/>
-      <c r="BE6" s="3"/>
-      <c r="BF6" s="3"/>
-      <c r="BG6" s="3"/>
-      <c r="BH6" s="3"/>
-      <c r="BI6" s="3"/>
-      <c r="BJ6" s="3"/>
-      <c r="BK6" s="3"/>
-      <c r="BL6" s="3"/>
-      <c r="BM6" s="3"/>
-      <c r="BN6" s="3"/>
-      <c r="BO6" s="3"/>
-      <c r="BP6" s="3"/>
-      <c r="BQ6" s="3"/>
-      <c r="BR6" s="3"/>
-      <c r="BS6" s="3"/>
-      <c r="BT6" s="3"/>
-      <c r="BU6" s="3"/>
-      <c r="BV6" s="3"/>
-      <c r="BW6" s="3"/>
-      <c r="BX6" s="3"/>
-      <c r="BY6" s="3"/>
-      <c r="BZ6" s="3"/>
-      <c r="CA6" s="3"/>
-      <c r="CB6" s="3"/>
-      <c r="CC6" s="3"/>
-      <c r="CD6" s="3"/>
-      <c r="CE6" s="3"/>
-      <c r="CF6" s="3"/>
-      <c r="CG6" s="3"/>
-      <c r="CH6" s="3"/>
-      <c r="CI6" s="3"/>
-      <c r="CJ6" s="3"/>
-    </row>
-    <row r="7" spans="1:88" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="3"/>
+      <c r="N7" s="3"/>
+      <c r="O7" s="3"/>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3"/>
+      <c r="R7" s="3"/>
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+      <c r="AO7" s="3"/>
+      <c r="AP7" s="3"/>
+      <c r="AQ7" s="3"/>
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="3"/>
+      <c r="AT7" s="3"/>
+      <c r="AU7" s="3"/>
+      <c r="AV7" s="3"/>
+      <c r="AW7" s="3"/>
+      <c r="AX7" s="3"/>
+      <c r="AY7" s="3"/>
+      <c r="AZ7" s="3"/>
+      <c r="BA7" s="3"/>
+      <c r="BB7" s="3"/>
+      <c r="BC7" s="3"/>
+      <c r="BD7" s="3"/>
+      <c r="BE7" s="3"/>
+      <c r="BF7" s="3"/>
+      <c r="BG7" s="3"/>
+      <c r="BH7" s="3"/>
+      <c r="BI7" s="3"/>
+      <c r="BJ7" s="3"/>
+      <c r="BK7" s="3"/>
+      <c r="BL7" s="3"/>
+      <c r="BM7" s="3"/>
+      <c r="BN7" s="3"/>
+      <c r="BO7" s="3"/>
+      <c r="BP7" s="3"/>
+      <c r="BQ7" s="3"/>
+      <c r="BR7" s="3"/>
+      <c r="BS7" s="3"/>
+      <c r="BT7" s="3"/>
+      <c r="BU7" s="3"/>
+      <c r="BV7" s="3"/>
+      <c r="BW7" s="3"/>
+      <c r="BX7" s="3"/>
+      <c r="BY7" s="3"/>
+      <c r="BZ7" s="3"/>
+      <c r="CA7" s="3"/>
+      <c r="CB7" s="3"/>
+      <c r="CC7" s="3"/>
+      <c r="CD7" s="3"/>
+      <c r="CE7" s="3"/>
+      <c r="CF7" s="3"/>
+      <c r="CG7" s="3"/>
+      <c r="CH7" s="3"/>
+      <c r="CI7" s="3"/>
+      <c r="CJ7" s="3"/>
+    </row>
+    <row r="8" spans="1:88" x14ac:dyDescent="0.35">
+      <c r="A8" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>50</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>42</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D8" t="s">
         <v>27</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F8" t="s">
         <v>36</v>
       </c>
-      <c r="G7" t="s">
+      <c r="G8" t="s">
         <v>51</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H8" t="s">
         <v>61</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I8" t="s">
         <v>62</v>
       </c>
-      <c r="J7" t="s">
+      <c r="J8" t="s">
         <v>52</v>
       </c>
-      <c r="K7" t="s">
+      <c r="K8" t="s">
         <v>86</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L8" t="s">
         <v>37</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M8" t="s">
         <v>19</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N8" t="s">
         <v>43</v>
       </c>
-      <c r="O7" t="s">
+      <c r="O8" t="s">
         <v>53</v>
       </c>
-      <c r="P7" t="s">
+      <c r="P8" t="s">
         <v>7</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="Q8" t="s">
         <v>20</v>
       </c>
-      <c r="R7" t="s">
+      <c r="R8" t="s">
         <v>84</v>
       </c>
-      <c r="S7" t="s">
+      <c r="S8" t="s">
         <v>38</v>
       </c>
-      <c r="T7" t="s">
+      <c r="T8" t="s">
         <v>8</v>
       </c>
-      <c r="U7" t="s">
+      <c r="U8" t="s">
         <v>74</v>
       </c>
-      <c r="V7" t="s">
+      <c r="V8" t="s">
         <v>28</v>
       </c>
-      <c r="W7" t="s">
+      <c r="W8" t="s">
         <v>29</v>
       </c>
-      <c r="X7" t="s">
+      <c r="X8" t="s">
         <v>9</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Y8" t="s">
         <v>63</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="Z8" t="s">
         <v>10</v>
       </c>
-      <c r="AA7" t="s">
+      <c r="AA8" t="s">
         <v>64</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AB8" t="s">
         <v>11</v>
       </c>
-      <c r="AC7" t="s">
+      <c r="AC8" t="s">
         <v>21</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AD8" t="s">
         <v>54</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AE8" t="s">
         <v>65</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AF8" t="s">
         <v>55</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AG8" t="s">
         <v>66</v>
       </c>
-      <c r="AH7" t="s">
+      <c r="AH8" t="s">
         <v>12</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AI8" t="s">
         <v>56</v>
       </c>
-      <c r="AJ7" t="s">
+      <c r="AJ8" t="s">
         <v>44</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AK8" t="s">
         <v>45</v>
       </c>
-      <c r="AL7" t="s">
+      <c r="AL8" t="s">
         <v>30</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AM8" t="s">
         <v>31</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AN8" t="s">
         <v>46</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AO8" t="s">
         <v>57</v>
       </c>
-      <c r="AP7" t="s">
+      <c r="AP8" t="s">
         <v>67</v>
       </c>
-      <c r="AQ7" t="s">
+      <c r="AQ8" t="s">
         <v>13</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AR8" t="s">
         <v>14</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AS8" t="s">
         <v>15</v>
       </c>
-      <c r="AT7" t="s">
+      <c r="AT8" t="s">
         <v>68</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AU8" t="s">
         <v>58</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AV8" t="s">
         <v>22</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AW8" t="s">
         <v>47</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AX8" t="s">
         <v>59</v>
       </c>
-      <c r="AY7" t="s">
+      <c r="AY8" t="s">
         <v>69</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="AZ8" t="s">
         <v>85</v>
       </c>
-      <c r="BA7" t="s">
+      <c r="BA8" t="s">
         <v>39</v>
       </c>
-      <c r="BB7" t="s">
+      <c r="BB8" t="s">
         <v>48</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BC8" t="s">
         <v>32</v>
       </c>
-      <c r="BD7" t="s">
+      <c r="BD8" t="s">
         <v>40</v>
       </c>
-      <c r="BE7" t="s">
+      <c r="BE8" t="s">
         <v>70</v>
       </c>
-      <c r="BF7" t="s">
+      <c r="BF8" t="s">
         <v>23</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BG8" t="s">
         <v>75</v>
       </c>
-      <c r="BH7" t="s">
+      <c r="BH8" t="s">
         <v>76</v>
       </c>
-      <c r="BI7" t="s">
+      <c r="BI8" t="s">
         <v>87</v>
       </c>
-      <c r="BJ7" t="s">
+      <c r="BJ8" t="s">
         <v>77</v>
       </c>
-      <c r="BK7" t="s">
+      <c r="BK8" t="s">
         <v>88</v>
       </c>
-      <c r="BL7" t="s">
+      <c r="BL8" t="s">
         <v>78</v>
       </c>
-      <c r="BM7" t="s">
+      <c r="BM8" t="s">
         <v>33</v>
       </c>
-      <c r="BN7" t="s">
+      <c r="BN8" t="s">
         <v>79</v>
       </c>
-      <c r="BO7" t="s">
+      <c r="BO8" t="s">
         <v>89</v>
       </c>
-      <c r="BP7" t="s">
+      <c r="BP8" t="s">
         <v>80</v>
       </c>
-      <c r="BQ7" t="s">
+      <c r="BQ8" t="s">
         <v>90</v>
       </c>
-      <c r="BR7" t="s">
+      <c r="BR8" t="s">
         <v>24</v>
       </c>
-      <c r="BS7" t="s">
+      <c r="BS8" t="s">
         <v>60</v>
       </c>
-      <c r="BT7" t="s">
+      <c r="BT8" t="s">
         <v>49</v>
       </c>
-      <c r="BU7" t="s">
+      <c r="BU8" t="s">
         <v>81</v>
       </c>
-      <c r="BV7" t="s">
+      <c r="BV8" t="s">
         <v>91</v>
       </c>
-      <c r="BW7" t="s">
+      <c r="BW8" t="s">
         <v>25</v>
       </c>
-      <c r="BX7" t="s">
+      <c r="BX8" t="s">
         <v>16</v>
       </c>
-      <c r="BY7" t="s">
+      <c r="BY8" t="s">
         <v>82</v>
       </c>
-      <c r="BZ7" t="s">
+      <c r="BZ8" t="s">
         <v>83</v>
       </c>
-      <c r="CA7" t="s">
+      <c r="CA8" t="s">
         <v>26</v>
       </c>
-      <c r="CB7" t="s">
+      <c r="CB8" t="s">
         <v>92</v>
       </c>
-      <c r="CC7" t="s">
+      <c r="CC8" t="s">
         <v>71</v>
       </c>
-      <c r="CD7" t="s">
+      <c r="CD8" t="s">
         <v>34</v>
       </c>
-      <c r="CE7" t="s">
+      <c r="CE8" t="s">
         <v>72</v>
       </c>
-      <c r="CF7" t="s">
+      <c r="CF8" t="s">
         <v>35</v>
       </c>
-      <c r="CG7" t="s">
+      <c r="CG8" t="s">
         <v>41</v>
       </c>
-      <c r="CH7" t="s">
+      <c r="CH8" t="s">
         <v>73</v>
       </c>
-      <c r="CI7" t="s">
+      <c r="CI8" t="s">
         <v>17</v>
       </c>
-      <c r="CJ7" t="s">
+      <c r="CJ8" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:88" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="6">
-        <v>13.98</v>
-      </c>
-      <c r="C8" s="6">
-        <v>1938.76</v>
-      </c>
-      <c r="D8" s="6">
-        <v>224.99</v>
-      </c>
-      <c r="E8" s="6">
-        <v>99.99</v>
-      </c>
-      <c r="F8" s="6">
-        <v>2023.54</v>
-      </c>
-      <c r="G8" s="6">
-        <v>8598.5899999999965</v>
-      </c>
-      <c r="H8" s="6">
-        <v>4435.57</v>
-      </c>
-      <c r="I8" s="6">
-        <v>3375.94</v>
-      </c>
-      <c r="J8" s="6">
-        <v>2161.9499999999998</v>
-      </c>
-      <c r="K8" s="6">
-        <v>2001.48</v>
-      </c>
-      <c r="L8" s="6">
-        <v>602.98</v>
-      </c>
-      <c r="M8" s="6">
-        <v>199</v>
-      </c>
-      <c r="N8" s="6">
-        <v>288.99</v>
-      </c>
-      <c r="O8" s="6">
-        <v>38.86</v>
-      </c>
-      <c r="P8" s="6">
-        <v>3061.7700000000004</v>
-      </c>
-      <c r="Q8" s="6">
-        <v>158</v>
-      </c>
-      <c r="R8" s="6">
-        <v>1649.9</v>
-      </c>
-      <c r="S8" s="6">
-        <v>219</v>
-      </c>
-      <c r="T8" s="6">
-        <v>222.99</v>
-      </c>
-      <c r="U8" s="6">
-        <v>7709.87</v>
-      </c>
-      <c r="V8" s="6">
-        <v>341.56</v>
-      </c>
-      <c r="W8" s="6">
-        <v>3472.8399999999983</v>
-      </c>
-      <c r="X8" s="6">
-        <v>3630.95</v>
-      </c>
-      <c r="Y8" s="6">
-        <v>1319.97</v>
-      </c>
-      <c r="Z8" s="6">
-        <v>2927.95</v>
-      </c>
-      <c r="AA8" s="6">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="AB8" s="6">
-        <v>613.99</v>
-      </c>
-      <c r="AC8" s="6">
-        <v>44.99</v>
-      </c>
-      <c r="AD8" s="6">
-        <v>943.99</v>
-      </c>
-      <c r="AE8" s="6">
-        <v>409.87</v>
-      </c>
-      <c r="AF8" s="6">
-        <v>2643.98</v>
-      </c>
-      <c r="AG8" s="6">
-        <v>690.67</v>
-      </c>
-      <c r="AH8" s="6">
-        <v>129.99</v>
-      </c>
-      <c r="AI8" s="6">
-        <v>2044.41</v>
-      </c>
-      <c r="AJ8" s="6">
-        <v>928.99</v>
-      </c>
-      <c r="AK8" s="6">
-        <v>2834.89</v>
-      </c>
-      <c r="AL8" s="6">
-        <v>7272.9189999999981</v>
-      </c>
-      <c r="AM8" s="6">
-        <v>1841.97</v>
-      </c>
-      <c r="AN8" s="6">
-        <v>4381.5899999999992</v>
-      </c>
-      <c r="AO8" s="6">
-        <v>967.76</v>
-      </c>
-      <c r="AP8" s="6">
-        <v>205.98000000000002</v>
-      </c>
-      <c r="AQ8" s="6">
-        <v>3127.5600000000004</v>
-      </c>
-      <c r="AR8" s="6">
-        <v>272</v>
-      </c>
-      <c r="AS8" s="6">
-        <v>728.98</v>
-      </c>
-      <c r="AT8" s="6">
-        <v>831.9</v>
-      </c>
-      <c r="AU8" s="6">
-        <v>3514.99</v>
-      </c>
-      <c r="AV8" s="6">
-        <v>405.8</v>
-      </c>
-      <c r="AW8" s="6">
-        <v>208.99</v>
-      </c>
-      <c r="AX8" s="6">
-        <v>2016</v>
-      </c>
-      <c r="AY8" s="6">
-        <v>4728.99</v>
-      </c>
-      <c r="AZ8" s="6">
-        <v>2143.66</v>
-      </c>
-      <c r="BA8" s="6">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="BB8" s="6">
-        <v>527</v>
-      </c>
-      <c r="BC8" s="6">
-        <v>2908.6059999999993</v>
-      </c>
-      <c r="BD8" s="6">
-        <v>44.99</v>
-      </c>
-      <c r="BE8" s="6">
-        <v>2552.88</v>
-      </c>
-      <c r="BF8" s="6"/>
-      <c r="BG8" s="6">
-        <v>4943.8899999999994</v>
-      </c>
-      <c r="BH8" s="6">
-        <v>1949.89</v>
-      </c>
-      <c r="BI8" s="6">
-        <v>1182</v>
-      </c>
-      <c r="BJ8" s="6">
-        <v>8874.6699999999983</v>
-      </c>
-      <c r="BK8" s="6">
-        <v>2079.77</v>
-      </c>
-      <c r="BL8" s="6">
-        <v>325.96000000000004</v>
-      </c>
-      <c r="BM8" s="6"/>
-      <c r="BN8" s="6">
-        <v>1738</v>
-      </c>
-      <c r="BO8" s="6">
-        <v>1777.79</v>
-      </c>
-      <c r="BP8" s="6">
-        <v>842.99</v>
-      </c>
-      <c r="BQ8" s="6">
-        <v>1451.9</v>
-      </c>
-      <c r="BR8" s="6">
-        <v>2773.35</v>
-      </c>
-      <c r="BS8" s="6"/>
-      <c r="BT8" s="6">
-        <v>2604.19</v>
-      </c>
-      <c r="BU8" s="6">
-        <v>14582.85</v>
-      </c>
-      <c r="BV8" s="6">
-        <v>13213.68</v>
-      </c>
-      <c r="BW8" s="6">
-        <v>3163.9</v>
-      </c>
-      <c r="BX8" s="6">
-        <v>4209.6699999999992</v>
-      </c>
-      <c r="BY8" s="6">
-        <v>14635.98</v>
-      </c>
-      <c r="BZ8" s="6">
-        <v>6688.91</v>
-      </c>
-      <c r="CA8" s="6">
-        <v>2958.8599999999988</v>
-      </c>
-      <c r="CB8" s="6">
-        <v>5711.68</v>
-      </c>
-      <c r="CC8" s="6">
-        <v>2030.39</v>
-      </c>
-      <c r="CD8" s="6">
-        <v>1016.9</v>
-      </c>
-      <c r="CE8" s="6">
-        <v>1009.88</v>
-      </c>
-      <c r="CF8" s="6">
-        <v>44.99</v>
-      </c>
-      <c r="CG8" s="6">
-        <v>3167.95</v>
-      </c>
-      <c r="CH8" s="6">
-        <v>2890.96</v>
-      </c>
-      <c r="CI8" s="6">
-        <v>910.96</v>
-      </c>
-      <c r="CJ8" s="6">
-        <v>4648.9399999999996</v>
       </c>
     </row>
     <row r="9" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" s="6">
-        <v>1309.8</v>
+        <v>13.98</v>
       </c>
       <c r="C9" s="6">
-        <v>3224.9</v>
+        <v>1938.76</v>
       </c>
       <c r="D9" s="6">
-        <v>69</v>
-      </c>
-      <c r="E9" s="6"/>
+        <v>224.99</v>
+      </c>
+      <c r="E9" s="6">
+        <v>99.99</v>
+      </c>
       <c r="F9" s="6">
-        <v>1089</v>
+        <v>2023.54</v>
       </c>
       <c r="G9" s="6">
-        <v>17428.349999999999</v>
+        <v>8598.5899999999965</v>
       </c>
       <c r="H9" s="6">
-        <v>4447.75</v>
+        <v>4435.57</v>
       </c>
       <c r="I9" s="6">
-        <v>3337.99</v>
+        <v>3375.94</v>
       </c>
       <c r="J9" s="6">
-        <v>1275.8900000000001</v>
+        <v>2161.9499999999998</v>
       </c>
       <c r="K9" s="6">
-        <v>2577</v>
+        <v>2001.48</v>
       </c>
       <c r="L9" s="6">
-        <v>248.99</v>
-      </c>
-      <c r="M9" s="6"/>
+        <v>602.98</v>
+      </c>
+      <c r="M9" s="6">
+        <v>199</v>
+      </c>
       <c r="N9" s="6">
-        <v>894.77</v>
+        <v>288.99</v>
       </c>
       <c r="O9" s="6">
-        <v>829.5</v>
+        <v>38.86</v>
       </c>
       <c r="P9" s="6">
-        <v>3753.4700000000003</v>
+        <v>3061.7700000000004</v>
       </c>
       <c r="Q9" s="6">
-        <v>153.99</v>
+        <v>158</v>
       </c>
       <c r="R9" s="6">
-        <v>2860</v>
+        <v>1649.9</v>
       </c>
       <c r="S9" s="6">
-        <v>187.99</v>
+        <v>219</v>
       </c>
       <c r="T9" s="6">
-        <v>49.9</v>
+        <v>222.99</v>
       </c>
       <c r="U9" s="6">
-        <v>2553</v>
+        <v>7709.87</v>
       </c>
       <c r="V9" s="6">
-        <v>786.68999999999994</v>
+        <v>341.56</v>
       </c>
       <c r="W9" s="6">
-        <v>6291.58</v>
+        <v>3472.8399999999983</v>
       </c>
       <c r="X9" s="6">
-        <v>1267.7</v>
+        <v>3630.95</v>
       </c>
       <c r="Y9" s="6">
-        <v>1974.8</v>
+        <v>1319.97</v>
       </c>
       <c r="Z9" s="6">
-        <v>4686.95</v>
+        <v>2927.95</v>
       </c>
       <c r="AA9" s="6">
-        <v>3566</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="AB9" s="6">
-        <v>224.99</v>
+        <v>613.99</v>
       </c>
       <c r="AC9" s="6">
-        <v>138</v>
+        <v>44.99</v>
       </c>
       <c r="AD9" s="6">
-        <v>1586</v>
+        <v>943.99</v>
       </c>
       <c r="AE9" s="6">
-        <v>746.99</v>
+        <v>409.87</v>
       </c>
       <c r="AF9" s="6">
-        <v>2554.7800000000002</v>
+        <v>2643.98</v>
       </c>
       <c r="AG9" s="6">
-        <v>3093.8</v>
-      </c>
-      <c r="AH9" s="6"/>
+        <v>690.67</v>
+      </c>
+      <c r="AH9" s="6">
+        <v>129.99</v>
+      </c>
       <c r="AI9" s="6">
-        <v>1024.3699999999999</v>
+        <v>2044.41</v>
       </c>
       <c r="AJ9" s="6">
-        <v>1606.5</v>
+        <v>928.99</v>
       </c>
       <c r="AK9" s="6">
-        <v>2130.89</v>
+        <v>2834.89</v>
       </c>
       <c r="AL9" s="6">
-        <v>4217.7699999999995</v>
+        <v>7272.9189999999981</v>
       </c>
       <c r="AM9" s="6">
-        <v>2259.89</v>
+        <v>1841.97</v>
       </c>
       <c r="AN9" s="6">
-        <v>574.9</v>
+        <v>4381.5899999999992</v>
       </c>
       <c r="AO9" s="6">
-        <v>2794.97</v>
+        <v>967.76</v>
       </c>
       <c r="AP9" s="6">
-        <v>1326.99</v>
+        <v>205.98000000000002</v>
       </c>
       <c r="AQ9" s="6">
-        <v>7254.6429999999991</v>
+        <v>3127.5600000000004</v>
       </c>
       <c r="AR9" s="6">
-        <v>1826.9</v>
+        <v>272</v>
       </c>
       <c r="AS9" s="6">
-        <v>1128.8799999999999</v>
+        <v>728.98</v>
       </c>
       <c r="AT9" s="6">
-        <v>39</v>
+        <v>831.9</v>
       </c>
       <c r="AU9" s="6">
-        <v>1268</v>
+        <v>3514.99</v>
       </c>
       <c r="AV9" s="6">
-        <v>4230.87</v>
+        <v>405.8</v>
       </c>
       <c r="AW9" s="6">
-        <v>314</v>
+        <v>208.99</v>
       </c>
       <c r="AX9" s="6">
-        <v>2046.7</v>
+        <v>2016</v>
       </c>
       <c r="AY9" s="6">
-        <v>268</v>
+        <v>4728.99</v>
       </c>
       <c r="AZ9" s="6">
-        <v>2693.49</v>
+        <v>2143.66</v>
       </c>
       <c r="BA9" s="6">
-        <v>64</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="BB9" s="6">
-        <v>1145.8899999999999</v>
+        <v>527</v>
       </c>
       <c r="BC9" s="6">
-        <v>3210.17</v>
+        <v>2908.6059999999993</v>
       </c>
       <c r="BD9" s="6">
-        <v>94</v>
+        <v>44.99</v>
       </c>
       <c r="BE9" s="6">
-        <v>1766.89</v>
+        <v>2552.88</v>
       </c>
       <c r="BF9" s="6"/>
       <c r="BG9" s="6">
-        <v>27868.400000000001</v>
+        <v>4943.8899999999994</v>
       </c>
       <c r="BH9" s="6">
-        <v>3960.8999999999996</v>
+        <v>1949.89</v>
       </c>
       <c r="BI9" s="6">
-        <v>4056</v>
+        <v>1182</v>
       </c>
       <c r="BJ9" s="6">
-        <v>8017.5999999999995</v>
+        <v>8874.6699999999983</v>
       </c>
       <c r="BK9" s="6">
-        <v>4160.6799999999994</v>
+        <v>2079.77</v>
       </c>
       <c r="BL9" s="6">
-        <v>6534.8</v>
-      </c>
-      <c r="BM9" s="6">
-        <v>129.99</v>
-      </c>
+        <v>325.96000000000004</v>
+      </c>
+      <c r="BM9" s="6"/>
       <c r="BN9" s="6">
-        <v>587</v>
+        <v>1738</v>
       </c>
       <c r="BO9" s="6">
-        <v>1928.7</v>
+        <v>1777.79</v>
       </c>
       <c r="BP9" s="6">
-        <v>5944.9</v>
+        <v>842.99</v>
       </c>
       <c r="BQ9" s="6">
-        <v>9182.7999999999993</v>
+        <v>1451.9</v>
       </c>
       <c r="BR9" s="6">
-        <v>3738.45</v>
+        <v>2773.35</v>
       </c>
       <c r="BS9" s="6"/>
       <c r="BT9" s="6">
-        <v>4452.8500000000004</v>
+        <v>2604.19</v>
       </c>
       <c r="BU9" s="6">
-        <v>5159</v>
+        <v>14582.85</v>
       </c>
       <c r="BV9" s="6">
-        <v>3573.7</v>
+        <v>13213.68</v>
       </c>
       <c r="BW9" s="6">
-        <v>2144.9499999999998</v>
+        <v>3163.9</v>
       </c>
       <c r="BX9" s="6">
-        <v>1213.8800000000001</v>
+        <v>4209.6699999999992</v>
       </c>
       <c r="BY9" s="6">
-        <v>7248.9</v>
+        <v>14635.98</v>
       </c>
       <c r="BZ9" s="6">
-        <v>9129.8799999999992</v>
+        <v>6688.91</v>
       </c>
       <c r="CA9" s="6">
-        <v>3130.96</v>
+        <v>2958.8599999999988</v>
       </c>
       <c r="CB9" s="6">
-        <v>11716</v>
+        <v>5711.68</v>
       </c>
       <c r="CC9" s="6">
-        <v>1507.19</v>
+        <v>2030.39</v>
       </c>
       <c r="CD9" s="6">
-        <v>1635.7900000000002</v>
+        <v>1016.9</v>
       </c>
       <c r="CE9" s="6">
-        <v>188.99</v>
-      </c>
-      <c r="CF9" s="6"/>
+        <v>1009.88</v>
+      </c>
+      <c r="CF9" s="6">
+        <v>44.99</v>
+      </c>
       <c r="CG9" s="6">
-        <v>2393.96</v>
+        <v>3167.95</v>
       </c>
       <c r="CH9" s="6">
-        <v>3392.89</v>
+        <v>2890.96</v>
       </c>
       <c r="CI9" s="6">
-        <v>552.87</v>
+        <v>910.96</v>
       </c>
       <c r="CJ9" s="6">
-        <v>9684.909999999998</v>
+        <v>4648.9399999999996</v>
       </c>
     </row>
     <row r="10" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B10" s="6">
         <v>4096</v>
@@ -6193,4157 +4278,4401 @@
     </row>
     <row r="11" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B11" s="6">
-        <v>1115.27</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="B11" s="6"/>
       <c r="C11" s="6">
-        <v>9485.99</v>
+        <v>2015.9700000000003</v>
       </c>
       <c r="D11" s="6">
-        <v>657.99</v>
-      </c>
-      <c r="E11" s="6"/>
+        <v>139.99</v>
+      </c>
+      <c r="E11" s="6">
+        <v>169</v>
+      </c>
       <c r="F11" s="6">
-        <v>2224.3700000000003</v>
+        <v>4331.8099999999995</v>
       </c>
       <c r="G11" s="6">
-        <v>7930.5699999999979</v>
+        <v>5655.8899999999994</v>
       </c>
       <c r="H11" s="6">
-        <v>4804.99</v>
+        <v>2515.9699999999993</v>
       </c>
       <c r="I11" s="6">
-        <v>10015.49</v>
+        <v>5354.8799999999992</v>
       </c>
       <c r="J11" s="6">
-        <v>2566.7000000000007</v>
-      </c>
-      <c r="K11" s="6">
-        <v>54.599999999999994</v>
-      </c>
-      <c r="L11" s="6"/>
+        <v>1560.36</v>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="6">
+        <v>781.98</v>
+      </c>
       <c r="M11" s="6"/>
       <c r="N11" s="6">
-        <v>494.80999999999995</v>
+        <v>194.89</v>
       </c>
       <c r="O11" s="6">
-        <v>2925.2000000000003</v>
+        <v>710.87</v>
       </c>
       <c r="P11" s="6">
-        <v>3458.86</v>
+        <v>2900.9499999999994</v>
       </c>
       <c r="Q11" s="6">
-        <v>196.9</v>
+        <v>388</v>
       </c>
       <c r="R11" s="6">
-        <v>9384</v>
+        <v>1841.5</v>
       </c>
       <c r="S11" s="6">
-        <v>402.89</v>
+        <v>646.98</v>
       </c>
       <c r="T11" s="6">
-        <v>79</v>
+        <v>652</v>
       </c>
       <c r="U11" s="6">
-        <v>2801.89</v>
+        <v>143.99</v>
       </c>
       <c r="V11" s="6">
-        <v>3005.87</v>
+        <v>178.99</v>
       </c>
       <c r="W11" s="6">
-        <v>8151.329999999999</v>
+        <v>4725.78</v>
       </c>
       <c r="X11" s="6">
-        <v>2118.7799999999997</v>
+        <v>154.97</v>
       </c>
       <c r="Y11" s="6">
-        <v>2177</v>
+        <v>20.97</v>
       </c>
       <c r="Z11" s="6">
-        <v>2368.88</v>
+        <v>4273.76</v>
       </c>
       <c r="AA11" s="6">
-        <v>4406.99</v>
+        <v>1945.99</v>
       </c>
       <c r="AB11" s="6">
-        <v>248.98000000000002</v>
-      </c>
-      <c r="AC11" s="6">
-        <v>153.99</v>
-      </c>
+        <v>2002.89</v>
+      </c>
+      <c r="AC11" s="6"/>
       <c r="AD11" s="6">
-        <v>193.99</v>
+        <v>35.99</v>
       </c>
       <c r="AE11" s="6">
-        <v>452</v>
+        <v>274.98</v>
       </c>
       <c r="AF11" s="6">
-        <v>5080.66</v>
+        <v>2286.79</v>
       </c>
       <c r="AG11" s="6">
-        <v>1646.6000000000001</v>
+        <v>51.980000000000004</v>
       </c>
       <c r="AH11" s="6"/>
       <c r="AI11" s="6">
-        <v>4319.880000000001</v>
+        <v>1036.8800000000001</v>
       </c>
       <c r="AJ11" s="6">
-        <v>428.89</v>
+        <v>1655</v>
       </c>
       <c r="AK11" s="6">
-        <v>11363.97</v>
+        <v>3234.88</v>
       </c>
       <c r="AL11" s="6">
-        <v>8718.869999999999</v>
+        <v>10738.64</v>
       </c>
       <c r="AM11" s="6">
-        <v>2459.5000000000005</v>
+        <v>1864.7900000000002</v>
       </c>
       <c r="AN11" s="6">
-        <v>2145</v>
+        <v>3325.79</v>
       </c>
       <c r="AO11" s="6">
-        <v>4354.87</v>
+        <v>2182.84</v>
       </c>
       <c r="AP11" s="6">
-        <v>3889.86</v>
+        <v>947.98</v>
       </c>
       <c r="AQ11" s="6">
-        <v>4239.75</v>
+        <v>1708.5900000000001</v>
       </c>
       <c r="AR11" s="6">
-        <v>1275.99</v>
+        <v>596.78</v>
       </c>
       <c r="AS11" s="6">
-        <v>2334.9899999999998</v>
+        <v>977.99</v>
       </c>
       <c r="AT11" s="6">
-        <v>114</v>
+        <v>176.89000000000001</v>
       </c>
       <c r="AU11" s="6">
-        <v>468</v>
+        <v>878.99</v>
       </c>
       <c r="AV11" s="6">
-        <v>1482.68</v>
-      </c>
-      <c r="AW11" s="6">
-        <v>299.8</v>
-      </c>
+        <v>1466.9</v>
+      </c>
+      <c r="AW11" s="6"/>
       <c r="AX11" s="6">
-        <v>1236.99</v>
+        <v>1271.99</v>
       </c>
       <c r="AY11" s="6">
-        <v>3891.98</v>
+        <v>2371.0100000000002</v>
       </c>
       <c r="AZ11" s="6">
-        <v>18774.98</v>
-      </c>
-      <c r="BA11" s="6">
-        <v>302.99</v>
-      </c>
+        <v>13751.9</v>
+      </c>
+      <c r="BA11" s="6"/>
       <c r="BB11" s="6">
-        <v>660.9</v>
+        <v>708.91</v>
       </c>
       <c r="BC11" s="6">
-        <v>5600.78</v>
-      </c>
-      <c r="BD11" s="6">
-        <v>1897.99</v>
-      </c>
+        <v>1773.98</v>
+      </c>
+      <c r="BD11" s="6"/>
       <c r="BE11" s="6">
-        <v>1383</v>
+        <v>1979.93</v>
       </c>
       <c r="BF11" s="6"/>
       <c r="BG11" s="6">
-        <v>4399.1900000000005</v>
+        <v>1863.6799999999998</v>
       </c>
       <c r="BH11" s="6">
-        <v>1410.7</v>
+        <v>319.97000000000003</v>
       </c>
       <c r="BI11" s="6">
-        <v>7450</v>
+        <v>1791</v>
       </c>
       <c r="BJ11" s="6">
-        <v>2186.9899999999998</v>
+        <v>1788.98</v>
       </c>
       <c r="BK11" s="6">
-        <v>6139.2999999999993</v>
+        <v>3293.8689999999997</v>
       </c>
       <c r="BL11" s="6">
-        <v>7862.1</v>
+        <v>716.09000000000015</v>
       </c>
       <c r="BM11" s="6">
-        <v>109.98</v>
+        <v>318</v>
       </c>
       <c r="BN11" s="6">
-        <v>4437.7699999999995</v>
+        <v>1489.98</v>
       </c>
       <c r="BO11" s="6">
-        <v>889.8</v>
+        <v>2859.99</v>
       </c>
       <c r="BP11" s="6">
-        <v>2150.8000000000002</v>
+        <v>7917.869999999999</v>
       </c>
       <c r="BQ11" s="6">
-        <v>6554</v>
+        <v>2380.89</v>
       </c>
       <c r="BR11" s="6">
-        <v>4134.08</v>
-      </c>
-      <c r="BS11" s="6"/>
+        <v>4426.6299999999992</v>
+      </c>
+      <c r="BS11" s="6">
+        <v>178.99</v>
+      </c>
       <c r="BT11" s="6">
-        <v>945.99</v>
+        <v>1224.97</v>
       </c>
       <c r="BU11" s="6">
-        <v>8310.99</v>
+        <v>13456.88</v>
       </c>
       <c r="BV11" s="6">
-        <v>499.89</v>
+        <v>7558.8599999999988</v>
       </c>
       <c r="BW11" s="6">
-        <v>3228.75</v>
+        <v>458.89</v>
       </c>
       <c r="BX11" s="6">
-        <v>3206.17</v>
+        <v>2459.4899999999998</v>
       </c>
       <c r="BY11" s="6">
-        <v>9850.7900000000009</v>
+        <v>6178.9699999999993</v>
       </c>
       <c r="BZ11" s="6">
-        <v>15403.699999999997</v>
+        <v>7253.8799999999992</v>
       </c>
       <c r="CA11" s="6">
-        <v>2409.38</v>
+        <v>4487.9799999999996</v>
       </c>
       <c r="CB11" s="6">
-        <v>4957.6899999999987</v>
+        <v>3422.97</v>
       </c>
       <c r="CC11" s="6">
-        <v>1020.99</v>
+        <v>10916.99</v>
       </c>
       <c r="CD11" s="6">
-        <v>1230</v>
+        <v>3967.9500000000003</v>
       </c>
       <c r="CE11" s="6">
-        <v>138.89000000000001</v>
+        <v>1182.79</v>
       </c>
       <c r="CF11" s="6"/>
       <c r="CG11" s="6">
-        <v>2443.58</v>
+        <v>1468.4599999999998</v>
       </c>
       <c r="CH11" s="6">
-        <v>3871.76</v>
+        <v>7226.98</v>
       </c>
       <c r="CI11" s="6">
-        <v>1264.99</v>
+        <v>707.99</v>
       </c>
       <c r="CJ11" s="6">
-        <v>13500.649999999998</v>
+        <v>2383.9899999999998</v>
       </c>
     </row>
     <row r="12" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6">
-        <v>2015.9700000000003</v>
-      </c>
-      <c r="D12" s="6">
-        <v>139.99</v>
-      </c>
+        <v>642.98</v>
+      </c>
+      <c r="D12" s="6"/>
       <c r="E12" s="6">
-        <v>169</v>
+        <v>258.99</v>
       </c>
       <c r="F12" s="6">
-        <v>4331.8099999999995</v>
+        <v>2625.86</v>
       </c>
       <c r="G12" s="6">
-        <v>5655.8899999999994</v>
+        <v>6394.74</v>
       </c>
       <c r="H12" s="6">
-        <v>2515.9699999999993</v>
+        <v>4528.3499999999995</v>
       </c>
       <c r="I12" s="6">
-        <v>5354.8799999999992</v>
+        <v>2328.21</v>
       </c>
       <c r="J12" s="6">
-        <v>1560.36</v>
+        <v>2216.89</v>
       </c>
       <c r="K12" s="6"/>
       <c r="L12" s="6">
-        <v>781.98</v>
+        <v>232.98000000000002</v>
       </c>
       <c r="M12" s="6"/>
-      <c r="N12" s="6">
-        <v>194.89</v>
-      </c>
+      <c r="N12" s="6"/>
       <c r="O12" s="6">
-        <v>710.87</v>
+        <v>854.78</v>
       </c>
       <c r="P12" s="6">
-        <v>2900.9499999999994</v>
+        <v>2998.55</v>
       </c>
       <c r="Q12" s="6">
-        <v>388</v>
-      </c>
-      <c r="R12" s="6">
-        <v>1841.5</v>
-      </c>
+        <v>140.99</v>
+      </c>
+      <c r="R12" s="6"/>
       <c r="S12" s="6">
-        <v>646.98</v>
+        <v>208.99</v>
       </c>
       <c r="T12" s="6">
-        <v>652</v>
-      </c>
-      <c r="U12" s="6">
-        <v>143.99</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U12" s="6"/>
       <c r="V12" s="6">
-        <v>178.99</v>
+        <v>425.59000000000003</v>
       </c>
       <c r="W12" s="6">
-        <v>4725.78</v>
+        <v>2501.89</v>
       </c>
       <c r="X12" s="6">
-        <v>154.97</v>
+        <v>1640.96</v>
       </c>
       <c r="Y12" s="6">
-        <v>20.97</v>
+        <v>83.800000000000011</v>
       </c>
       <c r="Z12" s="6">
-        <v>4273.76</v>
+        <v>3430.88</v>
       </c>
       <c r="AA12" s="6">
-        <v>1945.99</v>
+        <v>234</v>
       </c>
       <c r="AB12" s="6">
-        <v>2002.89</v>
-      </c>
-      <c r="AC12" s="6"/>
+        <v>59</v>
+      </c>
+      <c r="AC12" s="6">
+        <v>39.99</v>
+      </c>
       <c r="AD12" s="6">
-        <v>35.99</v>
+        <v>536.99</v>
       </c>
       <c r="AE12" s="6">
-        <v>274.98</v>
+        <v>112.47999999999999</v>
       </c>
       <c r="AF12" s="6">
-        <v>2286.79</v>
+        <v>625.99</v>
       </c>
       <c r="AG12" s="6">
-        <v>51.980000000000004</v>
+        <v>819.68</v>
       </c>
       <c r="AH12" s="6"/>
       <c r="AI12" s="6">
-        <v>1036.8800000000001</v>
+        <v>1506.5500000000002</v>
       </c>
       <c r="AJ12" s="6">
-        <v>1655</v>
+        <v>1035.98</v>
       </c>
       <c r="AK12" s="6">
-        <v>3234.88</v>
+        <v>59.9</v>
       </c>
       <c r="AL12" s="6">
-        <v>10738.64</v>
+        <v>6707.77</v>
       </c>
       <c r="AM12" s="6">
-        <v>1864.7900000000002</v>
+        <v>2337.96</v>
       </c>
       <c r="AN12" s="6">
-        <v>3325.79</v>
+        <v>284.78000000000003</v>
       </c>
       <c r="AO12" s="6">
-        <v>2182.84</v>
+        <v>777.87</v>
       </c>
       <c r="AP12" s="6">
-        <v>947.98</v>
+        <v>1192.8899999999999</v>
       </c>
       <c r="AQ12" s="6">
-        <v>1708.5900000000001</v>
+        <v>3049.37</v>
       </c>
       <c r="AR12" s="6">
-        <v>596.78</v>
+        <v>2127</v>
       </c>
       <c r="AS12" s="6">
-        <v>977.99</v>
+        <v>638.97</v>
       </c>
       <c r="AT12" s="6">
-        <v>176.89000000000001</v>
+        <v>235</v>
       </c>
       <c r="AU12" s="6">
-        <v>878.99</v>
+        <v>799</v>
       </c>
       <c r="AV12" s="6">
-        <v>1466.9</v>
+        <v>399</v>
       </c>
       <c r="AW12" s="6"/>
       <c r="AX12" s="6">
-        <v>1271.99</v>
+        <v>140.99</v>
       </c>
       <c r="AY12" s="6">
-        <v>2371.0100000000002</v>
-      </c>
-      <c r="AZ12" s="6">
-        <v>13751.9</v>
-      </c>
-      <c r="BA12" s="6"/>
+        <v>849</v>
+      </c>
+      <c r="AZ12" s="6"/>
+      <c r="BA12" s="6">
+        <v>44.99</v>
+      </c>
       <c r="BB12" s="6">
-        <v>708.91</v>
+        <v>0.99000000000000199</v>
       </c>
       <c r="BC12" s="6">
-        <v>1773.98</v>
+        <v>6420.7899999999981</v>
       </c>
       <c r="BD12" s="6"/>
       <c r="BE12" s="6">
-        <v>1979.93</v>
+        <v>1188.98</v>
       </c>
       <c r="BF12" s="6"/>
-      <c r="BG12" s="6">
-        <v>1863.6799999999998</v>
-      </c>
-      <c r="BH12" s="6">
-        <v>319.97000000000003</v>
-      </c>
-      <c r="BI12" s="6">
-        <v>1791</v>
-      </c>
-      <c r="BJ12" s="6">
-        <v>1788.98</v>
-      </c>
-      <c r="BK12" s="6">
-        <v>3293.8689999999997</v>
-      </c>
-      <c r="BL12" s="6">
-        <v>716.09000000000015</v>
-      </c>
+      <c r="BG12" s="6"/>
+      <c r="BH12" s="6"/>
+      <c r="BI12" s="6"/>
+      <c r="BJ12" s="6"/>
+      <c r="BK12" s="6"/>
+      <c r="BL12" s="6"/>
       <c r="BM12" s="6">
-        <v>318</v>
-      </c>
-      <c r="BN12" s="6">
-        <v>1489.98</v>
-      </c>
-      <c r="BO12" s="6">
-        <v>2859.99</v>
-      </c>
-      <c r="BP12" s="6">
-        <v>7917.869999999999</v>
-      </c>
-      <c r="BQ12" s="6">
-        <v>2380.89</v>
-      </c>
+        <v>238.98000000000002</v>
+      </c>
+      <c r="BN12" s="6"/>
+      <c r="BO12" s="6"/>
+      <c r="BP12" s="6"/>
+      <c r="BQ12" s="6"/>
       <c r="BR12" s="6">
-        <v>4426.6299999999992</v>
-      </c>
-      <c r="BS12" s="6">
-        <v>178.99</v>
-      </c>
+        <v>3784.1999999999994</v>
+      </c>
+      <c r="BS12" s="6"/>
       <c r="BT12" s="6">
-        <v>1224.97</v>
-      </c>
-      <c r="BU12" s="6">
-        <v>13456.88</v>
-      </c>
-      <c r="BV12" s="6">
-        <v>7558.8599999999988</v>
-      </c>
+        <v>760.97</v>
+      </c>
+      <c r="BU12" s="6"/>
+      <c r="BV12" s="6"/>
       <c r="BW12" s="6">
-        <v>458.89</v>
+        <v>433.98</v>
       </c>
       <c r="BX12" s="6">
-        <v>2459.4899999999998</v>
-      </c>
-      <c r="BY12" s="6">
-        <v>6178.9699999999993</v>
-      </c>
-      <c r="BZ12" s="6">
-        <v>7253.8799999999992</v>
-      </c>
+        <v>1832.59</v>
+      </c>
+      <c r="BY12" s="6"/>
+      <c r="BZ12" s="6"/>
       <c r="CA12" s="6">
-        <v>4487.9799999999996</v>
-      </c>
-      <c r="CB12" s="6">
-        <v>3422.97</v>
-      </c>
+        <v>1722.86</v>
+      </c>
+      <c r="CB12" s="6"/>
       <c r="CC12" s="6">
-        <v>10916.99</v>
+        <v>4728.8599999999997</v>
       </c>
       <c r="CD12" s="6">
-        <v>3967.9500000000003</v>
+        <v>277.98</v>
       </c>
       <c r="CE12" s="6">
-        <v>1182.79</v>
+        <v>44.99</v>
       </c>
       <c r="CF12" s="6"/>
       <c r="CG12" s="6">
-        <v>1468.4599999999998</v>
+        <v>1719.19</v>
       </c>
       <c r="CH12" s="6">
-        <v>7226.98</v>
+        <v>505.89</v>
       </c>
       <c r="CI12" s="6">
-        <v>707.99</v>
-      </c>
-      <c r="CJ12" s="6">
-        <v>2383.9899999999998</v>
-      </c>
+        <v>349.99</v>
+      </c>
+      <c r="CJ12" s="6"/>
     </row>
     <row r="13" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13" s="6">
-        <v>531.9</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="B13" s="6"/>
       <c r="C13" s="6">
-        <v>978</v>
-      </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
+        <v>4313.99</v>
+      </c>
+      <c r="D13" s="6">
+        <v>168.99</v>
+      </c>
+      <c r="E13" s="6">
+        <v>69</v>
+      </c>
       <c r="F13" s="6">
-        <v>1400.3</v>
+        <v>1981.83</v>
       </c>
       <c r="G13" s="6">
-        <v>6823.59</v>
+        <v>10330.039999999999</v>
       </c>
       <c r="H13" s="6">
-        <v>4529.55</v>
+        <v>6533.7399999999989</v>
       </c>
       <c r="I13" s="6">
-        <v>592.67999999999995</v>
+        <v>3421.6800000000003</v>
       </c>
       <c r="J13" s="6">
-        <v>1077.98</v>
-      </c>
-      <c r="K13" s="6"/>
+        <v>596.9</v>
+      </c>
+      <c r="K13" s="6">
+        <v>453.99</v>
+      </c>
       <c r="L13" s="6">
-        <v>280.38</v>
+        <v>57.980000000000004</v>
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6">
-        <v>592.9</v>
+        <v>50.89</v>
       </c>
       <c r="O13" s="6">
-        <v>1586.5900000000001</v>
+        <v>1172.7</v>
       </c>
       <c r="P13" s="6">
-        <v>7899.4800000000005</v>
-      </c>
-      <c r="Q13" s="6">
-        <v>217</v>
-      </c>
-      <c r="R13" s="6"/>
+        <v>9067.8599999999988</v>
+      </c>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6">
+        <v>5760</v>
+      </c>
       <c r="S13" s="6">
-        <v>615</v>
+        <v>198</v>
       </c>
       <c r="T13" s="6">
-        <v>129.99</v>
-      </c>
-      <c r="U13" s="6"/>
+        <v>441.89</v>
+      </c>
+      <c r="U13" s="6">
+        <v>4552.99</v>
+      </c>
       <c r="V13" s="6">
-        <v>631.78</v>
+        <v>223.99999999999997</v>
       </c>
       <c r="W13" s="6">
-        <v>7346.59</v>
+        <v>3597.86</v>
       </c>
       <c r="X13" s="6">
-        <v>1038.8799999999999</v>
+        <v>468.99</v>
       </c>
       <c r="Y13" s="6">
-        <v>205.8</v>
+        <v>1158</v>
       </c>
       <c r="Z13" s="6">
-        <v>3895.9</v>
+        <v>4535.99</v>
       </c>
       <c r="AA13" s="6">
-        <v>215.9</v>
+        <v>4450.9799999999996</v>
       </c>
       <c r="AB13" s="6">
-        <v>652.99</v>
-      </c>
-      <c r="AC13" s="6">
-        <v>79.900000000000006</v>
-      </c>
+        <v>1496</v>
+      </c>
+      <c r="AC13" s="6"/>
       <c r="AD13" s="6">
-        <v>1590.9</v>
+        <v>3983.99</v>
       </c>
       <c r="AE13" s="6">
-        <v>114.97999999999999</v>
+        <v>457.87</v>
       </c>
       <c r="AF13" s="6">
-        <v>1974.99</v>
+        <v>6648.7999999999993</v>
       </c>
       <c r="AG13" s="6">
-        <v>1483.7</v>
-      </c>
-      <c r="AH13" s="6"/>
+        <v>962.75</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>389.97</v>
+      </c>
       <c r="AI13" s="6">
-        <v>2775.5800000000004</v>
-      </c>
-      <c r="AJ13" s="6">
-        <v>2531.8900000000003</v>
-      </c>
+        <v>5082.68</v>
+      </c>
+      <c r="AJ13" s="6"/>
       <c r="AK13" s="6">
-        <v>666</v>
+        <v>351.97</v>
       </c>
       <c r="AL13" s="6">
-        <v>3758.82</v>
+        <v>10013.549999999999</v>
       </c>
       <c r="AM13" s="6">
-        <v>2236.1799999999998</v>
+        <v>2946.8499999999995</v>
       </c>
       <c r="AN13" s="6">
-        <v>1052.8799999999999</v>
+        <v>948.66000000000008</v>
       </c>
       <c r="AO13" s="6">
-        <v>7835.9599999999991</v>
+        <v>1690.94</v>
       </c>
       <c r="AP13" s="6">
-        <v>1067.99</v>
+        <v>1342.79</v>
       </c>
       <c r="AQ13" s="6">
-        <v>5419.8499999999985</v>
+        <v>809.67</v>
       </c>
       <c r="AR13" s="6">
-        <v>703.98</v>
+        <v>2937.88</v>
       </c>
       <c r="AS13" s="6">
-        <v>1071.77</v>
-      </c>
-      <c r="AT13" s="6"/>
+        <v>480.99</v>
+      </c>
+      <c r="AT13" s="6">
+        <v>75</v>
+      </c>
       <c r="AU13" s="6">
-        <v>1763.89</v>
+        <v>99</v>
       </c>
       <c r="AV13" s="6">
-        <v>1481.3899999999999</v>
+        <v>2891.9799999999996</v>
       </c>
       <c r="AW13" s="6">
-        <v>90</v>
+        <v>128.99</v>
       </c>
       <c r="AX13" s="6">
-        <v>139.4</v>
+        <v>2079.8900000000003</v>
       </c>
       <c r="AY13" s="6">
-        <v>497</v>
-      </c>
-      <c r="AZ13" s="6"/>
+        <v>4300</v>
+      </c>
+      <c r="AZ13" s="6">
+        <v>5268.64</v>
+      </c>
       <c r="BA13" s="6">
-        <v>39.99</v>
+        <v>190</v>
       </c>
       <c r="BB13" s="6">
-        <v>406.89</v>
+        <v>1128</v>
       </c>
       <c r="BC13" s="6">
-        <v>5380.57</v>
-      </c>
-      <c r="BD13" s="6">
-        <v>59</v>
-      </c>
+        <v>1927.7500000000002</v>
+      </c>
+      <c r="BD13" s="6"/>
       <c r="BE13" s="6">
-        <v>1315.97</v>
+        <v>612.99</v>
       </c>
       <c r="BF13" s="6"/>
-      <c r="BG13" s="6"/>
-      <c r="BH13" s="6"/>
-      <c r="BI13" s="6"/>
-      <c r="BJ13" s="6"/>
-      <c r="BK13" s="6"/>
-      <c r="BL13" s="6"/>
+      <c r="BG13" s="6">
+        <v>6229.8899999999994</v>
+      </c>
+      <c r="BH13" s="6">
+        <v>2325</v>
+      </c>
+      <c r="BI13" s="6">
+        <v>4810</v>
+      </c>
+      <c r="BJ13" s="6">
+        <v>10420.98</v>
+      </c>
+      <c r="BK13" s="6">
+        <v>11459.88</v>
+      </c>
+      <c r="BL13" s="6">
+        <v>9578.9</v>
+      </c>
       <c r="BM13" s="6">
-        <v>108</v>
-      </c>
-      <c r="BN13" s="6"/>
-      <c r="BO13" s="6"/>
-      <c r="BP13" s="6"/>
-      <c r="BQ13" s="6"/>
+        <v>89.99</v>
+      </c>
+      <c r="BN13" s="6">
+        <v>10274.069999999998</v>
+      </c>
+      <c r="BO13" s="6">
+        <v>598</v>
+      </c>
+      <c r="BP13" s="6">
+        <v>5594.8899999999994</v>
+      </c>
+      <c r="BQ13" s="6">
+        <v>3906.8</v>
+      </c>
       <c r="BR13" s="6">
-        <v>3220.68</v>
-      </c>
-      <c r="BS13" s="6"/>
+        <v>3819.4500000000003</v>
+      </c>
+      <c r="BS13" s="6">
+        <v>1399</v>
+      </c>
       <c r="BT13" s="6">
-        <v>421.99</v>
-      </c>
-      <c r="BU13" s="6"/>
-      <c r="BV13" s="6"/>
+        <v>5920.4</v>
+      </c>
+      <c r="BU13" s="6">
+        <v>9115.99</v>
+      </c>
+      <c r="BV13" s="6">
+        <v>6195.9699999999993</v>
+      </c>
       <c r="BW13" s="6">
-        <v>353</v>
+        <v>153.97</v>
       </c>
       <c r="BX13" s="6">
-        <v>4315.79</v>
-      </c>
-      <c r="BY13" s="6"/>
-      <c r="BZ13" s="6"/>
+        <v>2482.9700000000003</v>
+      </c>
+      <c r="BY13" s="6">
+        <v>14530.98</v>
+      </c>
+      <c r="BZ13" s="6">
+        <v>2731.94</v>
+      </c>
       <c r="CA13" s="6">
-        <v>1929.68</v>
-      </c>
-      <c r="CB13" s="6"/>
+        <v>4154.8500000000004</v>
+      </c>
+      <c r="CB13" s="6">
+        <v>3565.9399999999996</v>
+      </c>
       <c r="CC13" s="6">
-        <v>3971.98</v>
+        <v>3470</v>
       </c>
       <c r="CD13" s="6">
-        <v>1428.98</v>
+        <v>2811</v>
       </c>
       <c r="CE13" s="6">
-        <v>374.87</v>
-      </c>
-      <c r="CF13" s="6"/>
+        <v>508.87</v>
+      </c>
+      <c r="CF13" s="6">
+        <v>44.99</v>
+      </c>
       <c r="CG13" s="6">
-        <v>886.8</v>
+        <v>1209.29</v>
       </c>
       <c r="CH13" s="6">
-        <v>6247.5999999999995</v>
+        <v>411.78</v>
       </c>
       <c r="CI13" s="6">
-        <v>1945.89</v>
-      </c>
-      <c r="CJ13" s="6"/>
+        <v>429.96000000000004</v>
+      </c>
+      <c r="CJ13" s="6">
+        <v>22673.559999999998</v>
+      </c>
     </row>
     <row r="14" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6">
-        <v>642.98</v>
-      </c>
-      <c r="D14" s="6"/>
+        <v>4982.8399999999983</v>
+      </c>
+      <c r="D14" s="6">
+        <v>4.9000000000000004</v>
+      </c>
       <c r="E14" s="6">
-        <v>258.99</v>
+        <v>228.99</v>
       </c>
       <c r="F14" s="6">
-        <v>2625.86</v>
+        <v>8021.9599999999991</v>
       </c>
       <c r="G14" s="6">
-        <v>6394.74</v>
+        <v>4707.829999999999</v>
       </c>
       <c r="H14" s="6">
-        <v>4528.3499999999995</v>
+        <v>5987.49</v>
       </c>
       <c r="I14" s="6">
-        <v>2328.21</v>
+        <v>3042.8699999999994</v>
       </c>
       <c r="J14" s="6">
-        <v>2216.89</v>
-      </c>
-      <c r="K14" s="6"/>
+        <v>1756.5600000000002</v>
+      </c>
+      <c r="K14" s="6">
+        <v>3113.99</v>
+      </c>
       <c r="L14" s="6">
-        <v>232.98000000000002</v>
+        <v>471.99</v>
       </c>
       <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
+      <c r="N14" s="6">
+        <v>3455.48</v>
+      </c>
       <c r="O14" s="6">
-        <v>854.78</v>
+        <v>979.9</v>
       </c>
       <c r="P14" s="6">
-        <v>2998.55</v>
+        <v>1143.8800000000001</v>
       </c>
       <c r="Q14" s="6">
-        <v>140.99</v>
-      </c>
-      <c r="R14" s="6"/>
+        <v>277.98</v>
+      </c>
+      <c r="R14" s="6">
+        <v>7537.78</v>
+      </c>
       <c r="S14" s="6">
-        <v>208.99</v>
+        <v>307.99</v>
       </c>
       <c r="T14" s="6">
-        <v>0</v>
-      </c>
-      <c r="U14" s="6"/>
+        <v>777</v>
+      </c>
+      <c r="U14" s="6">
+        <v>18656.900000000001</v>
+      </c>
       <c r="V14" s="6">
-        <v>425.59000000000003</v>
+        <v>84.47</v>
       </c>
       <c r="W14" s="6">
-        <v>2501.89</v>
+        <v>6162.3499999999985</v>
       </c>
       <c r="X14" s="6">
-        <v>1640.96</v>
+        <v>295.88</v>
       </c>
       <c r="Y14" s="6">
-        <v>83.800000000000011</v>
+        <v>2185.8900000000003</v>
       </c>
       <c r="Z14" s="6">
-        <v>3430.88</v>
+        <v>4344.4799999999996</v>
       </c>
       <c r="AA14" s="6">
-        <v>234</v>
-      </c>
-      <c r="AB14" s="6">
-        <v>59</v>
-      </c>
+        <v>4067.7799999999997</v>
+      </c>
+      <c r="AB14" s="6"/>
       <c r="AC14" s="6">
-        <v>39.99</v>
+        <v>124.97999999999999</v>
       </c>
       <c r="AD14" s="6">
-        <v>536.99</v>
+        <v>219</v>
       </c>
       <c r="AE14" s="6">
-        <v>112.47999999999999</v>
+        <v>273.77</v>
       </c>
       <c r="AF14" s="6">
-        <v>625.99</v>
+        <v>2816.98</v>
       </c>
       <c r="AG14" s="6">
-        <v>819.68</v>
-      </c>
-      <c r="AH14" s="6"/>
+        <v>2155.8900000000003</v>
+      </c>
+      <c r="AH14" s="6">
+        <v>129.99</v>
+      </c>
       <c r="AI14" s="6">
-        <v>1506.5500000000002</v>
+        <v>2123.6800000000003</v>
       </c>
       <c r="AJ14" s="6">
-        <v>1035.98</v>
+        <v>582</v>
       </c>
       <c r="AK14" s="6">
-        <v>59.9</v>
+        <v>1073</v>
       </c>
       <c r="AL14" s="6">
-        <v>6707.77</v>
+        <v>12914.56</v>
       </c>
       <c r="AM14" s="6">
-        <v>2337.96</v>
+        <v>2270.9599999999996</v>
       </c>
       <c r="AN14" s="6">
-        <v>284.78000000000003</v>
+        <v>3012.6799999999994</v>
       </c>
       <c r="AO14" s="6">
-        <v>777.87</v>
+        <v>3184.99</v>
       </c>
       <c r="AP14" s="6">
-        <v>1192.8899999999999</v>
+        <v>5308.69</v>
       </c>
       <c r="AQ14" s="6">
-        <v>3049.37</v>
+        <v>649.07999999999993</v>
       </c>
       <c r="AR14" s="6">
-        <v>2127</v>
+        <v>2499</v>
       </c>
       <c r="AS14" s="6">
-        <v>638.97</v>
+        <v>3254.9</v>
       </c>
       <c r="AT14" s="6">
-        <v>235</v>
+        <v>384.98</v>
       </c>
       <c r="AU14" s="6">
-        <v>799</v>
+        <v>1026</v>
       </c>
       <c r="AV14" s="6">
-        <v>399</v>
-      </c>
-      <c r="AW14" s="6"/>
+        <v>2906.8</v>
+      </c>
+      <c r="AW14" s="6">
+        <v>437.89</v>
+      </c>
       <c r="AX14" s="6">
-        <v>140.99</v>
+        <v>2915</v>
       </c>
       <c r="AY14" s="6">
-        <v>849</v>
-      </c>
-      <c r="AZ14" s="6"/>
+        <v>5605.99</v>
+      </c>
+      <c r="AZ14" s="6">
+        <v>6448.8899999999994</v>
+      </c>
       <c r="BA14" s="6">
-        <v>44.99</v>
+        <v>89.98</v>
       </c>
       <c r="BB14" s="6">
-        <v>0.99000000000000199</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="BC14" s="6">
-        <v>6420.7899999999981</v>
-      </c>
-      <c r="BD14" s="6"/>
+        <v>1756.97</v>
+      </c>
+      <c r="BD14" s="6">
+        <v>174.97</v>
+      </c>
       <c r="BE14" s="6">
-        <v>1188.98</v>
+        <v>1295.8400000000001</v>
       </c>
       <c r="BF14" s="6"/>
-      <c r="BG14" s="6"/>
-      <c r="BH14" s="6"/>
-      <c r="BI14" s="6"/>
-      <c r="BJ14" s="6"/>
-      <c r="BK14" s="6"/>
-      <c r="BL14" s="6"/>
+      <c r="BG14" s="6">
+        <v>20536.879999999997</v>
+      </c>
+      <c r="BH14" s="6">
+        <v>4366.99</v>
+      </c>
+      <c r="BI14" s="6">
+        <v>7188.99</v>
+      </c>
+      <c r="BJ14" s="6">
+        <v>10718.79</v>
+      </c>
+      <c r="BK14" s="6">
+        <v>7148.8899999999994</v>
+      </c>
+      <c r="BL14" s="6">
+        <v>22201.989999999998</v>
+      </c>
       <c r="BM14" s="6">
-        <v>238.98000000000002</v>
-      </c>
-      <c r="BN14" s="6"/>
-      <c r="BO14" s="6"/>
-      <c r="BP14" s="6"/>
-      <c r="BQ14" s="6"/>
+        <v>134</v>
+      </c>
+      <c r="BN14" s="6">
+        <v>3463.9999999999995</v>
+      </c>
+      <c r="BO14" s="6">
+        <v>11875.99</v>
+      </c>
+      <c r="BP14" s="6">
+        <v>740.89</v>
+      </c>
+      <c r="BQ14" s="6">
+        <v>2373</v>
+      </c>
       <c r="BR14" s="6">
-        <v>3784.1999999999994</v>
+        <v>5263.69</v>
       </c>
       <c r="BS14" s="6"/>
       <c r="BT14" s="6">
-        <v>760.97</v>
-      </c>
-      <c r="BU14" s="6"/>
-      <c r="BV14" s="6"/>
+        <v>820.98</v>
+      </c>
+      <c r="BU14" s="6">
+        <v>9914.869999999999</v>
+      </c>
+      <c r="BV14" s="6">
+        <v>10083.759999999998</v>
+      </c>
       <c r="BW14" s="6">
-        <v>433.98</v>
+        <v>317</v>
       </c>
       <c r="BX14" s="6">
-        <v>1832.59</v>
-      </c>
-      <c r="BY14" s="6"/>
-      <c r="BZ14" s="6"/>
+        <v>1605.4899999999998</v>
+      </c>
+      <c r="BY14" s="6">
+        <v>7703.59</v>
+      </c>
+      <c r="BZ14" s="6">
+        <v>20972.879999999997</v>
+      </c>
       <c r="CA14" s="6">
-        <v>1722.86</v>
-      </c>
-      <c r="CB14" s="6"/>
+        <v>5071.2599999999993</v>
+      </c>
+      <c r="CB14" s="6">
+        <v>4703.8499999999995</v>
+      </c>
       <c r="CC14" s="6">
-        <v>4728.8599999999997</v>
+        <v>2940.99</v>
       </c>
       <c r="CD14" s="6">
-        <v>277.98</v>
+        <v>4332</v>
       </c>
       <c r="CE14" s="6">
+        <v>1526.89</v>
+      </c>
+      <c r="CF14" s="6">
         <v>44.99</v>
       </c>
-      <c r="CF14" s="6"/>
       <c r="CG14" s="6">
-        <v>1719.19</v>
+        <v>967.96</v>
       </c>
       <c r="CH14" s="6">
-        <v>505.89</v>
+        <v>6283.8899999999994</v>
       </c>
       <c r="CI14" s="6">
-        <v>349.99</v>
-      </c>
-      <c r="CJ14" s="6"/>
+        <v>401.93</v>
+      </c>
+      <c r="CJ14" s="6">
+        <v>29391.550000000003</v>
+      </c>
     </row>
     <row r="15" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15" s="6">
-        <v>3097.69</v>
+        <v>0</v>
       </c>
       <c r="C15" s="6">
-        <v>6402.99</v>
-      </c>
-      <c r="D15" s="6">
-        <v>328.88</v>
-      </c>
-      <c r="E15" s="6">
-        <v>79</v>
-      </c>
+        <v>7263.8499999999995</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="6">
-        <v>4730.9699999999993</v>
+        <v>2284</v>
       </c>
       <c r="G15" s="6">
-        <v>12481.88</v>
+        <v>8548.82</v>
       </c>
       <c r="H15" s="6">
-        <v>13231.689999999999</v>
+        <v>739.85</v>
       </c>
       <c r="I15" s="6">
-        <v>727.88</v>
+        <v>5000.66</v>
       </c>
       <c r="J15" s="6">
-        <v>7113.8899999999994</v>
+        <v>454.49</v>
       </c>
       <c r="K15" s="6">
-        <v>2618</v>
-      </c>
-      <c r="L15" s="6"/>
+        <v>4942.4799999999996</v>
+      </c>
+      <c r="L15" s="6">
+        <v>134.97999999999999</v>
+      </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6">
-        <v>4336.8799999999992</v>
+        <v>1961.99</v>
       </c>
       <c r="O15" s="6">
-        <v>587.79999999999995</v>
+        <v>617.96</v>
       </c>
       <c r="P15" s="6">
-        <v>1667.17</v>
+        <v>4120.2800000000007</v>
       </c>
       <c r="Q15" s="6">
-        <v>607</v>
+        <v>159</v>
       </c>
       <c r="R15" s="6">
-        <v>12676.89</v>
+        <v>1595</v>
       </c>
       <c r="S15" s="6">
-        <v>345.7</v>
+        <v>2457</v>
       </c>
       <c r="T15" s="6">
-        <v>12.99</v>
+        <v>-70</v>
       </c>
       <c r="U15" s="6">
-        <v>3142.9</v>
+        <v>5551.7899999999991</v>
       </c>
       <c r="V15" s="6">
-        <v>720.79</v>
+        <v>169.87</v>
       </c>
       <c r="W15" s="6">
-        <v>4956.99</v>
+        <v>4102.67</v>
       </c>
       <c r="X15" s="6">
-        <v>2271.29</v>
+        <v>1420.8000000000002</v>
       </c>
       <c r="Y15" s="6">
-        <v>3794.79</v>
+        <v>5149.88</v>
       </c>
       <c r="Z15" s="6">
-        <v>6046.7899999999991</v>
+        <v>7789.99</v>
       </c>
       <c r="AA15" s="6">
-        <v>2133.9899999999998</v>
+        <v>2196</v>
       </c>
       <c r="AB15" s="6">
-        <v>413</v>
-      </c>
-      <c r="AC15" s="6"/>
+        <v>1966.99</v>
+      </c>
+      <c r="AC15" s="6">
+        <v>392.98</v>
+      </c>
       <c r="AD15" s="6">
-        <v>2803.89</v>
+        <v>1222</v>
       </c>
       <c r="AE15" s="6">
-        <v>133.60000000000002</v>
+        <v>268.77999999999997</v>
       </c>
       <c r="AF15" s="6">
-        <v>1161.99</v>
+        <v>2679.99</v>
       </c>
       <c r="AG15" s="6">
-        <v>2003.6</v>
+        <v>1354.67</v>
       </c>
       <c r="AH15" s="6"/>
       <c r="AI15" s="6">
-        <v>7702.2599999999993</v>
+        <v>1678.4700000000005</v>
       </c>
       <c r="AJ15" s="6">
-        <v>227</v>
-      </c>
-      <c r="AK15" s="6">
-        <v>2320.89</v>
-      </c>
+        <v>186.88</v>
+      </c>
+      <c r="AK15" s="6"/>
       <c r="AL15" s="6">
-        <v>11647.789999999999</v>
+        <v>8565.8599999999988</v>
       </c>
       <c r="AM15" s="6">
-        <v>2774.69</v>
+        <v>1626.89</v>
       </c>
       <c r="AN15" s="6">
-        <v>1978.97</v>
+        <v>1619.58</v>
       </c>
       <c r="AO15" s="6">
-        <v>2029.9899999999998</v>
+        <v>3067.89</v>
       </c>
       <c r="AP15" s="6">
-        <v>2412.79</v>
+        <v>1612.77</v>
       </c>
       <c r="AQ15" s="6">
-        <v>2896.7799999999997</v>
+        <v>902.66</v>
       </c>
       <c r="AR15" s="6">
-        <v>3396.99</v>
+        <v>1951.97</v>
       </c>
       <c r="AS15" s="6">
-        <v>1327</v>
+        <v>1030.98</v>
       </c>
       <c r="AT15" s="6">
-        <v>188</v>
+        <v>547.98</v>
       </c>
       <c r="AU15" s="6">
-        <v>843</v>
+        <v>124.97</v>
       </c>
       <c r="AV15" s="6">
-        <v>1866.98</v>
+        <v>4514</v>
       </c>
       <c r="AW15" s="6">
-        <v>286.99</v>
+        <v>74.009999999999991</v>
       </c>
       <c r="AX15" s="6">
-        <v>5172.7</v>
+        <v>1512.99</v>
       </c>
       <c r="AY15" s="6">
-        <v>3729.9</v>
+        <v>5125.9799999999996</v>
       </c>
       <c r="AZ15" s="6">
-        <v>12036.669999999998</v>
+        <v>4251.9499999999989</v>
       </c>
       <c r="BA15" s="6">
-        <v>291.89</v>
+        <v>168.99</v>
       </c>
       <c r="BB15" s="6">
-        <v>575.88</v>
+        <v>219.98000000000002</v>
       </c>
       <c r="BC15" s="6">
-        <v>6805.4499999999989</v>
-      </c>
-      <c r="BD15" s="6">
-        <v>49</v>
-      </c>
+        <v>3873.37</v>
+      </c>
+      <c r="BD15" s="6"/>
       <c r="BE15" s="6">
-        <v>1591.8600000000001</v>
+        <v>455.86</v>
       </c>
       <c r="BF15" s="6"/>
       <c r="BG15" s="6">
-        <v>3957.69</v>
+        <v>14342.539999999999</v>
       </c>
       <c r="BH15" s="6">
-        <v>899.6</v>
+        <v>2241.9899999999998</v>
       </c>
       <c r="BI15" s="6">
-        <v>5346.9</v>
+        <v>7053</v>
       </c>
       <c r="BJ15" s="6">
-        <v>950</v>
+        <v>5120.8999999999996</v>
       </c>
       <c r="BK15" s="6">
-        <v>13510.689999999999</v>
+        <v>3982.9399999999996</v>
       </c>
       <c r="BL15" s="6">
-        <v>5819</v>
+        <v>2913.9799999999996</v>
       </c>
       <c r="BM15" s="6">
-        <v>386.9</v>
+        <v>327.99</v>
       </c>
       <c r="BN15" s="6">
-        <v>7119</v>
+        <v>10925.88</v>
       </c>
       <c r="BO15" s="6">
-        <v>5503.8</v>
+        <v>3541.98</v>
       </c>
       <c r="BP15" s="6">
-        <v>285</v>
+        <v>5474.8499999999995</v>
       </c>
       <c r="BQ15" s="6">
-        <v>3441.8899999999994</v>
+        <v>4845</v>
       </c>
       <c r="BR15" s="6">
-        <v>2125.4700000000003</v>
-      </c>
-      <c r="BS15" s="6"/>
+        <v>3942.6800000000003</v>
+      </c>
+      <c r="BS15" s="6">
+        <v>49.99</v>
+      </c>
       <c r="BT15" s="6">
-        <v>347.89</v>
+        <v>682.89</v>
       </c>
       <c r="BU15" s="6">
-        <v>5865.9</v>
+        <v>6157.9699999999993</v>
       </c>
       <c r="BV15" s="6">
-        <v>233.60000000000002</v>
+        <v>2999.79</v>
       </c>
       <c r="BW15" s="6">
-        <v>845.89</v>
+        <v>2306.89</v>
       </c>
       <c r="BX15" s="6">
-        <v>2152.38</v>
+        <v>6037.6900000000005</v>
       </c>
       <c r="BY15" s="6">
-        <v>13716.9</v>
+        <v>9892.89</v>
       </c>
       <c r="BZ15" s="6">
-        <v>17080.979999999996</v>
+        <v>8967.5</v>
       </c>
       <c r="CA15" s="6">
-        <v>1092.0899999999997</v>
+        <v>6951.98</v>
       </c>
       <c r="CB15" s="6">
-        <v>1536.9</v>
+        <v>1124.8399999999997</v>
       </c>
       <c r="CC15" s="6">
-        <v>2139.9899999999998</v>
+        <v>6111.99</v>
       </c>
       <c r="CD15" s="6">
-        <v>797.99</v>
+        <v>418.99</v>
       </c>
       <c r="CE15" s="6">
-        <v>693.68999999999994</v>
+        <v>245.95000000000005</v>
       </c>
       <c r="CF15" s="6"/>
       <c r="CG15" s="6">
-        <v>2034.56</v>
+        <v>3092.09</v>
       </c>
       <c r="CH15" s="6">
-        <v>921.8</v>
+        <v>970.9</v>
       </c>
       <c r="CI15" s="6">
-        <v>597</v>
+        <v>445.85</v>
       </c>
       <c r="CJ15" s="6">
-        <v>20853.099999999999</v>
+        <v>16275.859999999999</v>
       </c>
     </row>
     <row r="16" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="6"/>
+        <v>105</v>
+      </c>
+      <c r="B16" s="6">
+        <v>2069</v>
+      </c>
       <c r="C16" s="6">
-        <v>4313.99</v>
+        <v>4173.9519999999993</v>
       </c>
       <c r="D16" s="6">
-        <v>168.99</v>
+        <v>42.9</v>
       </c>
       <c r="E16" s="6">
-        <v>69</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="F16" s="6">
-        <v>1981.83</v>
+        <v>2257.17</v>
       </c>
       <c r="G16" s="6">
-        <v>10330.039999999999</v>
+        <v>16516.96</v>
       </c>
       <c r="H16" s="6">
-        <v>6533.7399999999989</v>
+        <v>4018.69</v>
       </c>
       <c r="I16" s="6">
-        <v>3421.6800000000003</v>
-      </c>
-      <c r="J16" s="6">
-        <v>596.9</v>
-      </c>
+        <v>7124.74</v>
+      </c>
+      <c r="J16" s="6"/>
       <c r="K16" s="6">
-        <v>453.99</v>
+        <v>59</v>
       </c>
       <c r="L16" s="6">
-        <v>57.980000000000004</v>
-      </c>
-      <c r="M16" s="6"/>
+        <v>489.89</v>
+      </c>
+      <c r="M16" s="6">
+        <v>0</v>
+      </c>
       <c r="N16" s="6">
-        <v>50.89</v>
+        <v>1108.97</v>
       </c>
       <c r="O16" s="6">
-        <v>1172.7</v>
+        <v>1274.8699999999999</v>
       </c>
       <c r="P16" s="6">
-        <v>9067.8599999999988</v>
+        <v>1186.94</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6">
-        <v>5760</v>
+        <v>10094.89</v>
       </c>
       <c r="S16" s="6">
-        <v>198</v>
+        <v>175.98000000000002</v>
       </c>
       <c r="T16" s="6">
-        <v>441.89</v>
+        <v>1338.89</v>
       </c>
       <c r="U16" s="6">
-        <v>4552.99</v>
+        <v>4894.9799999999996</v>
       </c>
       <c r="V16" s="6">
-        <v>223.99999999999997</v>
+        <v>416.79999999999995</v>
       </c>
       <c r="W16" s="6">
-        <v>3597.86</v>
+        <v>6578.8399999999992</v>
       </c>
       <c r="X16" s="6">
-        <v>468.99</v>
+        <v>1611.88</v>
       </c>
       <c r="Y16" s="6">
-        <v>1158</v>
+        <v>749</v>
       </c>
       <c r="Z16" s="6">
-        <v>4535.99</v>
+        <v>8030.98</v>
       </c>
       <c r="AA16" s="6">
-        <v>4450.9799999999996</v>
+        <v>7743.9</v>
       </c>
       <c r="AB16" s="6">
-        <v>1496</v>
-      </c>
-      <c r="AC16" s="6"/>
+        <v>-579</v>
+      </c>
+      <c r="AC16" s="6">
+        <v>285</v>
+      </c>
       <c r="AD16" s="6">
-        <v>3983.99</v>
+        <v>2105</v>
       </c>
       <c r="AE16" s="6">
-        <v>457.87</v>
+        <v>212.79000000000002</v>
       </c>
       <c r="AF16" s="6">
-        <v>6648.7999999999993</v>
+        <v>4608.8</v>
       </c>
       <c r="AG16" s="6">
-        <v>962.75</v>
-      </c>
-      <c r="AH16" s="6">
-        <v>389.97</v>
-      </c>
+        <v>4041.2000000000003</v>
+      </c>
+      <c r="AH16" s="6"/>
       <c r="AI16" s="6">
-        <v>5082.68</v>
-      </c>
-      <c r="AJ16" s="6"/>
+        <v>5024.57</v>
+      </c>
+      <c r="AJ16" s="6">
+        <v>368.98</v>
+      </c>
       <c r="AK16" s="6">
-        <v>351.97</v>
+        <v>2516.9899999999998</v>
       </c>
       <c r="AL16" s="6">
-        <v>10013.549999999999</v>
+        <v>12186.63</v>
       </c>
       <c r="AM16" s="6">
-        <v>2946.8499999999995</v>
+        <v>3288.5699999999997</v>
       </c>
       <c r="AN16" s="6">
-        <v>948.66000000000008</v>
+        <v>3228.38</v>
       </c>
       <c r="AO16" s="6">
-        <v>1690.94</v>
+        <v>1483.88</v>
       </c>
       <c r="AP16" s="6">
-        <v>1342.79</v>
+        <v>1841.97</v>
       </c>
       <c r="AQ16" s="6">
-        <v>809.67</v>
+        <v>1135.5700000000002</v>
       </c>
       <c r="AR16" s="6">
-        <v>2937.88</v>
+        <v>1050.99</v>
       </c>
       <c r="AS16" s="6">
-        <v>480.99</v>
+        <v>4484</v>
       </c>
       <c r="AT16" s="6">
-        <v>75</v>
+        <v>253</v>
       </c>
       <c r="AU16" s="6">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="AV16" s="6">
-        <v>2891.9799999999996</v>
+        <v>432.79</v>
       </c>
       <c r="AW16" s="6">
-        <v>128.99</v>
+        <v>1069.99</v>
       </c>
       <c r="AX16" s="6">
-        <v>2079.8900000000003</v>
+        <v>763.97</v>
       </c>
       <c r="AY16" s="6">
-        <v>4300</v>
+        <v>4116</v>
       </c>
       <c r="AZ16" s="6">
-        <v>5268.64</v>
-      </c>
-      <c r="BA16" s="6">
-        <v>190</v>
-      </c>
+        <v>3289.87</v>
+      </c>
+      <c r="BA16" s="6"/>
       <c r="BB16" s="6">
-        <v>1128</v>
+        <v>585.84</v>
       </c>
       <c r="BC16" s="6">
-        <v>1927.7500000000002</v>
+        <v>754.75</v>
       </c>
       <c r="BD16" s="6"/>
       <c r="BE16" s="6">
-        <v>612.99</v>
+        <v>103.99000000000001</v>
       </c>
       <c r="BF16" s="6"/>
       <c r="BG16" s="6">
-        <v>6229.8899999999994</v>
+        <v>21183.68</v>
       </c>
       <c r="BH16" s="6">
-        <v>2325</v>
+        <v>7942.98</v>
       </c>
       <c r="BI16" s="6">
-        <v>4810</v>
+        <v>5418.98</v>
       </c>
       <c r="BJ16" s="6">
-        <v>10420.98</v>
+        <v>14741.89</v>
       </c>
       <c r="BK16" s="6">
-        <v>11459.88</v>
+        <v>11933.789999999999</v>
       </c>
       <c r="BL16" s="6">
-        <v>9578.9</v>
-      </c>
-      <c r="BM16" s="6">
-        <v>89.99</v>
-      </c>
+        <v>4887.7800000000007</v>
+      </c>
+      <c r="BM16" s="6"/>
       <c r="BN16" s="6">
-        <v>10274.069999999998</v>
+        <v>5996.9</v>
       </c>
       <c r="BO16" s="6">
-        <v>598</v>
+        <v>1679.97</v>
       </c>
       <c r="BP16" s="6">
-        <v>5594.8899999999994</v>
+        <v>5701.98</v>
       </c>
       <c r="BQ16" s="6">
-        <v>3906.8</v>
+        <v>10396.450000000001</v>
       </c>
       <c r="BR16" s="6">
-        <v>3819.4500000000003</v>
+        <v>3709.59</v>
       </c>
       <c r="BS16" s="6">
-        <v>1399</v>
+        <v>49.9</v>
       </c>
       <c r="BT16" s="6">
-        <v>5920.4</v>
+        <v>3628</v>
       </c>
       <c r="BU16" s="6">
-        <v>9115.99</v>
+        <v>12430.98</v>
       </c>
       <c r="BV16" s="6">
-        <v>6195.9699999999993</v>
+        <v>5850.9399999999987</v>
       </c>
       <c r="BW16" s="6">
-        <v>153.97</v>
+        <v>174.99</v>
       </c>
       <c r="BX16" s="6">
-        <v>2482.9700000000003</v>
+        <v>1293.79</v>
       </c>
       <c r="BY16" s="6">
-        <v>14530.98</v>
+        <v>6147</v>
       </c>
       <c r="BZ16" s="6">
-        <v>2731.94</v>
+        <v>11911.789999999999</v>
       </c>
       <c r="CA16" s="6">
-        <v>4154.8500000000004</v>
+        <v>4013.6699999999992</v>
       </c>
       <c r="CB16" s="6">
-        <v>3565.9399999999996</v>
+        <v>1267.93</v>
       </c>
       <c r="CC16" s="6">
-        <v>3470</v>
+        <v>1299</v>
       </c>
       <c r="CD16" s="6">
-        <v>2811</v>
+        <v>536.99</v>
       </c>
       <c r="CE16" s="6">
-        <v>508.87</v>
-      </c>
-      <c r="CF16" s="6">
-        <v>44.99</v>
-      </c>
+        <v>1816.99</v>
+      </c>
+      <c r="CF16" s="6"/>
       <c r="CG16" s="6">
-        <v>1209.29</v>
+        <v>4585.6499999999996</v>
       </c>
       <c r="CH16" s="6">
-        <v>411.78</v>
+        <v>142.97999999999999</v>
       </c>
       <c r="CI16" s="6">
-        <v>429.96000000000004</v>
+        <v>1761.99</v>
       </c>
       <c r="CJ16" s="6">
-        <v>22673.559999999998</v>
+        <v>25133.469999999998</v>
       </c>
     </row>
     <row r="17" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B17" s="6">
-        <v>2330.0899999999997</v>
+        <v>1199</v>
       </c>
       <c r="C17" s="6">
-        <v>4312</v>
-      </c>
-      <c r="D17" s="6"/>
+        <v>1080</v>
+      </c>
+      <c r="D17" s="6">
+        <v>42.9</v>
+      </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6">
-        <v>2742.4799999999996</v>
+        <v>8602.58</v>
       </c>
       <c r="G17" s="6">
-        <v>6179.5899999999983</v>
+        <v>6297.44</v>
       </c>
       <c r="H17" s="6">
-        <v>10021.689999999999</v>
+        <v>4435.6899999999996</v>
       </c>
       <c r="I17" s="6">
-        <v>2317.75</v>
+        <v>3958.67</v>
       </c>
       <c r="J17" s="6">
-        <v>3437.88</v>
+        <v>1298.95</v>
       </c>
       <c r="K17" s="6">
-        <v>1897</v>
+        <v>5427</v>
       </c>
       <c r="L17" s="6">
-        <v>192.9</v>
+        <v>129.99</v>
       </c>
       <c r="M17" s="6"/>
       <c r="N17" s="6">
-        <v>224.99</v>
+        <v>1226.79</v>
       </c>
       <c r="O17" s="6">
-        <v>774.99</v>
+        <v>1062.98</v>
       </c>
       <c r="P17" s="6">
-        <v>3481.3800000000006</v>
-      </c>
-      <c r="Q17" s="6">
-        <v>49</v>
-      </c>
+        <v>4100.6899999999996</v>
+      </c>
+      <c r="Q17" s="6"/>
       <c r="R17" s="6">
-        <v>12404.8</v>
+        <v>11037.99</v>
       </c>
       <c r="S17" s="6">
-        <v>1016.78</v>
+        <v>150.99</v>
       </c>
       <c r="T17" s="6">
-        <v>129.99</v>
+        <v>44.99</v>
       </c>
       <c r="U17" s="6">
-        <v>103</v>
+        <v>6425.9900000000016</v>
       </c>
       <c r="V17" s="6">
-        <v>3070.9700000000003</v>
+        <v>1092.8</v>
       </c>
       <c r="W17" s="6">
-        <v>4475.7</v>
+        <v>2784.89</v>
       </c>
       <c r="X17" s="6">
-        <v>282.79000000000002</v>
+        <v>462.07</v>
       </c>
       <c r="Y17" s="6">
-        <v>1870.6000000000001</v>
+        <v>1355.9</v>
       </c>
       <c r="Z17" s="6">
-        <v>7732.5</v>
+        <v>3367.7799999999997</v>
       </c>
       <c r="AA17" s="6">
-        <v>1595.98</v>
+        <v>815.99</v>
       </c>
       <c r="AB17" s="6">
-        <v>1903.9</v>
-      </c>
-      <c r="AC17" s="6"/>
+        <v>597.99</v>
+      </c>
+      <c r="AC17" s="6">
+        <v>45</v>
+      </c>
       <c r="AD17" s="6">
-        <v>96.990000000000009</v>
+        <v>3474.89</v>
       </c>
       <c r="AE17" s="6">
-        <v>367.99</v>
+        <v>653.89</v>
       </c>
       <c r="AF17" s="6">
-        <v>9009.59</v>
+        <v>743.39</v>
       </c>
       <c r="AG17" s="6">
-        <v>1474.5</v>
+        <v>3281.7799999999997</v>
       </c>
       <c r="AH17" s="6"/>
       <c r="AI17" s="6">
-        <v>6201.1799999999994</v>
+        <v>5518.6399999999994</v>
       </c>
       <c r="AJ17" s="6">
-        <v>3937.88</v>
+        <v>1211.97</v>
       </c>
       <c r="AK17" s="6">
-        <v>3487.9</v>
+        <v>1124.8600000000001</v>
       </c>
       <c r="AL17" s="6">
-        <v>8768.7900000000009</v>
+        <v>13978.49</v>
       </c>
       <c r="AM17" s="6">
-        <v>1458.08</v>
+        <v>5304.7699999999995</v>
       </c>
       <c r="AN17" s="6">
-        <v>4870.8999999999996</v>
+        <v>6096.6900000000005</v>
       </c>
       <c r="AO17" s="6">
-        <v>3724.8599999999997</v>
+        <v>6535.98</v>
       </c>
       <c r="AP17" s="6">
-        <v>5604.7499999999982</v>
+        <v>2535.8000000000002</v>
       </c>
       <c r="AQ17" s="6">
-        <v>4257.9799999999996</v>
+        <v>1492.3</v>
       </c>
       <c r="AR17" s="6">
-        <v>3245.99</v>
+        <v>3528.5</v>
       </c>
       <c r="AS17" s="6">
-        <v>182.69000000000003</v>
+        <v>4451.99</v>
       </c>
       <c r="AT17" s="6">
-        <v>226</v>
+        <v>346.99</v>
       </c>
       <c r="AU17" s="6">
-        <v>782.99</v>
+        <v>243.97900000000004</v>
       </c>
       <c r="AV17" s="6">
-        <v>572.66999999999996</v>
+        <v>3687</v>
       </c>
       <c r="AW17" s="6">
-        <v>1708.99</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="AX17" s="6">
-        <v>1467</v>
+        <v>5453</v>
       </c>
       <c r="AY17" s="6">
-        <v>2169.98</v>
+        <v>2248</v>
       </c>
       <c r="AZ17" s="6">
-        <v>15909</v>
+        <v>2067.94</v>
       </c>
       <c r="BA17" s="6">
-        <v>1014.9</v>
+        <v>248</v>
       </c>
       <c r="BB17" s="6">
-        <v>1380.97</v>
+        <v>1897.8899999999999</v>
       </c>
       <c r="BC17" s="6">
-        <v>5544.8</v>
+        <v>2487.88</v>
       </c>
       <c r="BD17" s="6">
-        <v>29</v>
+        <v>134.97</v>
       </c>
       <c r="BE17" s="6">
-        <v>2065.88</v>
-      </c>
-      <c r="BF17" s="6">
-        <v>899</v>
-      </c>
+        <v>503.96000000000004</v>
+      </c>
+      <c r="BF17" s="6"/>
       <c r="BG17" s="6">
-        <v>21190.5</v>
+        <v>18986.669999999998</v>
       </c>
       <c r="BH17" s="6">
-        <v>2670.6</v>
+        <v>13621</v>
       </c>
       <c r="BI17" s="6">
-        <v>2441.9</v>
+        <v>653.99</v>
       </c>
       <c r="BJ17" s="6">
-        <v>11724.9</v>
+        <v>13008.8</v>
       </c>
       <c r="BK17" s="6">
-        <v>13426.699999999999</v>
+        <v>9492.9599999999991</v>
       </c>
       <c r="BL17" s="6">
-        <v>5726</v>
+        <v>2598.88</v>
       </c>
       <c r="BM17" s="6"/>
       <c r="BN17" s="6">
-        <v>22143</v>
+        <v>10407.98</v>
       </c>
       <c r="BO17" s="6">
-        <v>3718.9</v>
+        <v>3449.9</v>
       </c>
       <c r="BP17" s="6">
-        <v>2347.6999999999998</v>
+        <v>3328</v>
       </c>
       <c r="BQ17" s="6">
-        <v>14081.9</v>
+        <v>3585</v>
       </c>
       <c r="BR17" s="6">
-        <v>8923.8799999999992</v>
-      </c>
-      <c r="BS17" s="6"/>
+        <v>2749.4999999999995</v>
+      </c>
+      <c r="BS17" s="6">
+        <v>59.9</v>
+      </c>
       <c r="BT17" s="6">
-        <v>10199.589999999998</v>
+        <v>14002.599999999999</v>
       </c>
       <c r="BU17" s="6">
-        <v>10626.99</v>
+        <v>18544.79</v>
       </c>
       <c r="BV17" s="6">
-        <v>2303.9</v>
+        <v>11841.89</v>
       </c>
       <c r="BW17" s="6">
-        <v>452</v>
+        <v>45</v>
       </c>
       <c r="BX17" s="6">
-        <v>3532.58</v>
+        <v>3994.87</v>
       </c>
       <c r="BY17" s="6">
-        <v>10383</v>
+        <v>4112</v>
       </c>
       <c r="BZ17" s="6">
-        <v>16962</v>
+        <v>4665.7</v>
       </c>
       <c r="CA17" s="6">
-        <v>1901.76</v>
+        <v>5372.65</v>
       </c>
       <c r="CB17" s="6">
-        <v>7071.9</v>
+        <v>2077.8900000000003</v>
       </c>
       <c r="CC17" s="6">
-        <v>5379.79</v>
+        <v>304.37</v>
       </c>
       <c r="CD17" s="6">
-        <v>1340.99</v>
+        <v>347</v>
       </c>
       <c r="CE17" s="6">
-        <v>2352.58</v>
+        <v>211.59</v>
       </c>
       <c r="CF17" s="6"/>
       <c r="CG17" s="6">
-        <v>1714.78</v>
+        <v>1410.8899999999999</v>
       </c>
       <c r="CH17" s="6">
-        <v>10631.8</v>
+        <v>1701.98</v>
       </c>
       <c r="CI17" s="6">
-        <v>2838.79</v>
+        <v>331.97</v>
       </c>
       <c r="CJ17" s="6">
-        <v>20770.690000000006</v>
+        <v>4993.9399999999996</v>
       </c>
     </row>
     <row r="18" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="6"/>
+        <v>107</v>
+      </c>
+      <c r="B18" s="6">
+        <v>2698</v>
+      </c>
       <c r="C18" s="6">
-        <v>4982.8399999999983</v>
+        <v>1369.9</v>
       </c>
       <c r="D18" s="6">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="E18" s="6">
-        <v>228.99</v>
-      </c>
+        <v>1643.98</v>
+      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="6">
-        <v>8021.9599999999991</v>
+        <v>2166.59</v>
       </c>
       <c r="G18" s="6">
-        <v>4707.829999999999</v>
+        <v>14087.319999999996</v>
       </c>
       <c r="H18" s="6">
-        <v>5987.49</v>
+        <v>3763.49</v>
       </c>
       <c r="I18" s="6">
-        <v>3042.8699999999994</v>
+        <v>3901.8100000000004</v>
       </c>
       <c r="J18" s="6">
-        <v>1756.5600000000002</v>
+        <v>7348.869999999999</v>
       </c>
       <c r="K18" s="6">
-        <v>3113.99</v>
+        <v>429</v>
       </c>
       <c r="L18" s="6">
-        <v>471.99</v>
+        <v>258.99</v>
       </c>
       <c r="M18" s="6"/>
       <c r="N18" s="6">
-        <v>3455.48</v>
+        <v>314.89</v>
       </c>
       <c r="O18" s="6">
-        <v>979.9</v>
+        <v>152.76999999999998</v>
       </c>
       <c r="P18" s="6">
-        <v>1143.8800000000001</v>
+        <v>3583.8399999999992</v>
       </c>
       <c r="Q18" s="6">
-        <v>277.98</v>
+        <v>368.8</v>
       </c>
       <c r="R18" s="6">
-        <v>7537.78</v>
+        <v>14412.98</v>
       </c>
       <c r="S18" s="6">
-        <v>307.99</v>
+        <v>139.99</v>
       </c>
       <c r="T18" s="6">
-        <v>777</v>
+        <v>168.98000000000002</v>
       </c>
       <c r="U18" s="6">
-        <v>18656.900000000001</v>
+        <v>6733.9000000000015</v>
       </c>
       <c r="V18" s="6">
-        <v>84.47</v>
+        <v>902.79</v>
       </c>
       <c r="W18" s="6">
-        <v>6162.3499999999985</v>
+        <v>3138.9</v>
       </c>
       <c r="X18" s="6">
-        <v>295.88</v>
+        <v>2151.79</v>
       </c>
       <c r="Y18" s="6">
-        <v>2185.8900000000003</v>
+        <v>121.88999999999999</v>
       </c>
       <c r="Z18" s="6">
-        <v>4344.4799999999996</v>
+        <v>3187.9700000000003</v>
       </c>
       <c r="AA18" s="6">
-        <v>4067.7799999999997</v>
-      </c>
-      <c r="AB18" s="6"/>
+        <v>2195.98</v>
+      </c>
+      <c r="AB18" s="6">
+        <v>499</v>
+      </c>
       <c r="AC18" s="6">
-        <v>124.97999999999999</v>
+        <v>997.88</v>
       </c>
       <c r="AD18" s="6">
-        <v>219</v>
+        <v>65</v>
       </c>
       <c r="AE18" s="6">
-        <v>273.77</v>
+        <v>1001.6899999999999</v>
       </c>
       <c r="AF18" s="6">
-        <v>2816.98</v>
+        <v>3454.88</v>
       </c>
       <c r="AG18" s="6">
-        <v>2155.8900000000003</v>
-      </c>
-      <c r="AH18" s="6">
-        <v>129.99</v>
-      </c>
+        <v>464.88</v>
+      </c>
+      <c r="AH18" s="6"/>
       <c r="AI18" s="6">
-        <v>2123.6800000000003</v>
+        <v>2136.4300000000003</v>
       </c>
       <c r="AJ18" s="6">
-        <v>582</v>
+        <v>3097</v>
       </c>
       <c r="AK18" s="6">
-        <v>1073</v>
+        <v>2900.8399999999997</v>
       </c>
       <c r="AL18" s="6">
-        <v>12914.56</v>
+        <v>12313.759999999998</v>
       </c>
       <c r="AM18" s="6">
-        <v>2270.9599999999996</v>
+        <v>2132.9499999999998</v>
       </c>
       <c r="AN18" s="6">
-        <v>3012.6799999999994</v>
+        <v>193</v>
       </c>
       <c r="AO18" s="6">
-        <v>3184.99</v>
+        <v>3184.8599999999997</v>
       </c>
       <c r="AP18" s="6">
-        <v>5308.69</v>
+        <v>1769.67</v>
       </c>
       <c r="AQ18" s="6">
-        <v>649.07999999999993</v>
+        <v>1850.88</v>
       </c>
       <c r="AR18" s="6">
-        <v>2499</v>
+        <v>589.78</v>
       </c>
       <c r="AS18" s="6">
-        <v>3254.9</v>
+        <v>327.98</v>
       </c>
       <c r="AT18" s="6">
-        <v>384.98</v>
+        <v>178.99</v>
       </c>
       <c r="AU18" s="6">
-        <v>1026</v>
+        <v>2048</v>
       </c>
       <c r="AV18" s="6">
-        <v>2906.8</v>
+        <v>4355.79</v>
       </c>
       <c r="AW18" s="6">
-        <v>437.89</v>
+        <v>289.98</v>
       </c>
       <c r="AX18" s="6">
-        <v>2915</v>
+        <v>752.9</v>
       </c>
       <c r="AY18" s="6">
-        <v>5605.99</v>
+        <v>6126</v>
       </c>
       <c r="AZ18" s="6">
-        <v>6448.8899999999994</v>
+        <v>5163.8999999999996</v>
       </c>
       <c r="BA18" s="6">
-        <v>89.98</v>
+        <v>169</v>
       </c>
       <c r="BB18" s="6">
-        <v>79.989999999999995</v>
+        <v>554.98</v>
       </c>
       <c r="BC18" s="6">
-        <v>1756.97</v>
-      </c>
-      <c r="BD18" s="6">
-        <v>174.97</v>
-      </c>
+        <v>6199.9</v>
+      </c>
+      <c r="BD18" s="6"/>
       <c r="BE18" s="6">
-        <v>1295.8400000000001</v>
+        <v>1468.8799999999999</v>
       </c>
       <c r="BF18" s="6"/>
       <c r="BG18" s="6">
-        <v>20536.879999999997</v>
+        <v>12109.789999999999</v>
       </c>
       <c r="BH18" s="6">
-        <v>4366.99</v>
+        <v>6098.9</v>
       </c>
       <c r="BI18" s="6">
-        <v>7188.99</v>
+        <v>1199</v>
       </c>
       <c r="BJ18" s="6">
-        <v>10718.79</v>
+        <v>4751.99</v>
       </c>
       <c r="BK18" s="6">
-        <v>7148.8899999999994</v>
+        <v>6896</v>
       </c>
       <c r="BL18" s="6">
-        <v>22201.989999999998</v>
+        <v>1418.93</v>
       </c>
       <c r="BM18" s="6">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="BN18" s="6">
-        <v>3463.9999999999995</v>
+        <v>5562.99</v>
       </c>
       <c r="BO18" s="6">
-        <v>11875.99</v>
+        <v>8500.99</v>
       </c>
       <c r="BP18" s="6">
-        <v>740.89</v>
+        <v>6106.99</v>
       </c>
       <c r="BQ18" s="6">
-        <v>2373</v>
+        <v>6605.99</v>
       </c>
       <c r="BR18" s="6">
-        <v>5263.69</v>
-      </c>
-      <c r="BS18" s="6"/>
+        <v>2994.42</v>
+      </c>
+      <c r="BS18" s="6">
+        <v>139.88</v>
+      </c>
       <c r="BT18" s="6">
-        <v>820.98</v>
+        <v>2809.88</v>
       </c>
       <c r="BU18" s="6">
-        <v>9914.869999999999</v>
+        <v>23693.88</v>
       </c>
       <c r="BV18" s="6">
-        <v>10083.759999999998</v>
+        <v>3778.59</v>
       </c>
       <c r="BW18" s="6">
-        <v>317</v>
+        <v>669</v>
       </c>
       <c r="BX18" s="6">
-        <v>1605.4899999999998</v>
+        <v>2860.4900000000002</v>
       </c>
       <c r="BY18" s="6">
-        <v>7703.59</v>
+        <v>5348.99</v>
       </c>
       <c r="BZ18" s="6">
-        <v>20972.879999999997</v>
+        <v>9410.7999999999993</v>
       </c>
       <c r="CA18" s="6">
-        <v>5071.2599999999993</v>
+        <v>4099.54</v>
       </c>
       <c r="CB18" s="6">
-        <v>4703.8499999999995</v>
+        <v>6971.98</v>
       </c>
       <c r="CC18" s="6">
-        <v>2940.99</v>
+        <v>209.98000000000002</v>
       </c>
       <c r="CD18" s="6">
-        <v>4332</v>
+        <v>1464.8899999999999</v>
       </c>
       <c r="CE18" s="6">
-        <v>1526.89</v>
-      </c>
-      <c r="CF18" s="6">
-        <v>44.99</v>
-      </c>
+        <v>1048.8900000000001</v>
+      </c>
+      <c r="CF18" s="6"/>
       <c r="CG18" s="6">
-        <v>967.96</v>
+        <v>3803.6</v>
       </c>
       <c r="CH18" s="6">
-        <v>6283.8899999999994</v>
+        <v>138.78</v>
       </c>
       <c r="CI18" s="6">
-        <v>401.93</v>
+        <v>2989.27</v>
       </c>
       <c r="CJ18" s="6">
-        <v>29391.550000000003</v>
+        <v>33508.139999999992</v>
       </c>
     </row>
     <row r="19" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B19" s="6">
-        <v>632.79999999999995</v>
+        <v>1309.8</v>
       </c>
       <c r="C19" s="6">
-        <v>7463.8799999999992</v>
+        <v>3224.9</v>
       </c>
       <c r="D19" s="6">
-        <v>1647.89</v>
+        <v>69</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6">
-        <v>1955.48</v>
+        <v>1089</v>
       </c>
       <c r="G19" s="6">
-        <v>12652.89</v>
+        <v>17428.349999999999</v>
       </c>
       <c r="H19" s="6">
-        <v>3363.78</v>
+        <v>4447.75</v>
       </c>
       <c r="I19" s="6">
-        <v>2533.9199999999996</v>
+        <v>3337.99</v>
       </c>
       <c r="J19" s="6">
-        <v>2989.77</v>
+        <v>1275.8900000000001</v>
       </c>
       <c r="K19" s="6">
-        <v>1742.9</v>
+        <v>2577</v>
       </c>
       <c r="L19" s="6">
-        <v>95.89</v>
+        <v>248.99</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6">
-        <v>1454.8</v>
+        <v>894.77</v>
       </c>
       <c r="O19" s="6">
-        <v>1103.7</v>
+        <v>829.5</v>
       </c>
       <c r="P19" s="6">
-        <v>5346.4599999999982</v>
+        <v>3753.4700000000003</v>
       </c>
       <c r="Q19" s="6">
-        <v>237.99</v>
+        <v>153.99</v>
       </c>
       <c r="R19" s="6">
-        <v>9094.8799999999992</v>
+        <v>2860</v>
       </c>
       <c r="S19" s="6">
-        <v>710.9</v>
+        <v>187.99</v>
       </c>
       <c r="T19" s="6">
-        <v>109.9</v>
+        <v>49.9</v>
       </c>
       <c r="U19" s="6">
-        <v>3582.8</v>
+        <v>2553</v>
       </c>
       <c r="V19" s="6">
-        <v>4012.7100000000005</v>
+        <v>786.68999999999994</v>
       </c>
       <c r="W19" s="6">
-        <v>7745.09</v>
+        <v>6291.58</v>
       </c>
       <c r="X19" s="6">
-        <v>1027.8900000000001</v>
+        <v>1267.7</v>
       </c>
       <c r="Y19" s="6">
-        <v>1492.78</v>
+        <v>1974.8</v>
       </c>
       <c r="Z19" s="6">
-        <v>5938.99</v>
+        <v>4686.95</v>
       </c>
       <c r="AA19" s="6">
-        <v>3596</v>
+        <v>3566</v>
       </c>
       <c r="AB19" s="6">
-        <v>248.98000000000002</v>
-      </c>
-      <c r="AC19" s="6"/>
+        <v>224.99</v>
+      </c>
+      <c r="AC19" s="6">
+        <v>138</v>
+      </c>
       <c r="AD19" s="6">
-        <v>265.89999999999998</v>
+        <v>1586</v>
       </c>
       <c r="AE19" s="6">
-        <v>115</v>
+        <v>746.99</v>
       </c>
       <c r="AF19" s="6">
-        <v>2405.69</v>
+        <v>2554.7800000000002</v>
       </c>
       <c r="AG19" s="6">
-        <v>1187.8900000000001</v>
+        <v>3093.8</v>
       </c>
       <c r="AH19" s="6"/>
       <c r="AI19" s="6">
-        <v>4861.9799999999996</v>
+        <v>1024.3699999999999</v>
       </c>
       <c r="AJ19" s="6">
-        <v>2566.8900000000003</v>
+        <v>1606.5</v>
       </c>
       <c r="AK19" s="6">
-        <v>363.88</v>
+        <v>2130.89</v>
       </c>
       <c r="AL19" s="6">
-        <v>7552.6899999999987</v>
+        <v>4217.7699999999995</v>
       </c>
       <c r="AM19" s="6">
-        <v>3539.7900000000004</v>
+        <v>2259.8900000000003</v>
       </c>
       <c r="AN19" s="6">
-        <v>1237.77</v>
+        <v>574.9</v>
       </c>
       <c r="AO19" s="6">
-        <v>918.98</v>
+        <v>2794.97</v>
       </c>
       <c r="AP19" s="6">
-        <v>2130.98</v>
+        <v>1326.99</v>
       </c>
       <c r="AQ19" s="6">
-        <v>6366.8799999999992</v>
+        <v>7254.6429999999991</v>
       </c>
       <c r="AR19" s="6">
-        <v>324.89999999999998</v>
+        <v>1826.9</v>
       </c>
       <c r="AS19" s="6">
-        <v>3625.89</v>
+        <v>1128.8799999999999</v>
       </c>
       <c r="AT19" s="6">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="AU19" s="6">
-        <v>2411.9899999999998</v>
+        <v>1268</v>
       </c>
       <c r="AV19" s="6">
-        <v>207.9</v>
+        <v>4230.87</v>
       </c>
       <c r="AW19" s="6">
-        <v>2723</v>
+        <v>314</v>
       </c>
       <c r="AX19" s="6">
-        <v>1728</v>
+        <v>2046.7</v>
       </c>
       <c r="AY19" s="6">
-        <v>1568</v>
+        <v>268</v>
       </c>
       <c r="AZ19" s="6">
-        <v>9979.5</v>
+        <v>2693.49</v>
       </c>
       <c r="BA19" s="6">
-        <v>217.9</v>
+        <v>64</v>
       </c>
       <c r="BB19" s="6">
-        <v>343</v>
+        <v>1145.8899999999999</v>
       </c>
       <c r="BC19" s="6">
-        <v>1762.67</v>
+        <v>3210.17</v>
       </c>
       <c r="BD19" s="6">
-        <v>99.98</v>
+        <v>94</v>
       </c>
       <c r="BE19" s="6">
-        <v>2323.7600000000002</v>
+        <v>1766.89</v>
       </c>
       <c r="BF19" s="6"/>
       <c r="BG19" s="6">
-        <v>31554.79</v>
+        <v>27868.400000000001</v>
       </c>
       <c r="BH19" s="6">
-        <v>3568</v>
+        <v>3960.8999999999996</v>
       </c>
       <c r="BI19" s="6">
-        <v>8457.89</v>
+        <v>4056</v>
       </c>
       <c r="BJ19" s="6">
-        <v>8816</v>
+        <v>8017.5999999999995</v>
       </c>
       <c r="BK19" s="6">
-        <v>22550.590000000004</v>
+        <v>4160.6799999999994</v>
       </c>
       <c r="BL19" s="6">
-        <v>4016.49</v>
+        <v>6534.8</v>
       </c>
       <c r="BM19" s="6">
-        <v>99</v>
+        <v>129.99</v>
       </c>
       <c r="BN19" s="6">
-        <v>20884.900000000001</v>
+        <v>587</v>
       </c>
       <c r="BO19" s="6">
-        <v>2359.79</v>
+        <v>1928.7</v>
       </c>
       <c r="BP19" s="6">
-        <v>6561</v>
+        <v>5944.9</v>
       </c>
       <c r="BQ19" s="6">
-        <v>7318.9</v>
+        <v>9182.7999999999993</v>
       </c>
       <c r="BR19" s="6">
-        <v>858.9699999999998</v>
+        <v>3738.45</v>
       </c>
       <c r="BS19" s="6"/>
       <c r="BT19" s="6">
-        <v>3297.99</v>
+        <v>4452.8500000000004</v>
       </c>
       <c r="BU19" s="6">
-        <v>25747.989999999998</v>
+        <v>5159</v>
       </c>
       <c r="BV19" s="6">
-        <v>10859.89</v>
+        <v>3573.7</v>
       </c>
       <c r="BW19" s="6">
-        <v>1750</v>
+        <v>2144.9499999999998</v>
       </c>
       <c r="BX19" s="6">
-        <v>2062.48</v>
+        <v>1213.8800000000001</v>
       </c>
       <c r="BY19" s="6">
-        <v>20231.8</v>
+        <v>7248.9</v>
       </c>
       <c r="BZ19" s="6">
-        <v>10543.89</v>
+        <v>9129.8799999999992</v>
       </c>
       <c r="CA19" s="6">
-        <v>4027.2799999999997</v>
+        <v>3130.96</v>
       </c>
       <c r="CB19" s="6">
-        <v>8922</v>
+        <v>11716</v>
       </c>
       <c r="CC19" s="6">
-        <v>2336.9899999999998</v>
+        <v>1507.19</v>
       </c>
       <c r="CD19" s="6">
-        <v>2005.77</v>
+        <v>1635.7900000000002</v>
       </c>
       <c r="CE19" s="6">
-        <v>1771</v>
+        <v>188.99</v>
       </c>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6">
-        <v>1175.79</v>
+        <v>2393.96</v>
       </c>
       <c r="CH19" s="6">
-        <v>2344.9</v>
+        <v>3392.89</v>
       </c>
       <c r="CI19" s="6">
-        <v>696</v>
+        <v>552.87</v>
       </c>
       <c r="CJ19" s="6">
-        <v>22499.150000000005</v>
+        <v>9684.909999999998</v>
       </c>
     </row>
     <row r="20" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B20" s="6">
-        <v>0</v>
+        <v>1115.27</v>
       </c>
       <c r="C20" s="6">
-        <v>7263.8499999999995</v>
-      </c>
-      <c r="D20" s="6"/>
+        <v>9485.99</v>
+      </c>
+      <c r="D20" s="6">
+        <v>657.99</v>
+      </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6">
-        <v>2284</v>
+        <v>2224.3700000000003</v>
       </c>
       <c r="G20" s="6">
-        <v>8548.82</v>
+        <v>7930.5699999999979</v>
       </c>
       <c r="H20" s="6">
-        <v>739.85</v>
+        <v>4804.99</v>
       </c>
       <c r="I20" s="6">
-        <v>5000.66</v>
+        <v>10015.49</v>
       </c>
       <c r="J20" s="6">
-        <v>454.49</v>
+        <v>2566.7000000000007</v>
       </c>
       <c r="K20" s="6">
-        <v>4942.4799999999996</v>
-      </c>
-      <c r="L20" s="6">
-        <v>134.97999999999999</v>
-      </c>
+        <v>54.599999999999994</v>
+      </c>
+      <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6">
-        <v>1961.99</v>
+        <v>494.80999999999995</v>
       </c>
       <c r="O20" s="6">
-        <v>617.96</v>
+        <v>2925.2000000000003</v>
       </c>
       <c r="P20" s="6">
-        <v>4120.2800000000007</v>
+        <v>3458.86</v>
       </c>
       <c r="Q20" s="6">
-        <v>159</v>
+        <v>196.9</v>
       </c>
       <c r="R20" s="6">
-        <v>1595</v>
+        <v>9384</v>
       </c>
       <c r="S20" s="6">
-        <v>2457</v>
+        <v>402.89</v>
       </c>
       <c r="T20" s="6">
-        <v>-70</v>
+        <v>79</v>
       </c>
       <c r="U20" s="6">
-        <v>5551.7899999999991</v>
+        <v>2801.89</v>
       </c>
       <c r="V20" s="6">
-        <v>169.87</v>
+        <v>3005.87</v>
       </c>
       <c r="W20" s="6">
-        <v>4102.67</v>
+        <v>8151.329999999999</v>
       </c>
       <c r="X20" s="6">
-        <v>1420.8000000000002</v>
+        <v>2118.7799999999997</v>
       </c>
       <c r="Y20" s="6">
-        <v>5149.88</v>
+        <v>2177</v>
       </c>
       <c r="Z20" s="6">
-        <v>7789.99</v>
+        <v>2368.88</v>
       </c>
       <c r="AA20" s="6">
-        <v>2196</v>
+        <v>4406.99</v>
       </c>
       <c r="AB20" s="6">
-        <v>1966.99</v>
+        <v>248.98000000000002</v>
       </c>
       <c r="AC20" s="6">
-        <v>392.98</v>
+        <v>153.99</v>
       </c>
       <c r="AD20" s="6">
-        <v>1222</v>
+        <v>193.99</v>
       </c>
       <c r="AE20" s="6">
-        <v>268.77999999999997</v>
+        <v>452</v>
       </c>
       <c r="AF20" s="6">
-        <v>2679.99</v>
+        <v>5080.66</v>
       </c>
       <c r="AG20" s="6">
-        <v>1354.67</v>
+        <v>1646.6000000000001</v>
       </c>
       <c r="AH20" s="6"/>
       <c r="AI20" s="6">
-        <v>1678.4700000000005</v>
+        <v>4319.880000000001</v>
       </c>
       <c r="AJ20" s="6">
-        <v>186.88</v>
-      </c>
-      <c r="AK20" s="6"/>
+        <v>428.89</v>
+      </c>
+      <c r="AK20" s="6">
+        <v>11363.97</v>
+      </c>
       <c r="AL20" s="6">
-        <v>8565.8599999999988</v>
+        <v>8718.869999999999</v>
       </c>
       <c r="AM20" s="6">
-        <v>1626.89</v>
+        <v>2459.5000000000005</v>
       </c>
       <c r="AN20" s="6">
-        <v>1619.58</v>
+        <v>2145</v>
       </c>
       <c r="AO20" s="6">
-        <v>3067.89</v>
+        <v>4354.87</v>
       </c>
       <c r="AP20" s="6">
-        <v>1612.77</v>
+        <v>3889.86</v>
       </c>
       <c r="AQ20" s="6">
-        <v>902.66</v>
+        <v>4239.75</v>
       </c>
       <c r="AR20" s="6">
-        <v>1951.97</v>
+        <v>1275.99</v>
       </c>
       <c r="AS20" s="6">
-        <v>1030.98</v>
+        <v>2334.9899999999998</v>
       </c>
       <c r="AT20" s="6">
-        <v>547.98</v>
+        <v>114</v>
       </c>
       <c r="AU20" s="6">
-        <v>124.97</v>
+        <v>468</v>
       </c>
       <c r="AV20" s="6">
-        <v>4514</v>
+        <v>1482.68</v>
       </c>
       <c r="AW20" s="6">
-        <v>74.009999999999991</v>
+        <v>299.8</v>
       </c>
       <c r="AX20" s="6">
-        <v>1512.99</v>
+        <v>1236.99</v>
       </c>
       <c r="AY20" s="6">
-        <v>5125.9799999999996</v>
+        <v>3891.98</v>
       </c>
       <c r="AZ20" s="6">
-        <v>4251.9499999999989</v>
+        <v>18774.98</v>
       </c>
       <c r="BA20" s="6">
-        <v>168.99</v>
+        <v>302.99</v>
       </c>
       <c r="BB20" s="6">
-        <v>219.98000000000002</v>
+        <v>660.9</v>
       </c>
       <c r="BC20" s="6">
-        <v>3873.37</v>
-      </c>
-      <c r="BD20" s="6"/>
+        <v>5600.78</v>
+      </c>
+      <c r="BD20" s="6">
+        <v>1897.99</v>
+      </c>
       <c r="BE20" s="6">
-        <v>455.86</v>
+        <v>1383</v>
       </c>
       <c r="BF20" s="6"/>
       <c r="BG20" s="6">
-        <v>14342.539999999999</v>
+        <v>4399.1900000000005</v>
       </c>
       <c r="BH20" s="6">
-        <v>2241.9899999999998</v>
+        <v>1410.7</v>
       </c>
       <c r="BI20" s="6">
-        <v>7053</v>
+        <v>7450</v>
       </c>
       <c r="BJ20" s="6">
-        <v>5120.8999999999996</v>
+        <v>2186.9899999999998</v>
       </c>
       <c r="BK20" s="6">
-        <v>3982.9399999999996</v>
+        <v>6139.3</v>
       </c>
       <c r="BL20" s="6">
-        <v>2913.9799999999996</v>
+        <v>7862.1</v>
       </c>
       <c r="BM20" s="6">
-        <v>327.99</v>
+        <v>109.98</v>
       </c>
       <c r="BN20" s="6">
-        <v>10925.88</v>
+        <v>4437.7699999999995</v>
       </c>
       <c r="BO20" s="6">
-        <v>3541.98</v>
+        <v>889.8</v>
       </c>
       <c r="BP20" s="6">
-        <v>5474.8499999999995</v>
+        <v>2150.8000000000002</v>
       </c>
       <c r="BQ20" s="6">
-        <v>4845</v>
+        <v>6554</v>
       </c>
       <c r="BR20" s="6">
-        <v>3942.6800000000003</v>
-      </c>
-      <c r="BS20" s="6">
-        <v>49.99</v>
-      </c>
+        <v>4134.08</v>
+      </c>
+      <c r="BS20" s="6"/>
       <c r="BT20" s="6">
-        <v>682.89</v>
+        <v>945.99</v>
       </c>
       <c r="BU20" s="6">
-        <v>6157.9699999999993</v>
+        <v>8310.99</v>
       </c>
       <c r="BV20" s="6">
-        <v>2999.79</v>
+        <v>499.89</v>
       </c>
       <c r="BW20" s="6">
-        <v>2306.89</v>
+        <v>3228.75</v>
       </c>
       <c r="BX20" s="6">
-        <v>6037.6900000000005</v>
+        <v>3206.17</v>
       </c>
       <c r="BY20" s="6">
-        <v>9892.89</v>
+        <v>9850.7900000000009</v>
       </c>
       <c r="BZ20" s="6">
-        <v>8967.5</v>
+        <v>15403.699999999997</v>
       </c>
       <c r="CA20" s="6">
-        <v>6951.98</v>
+        <v>2409.38</v>
       </c>
       <c r="CB20" s="6">
-        <v>1124.8399999999997</v>
+        <v>4957.6899999999996</v>
       </c>
       <c r="CC20" s="6">
-        <v>6111.99</v>
+        <v>1020.99</v>
       </c>
       <c r="CD20" s="6">
-        <v>418.99</v>
+        <v>1230</v>
       </c>
       <c r="CE20" s="6">
-        <v>245.95000000000005</v>
+        <v>138.89000000000001</v>
       </c>
       <c r="CF20" s="6"/>
       <c r="CG20" s="6">
-        <v>3092.09</v>
+        <v>2443.58</v>
       </c>
       <c r="CH20" s="6">
-        <v>970.9</v>
+        <v>3871.76</v>
       </c>
       <c r="CI20" s="6">
-        <v>445.85</v>
+        <v>1264.99</v>
       </c>
       <c r="CJ20" s="6">
-        <v>16275.859999999999</v>
+        <v>13500.649999999998</v>
       </c>
     </row>
     <row r="21" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B21" s="6">
-        <v>1175.98</v>
+        <v>531.9</v>
       </c>
       <c r="C21" s="6">
-        <v>2900.69</v>
-      </c>
-      <c r="D21" s="6">
-        <v>468</v>
-      </c>
+        <v>978</v>
+      </c>
+      <c r="D21" s="6"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6">
-        <v>311.09300000000002</v>
+        <v>1400.3</v>
       </c>
       <c r="G21" s="6">
-        <v>14490.479999999998</v>
+        <v>6823.59</v>
       </c>
       <c r="H21" s="6">
-        <v>6241.1899999999987</v>
+        <v>4529.55</v>
       </c>
       <c r="I21" s="6">
-        <v>7335.79</v>
+        <v>592.67999999999995</v>
       </c>
       <c r="J21" s="6">
-        <v>4950.37</v>
-      </c>
-      <c r="K21" s="6">
-        <v>2398</v>
-      </c>
+        <v>1077.98</v>
+      </c>
+      <c r="K21" s="6"/>
       <c r="L21" s="6">
-        <v>89</v>
+        <v>280.38</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6">
-        <v>6238.8899999999994</v>
+        <v>592.9</v>
       </c>
       <c r="O21" s="6">
-        <v>772.88</v>
+        <v>1586.5900000000001</v>
       </c>
       <c r="P21" s="6">
-        <v>5049.8999999999996</v>
+        <v>7899.4800000000005</v>
       </c>
       <c r="Q21" s="6">
-        <v>159.97</v>
-      </c>
-      <c r="R21" s="6">
-        <v>9442.8799999999992</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="R21" s="6"/>
       <c r="S21" s="6">
-        <v>576.89</v>
+        <v>615</v>
       </c>
       <c r="T21" s="6">
-        <v>487.99</v>
-      </c>
-      <c r="U21" s="6">
-        <v>273.89999999999998</v>
-      </c>
+        <v>129.99</v>
+      </c>
+      <c r="U21" s="6"/>
       <c r="V21" s="6">
-        <v>906.9</v>
+        <v>631.78</v>
       </c>
       <c r="W21" s="6">
-        <v>3308.78</v>
+        <v>7346.59</v>
       </c>
       <c r="X21" s="6">
-        <v>236.99</v>
+        <v>1038.8799999999999</v>
       </c>
       <c r="Y21" s="6">
-        <v>3634.6000000000004</v>
+        <v>205.8</v>
       </c>
       <c r="Z21" s="6">
-        <v>3916.99</v>
+        <v>3895.9</v>
       </c>
       <c r="AA21" s="6">
-        <v>9394.99</v>
+        <v>215.9</v>
       </c>
       <c r="AB21" s="6">
-        <v>313.98</v>
+        <v>652.99</v>
       </c>
       <c r="AC21" s="6">
-        <v>129.99</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="AD21" s="6">
-        <v>687.99</v>
+        <v>1590.9</v>
       </c>
       <c r="AE21" s="6">
-        <v>254</v>
+        <v>114.97999999999999</v>
       </c>
       <c r="AF21" s="6">
-        <v>5118.59</v>
+        <v>1974.99</v>
       </c>
       <c r="AG21" s="6">
-        <v>1617.7</v>
+        <v>1483.7</v>
       </c>
       <c r="AH21" s="6"/>
       <c r="AI21" s="6">
-        <v>7109.4400000000005</v>
-      </c>
-      <c r="AJ21" s="6"/>
+        <v>2775.5800000000004</v>
+      </c>
+      <c r="AJ21" s="6">
+        <v>2531.8900000000003</v>
+      </c>
       <c r="AK21" s="6">
-        <v>4797.87</v>
+        <v>666</v>
       </c>
       <c r="AL21" s="6">
-        <v>14917.869999999999</v>
+        <v>3758.82</v>
       </c>
       <c r="AM21" s="6">
-        <v>678.49</v>
+        <v>2236.1799999999998</v>
       </c>
       <c r="AN21" s="6">
-        <v>2550</v>
+        <v>1052.8799999999999</v>
       </c>
       <c r="AO21" s="6">
-        <v>4585.8900000000003</v>
+        <v>7835.9599999999991</v>
       </c>
       <c r="AP21" s="6">
-        <v>1740.8899999999999</v>
+        <v>1067.99</v>
       </c>
       <c r="AQ21" s="6">
-        <v>4619.8500000000004</v>
+        <v>5419.8499999999985</v>
       </c>
       <c r="AR21" s="6">
-        <v>2305.79</v>
+        <v>703.98</v>
       </c>
       <c r="AS21" s="6">
-        <v>1473.88</v>
-      </c>
-      <c r="AT21" s="6">
-        <v>35</v>
-      </c>
+        <v>1071.77</v>
+      </c>
+      <c r="AT21" s="6"/>
       <c r="AU21" s="6">
-        <v>3345.9</v>
+        <v>1763.89</v>
       </c>
       <c r="AV21" s="6">
-        <v>1746.99</v>
+        <v>1481.3899999999999</v>
       </c>
       <c r="AW21" s="6">
-        <v>218.9</v>
+        <v>90</v>
       </c>
       <c r="AX21" s="6">
-        <v>798</v>
+        <v>139.4</v>
       </c>
       <c r="AY21" s="6">
-        <v>6704.9</v>
-      </c>
-      <c r="AZ21" s="6">
-        <v>9896.7000000000007</v>
-      </c>
+        <v>497</v>
+      </c>
+      <c r="AZ21" s="6"/>
       <c r="BA21" s="6">
-        <v>1736.89</v>
+        <v>39.99</v>
       </c>
       <c r="BB21" s="6">
-        <v>405.99</v>
+        <v>406.89</v>
       </c>
       <c r="BC21" s="6">
-        <v>10118.69</v>
+        <v>5380.57</v>
       </c>
       <c r="BD21" s="6">
-        <v>59.99</v>
+        <v>59</v>
       </c>
       <c r="BE21" s="6">
-        <v>2441.87</v>
+        <v>1315.97</v>
       </c>
       <c r="BF21" s="6"/>
-      <c r="BG21" s="6">
-        <v>3618.1000000000004</v>
-      </c>
-      <c r="BH21" s="6">
-        <v>5870.6999999999989</v>
-      </c>
-      <c r="BI21" s="6">
-        <v>722</v>
-      </c>
-      <c r="BJ21" s="6">
-        <v>14453.9</v>
-      </c>
-      <c r="BK21" s="6">
-        <v>17028.900000000001</v>
-      </c>
-      <c r="BL21" s="6">
-        <v>9839.7999999999993</v>
-      </c>
+      <c r="BG21" s="6"/>
+      <c r="BH21" s="6"/>
+      <c r="BI21" s="6"/>
+      <c r="BJ21" s="6"/>
+      <c r="BK21" s="6"/>
+      <c r="BL21" s="6"/>
       <c r="BM21" s="6">
-        <v>39</v>
-      </c>
-      <c r="BN21" s="6">
-        <v>8377.7900000000009</v>
-      </c>
-      <c r="BO21" s="6">
-        <v>4249.8900000000003</v>
-      </c>
-      <c r="BP21" s="6">
-        <v>9705.9</v>
-      </c>
-      <c r="BQ21" s="6">
-        <v>11077.5</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="BN21" s="6"/>
+      <c r="BO21" s="6"/>
+      <c r="BP21" s="6"/>
+      <c r="BQ21" s="6"/>
       <c r="BR21" s="6">
-        <v>4940.4799999999996</v>
+        <v>3220.68</v>
       </c>
       <c r="BS21" s="6"/>
       <c r="BT21" s="6">
-        <v>6144.8899999999994</v>
-      </c>
-      <c r="BU21" s="6">
-        <v>6295.7000000000007</v>
-      </c>
-      <c r="BV21" s="6">
-        <v>1013</v>
-      </c>
+        <v>421.99</v>
+      </c>
+      <c r="BU21" s="6"/>
+      <c r="BV21" s="6"/>
       <c r="BW21" s="6">
-        <v>298.78000000000003</v>
+        <v>353</v>
       </c>
       <c r="BX21" s="6">
-        <v>2549.3799999999997</v>
-      </c>
-      <c r="BY21" s="6">
-        <v>12277.789999999999</v>
-      </c>
-      <c r="BZ21" s="6">
-        <v>23049</v>
-      </c>
+        <v>4315.79</v>
+      </c>
+      <c r="BY21" s="6"/>
+      <c r="BZ21" s="6"/>
       <c r="CA21" s="6">
-        <v>6556.5599999999995</v>
-      </c>
-      <c r="CB21" s="6">
-        <v>9715.9</v>
-      </c>
+        <v>1929.68</v>
+      </c>
+      <c r="CB21" s="6"/>
       <c r="CC21" s="6">
-        <v>1977.99</v>
+        <v>3971.98</v>
       </c>
       <c r="CD21" s="6">
-        <v>1577.97</v>
+        <v>1428.98</v>
       </c>
       <c r="CE21" s="6">
-        <v>1991.78</v>
+        <v>374.87</v>
       </c>
       <c r="CF21" s="6"/>
       <c r="CG21" s="6">
-        <v>1465.64</v>
+        <v>886.8</v>
       </c>
       <c r="CH21" s="6">
-        <v>3937.3</v>
+        <v>6247.5999999999995</v>
       </c>
       <c r="CI21" s="6">
-        <v>892.87</v>
-      </c>
-      <c r="CJ21" s="6">
-        <v>16749.019999999993</v>
-      </c>
+        <v>1945.89</v>
+      </c>
+      <c r="CJ21" s="6"/>
     </row>
     <row r="22" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B22" s="6">
-        <v>2069</v>
+        <v>3097.69</v>
       </c>
       <c r="C22" s="6">
-        <v>4173.9519999999993</v>
+        <v>6402.99</v>
       </c>
       <c r="D22" s="6">
-        <v>42.9</v>
+        <v>328.88</v>
       </c>
       <c r="E22" s="6">
-        <v>69.989999999999995</v>
+        <v>79</v>
       </c>
       <c r="F22" s="6">
-        <v>2257.17</v>
+        <v>4730.9699999999993</v>
       </c>
       <c r="G22" s="6">
-        <v>16516.96</v>
+        <v>12481.88</v>
       </c>
       <c r="H22" s="6">
-        <v>4018.69</v>
+        <v>13231.689999999999</v>
       </c>
       <c r="I22" s="6">
-        <v>7124.74</v>
-      </c>
-      <c r="J22" s="6"/>
+        <v>727.88</v>
+      </c>
+      <c r="J22" s="6">
+        <v>7113.8899999999994</v>
+      </c>
       <c r="K22" s="6">
-        <v>59</v>
-      </c>
-      <c r="L22" s="6">
-        <v>489.89</v>
-      </c>
-      <c r="M22" s="6">
-        <v>0</v>
-      </c>
+        <v>2618</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
       <c r="N22" s="6">
-        <v>1108.97</v>
+        <v>4336.8799999999992</v>
       </c>
       <c r="O22" s="6">
-        <v>1274.8699999999999</v>
+        <v>587.79999999999995</v>
       </c>
       <c r="P22" s="6">
-        <v>1186.94</v>
-      </c>
-      <c r="Q22" s="6"/>
+        <v>1667.17</v>
+      </c>
+      <c r="Q22" s="6">
+        <v>607</v>
+      </c>
       <c r="R22" s="6">
-        <v>10094.89</v>
+        <v>12676.89</v>
       </c>
       <c r="S22" s="6">
-        <v>175.98000000000002</v>
+        <v>345.7</v>
       </c>
       <c r="T22" s="6">
-        <v>1338.89</v>
+        <v>12.99</v>
       </c>
       <c r="U22" s="6">
-        <v>4894.9799999999996</v>
+        <v>3142.9</v>
       </c>
       <c r="V22" s="6">
-        <v>416.79999999999995</v>
+        <v>720.79</v>
       </c>
       <c r="W22" s="6">
-        <v>6578.8399999999992</v>
+        <v>4956.99</v>
       </c>
       <c r="X22" s="6">
-        <v>1611.88</v>
+        <v>2271.29</v>
       </c>
       <c r="Y22" s="6">
-        <v>749</v>
+        <v>3794.79</v>
       </c>
       <c r="Z22" s="6">
-        <v>8030.98</v>
+        <v>6046.7899999999991</v>
       </c>
       <c r="AA22" s="6">
-        <v>7743.9</v>
+        <v>2133.9899999999998</v>
       </c>
       <c r="AB22" s="6">
-        <v>-579</v>
-      </c>
-      <c r="AC22" s="6">
-        <v>285</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="AC22" s="6"/>
       <c r="AD22" s="6">
-        <v>2105</v>
+        <v>2803.89</v>
       </c>
       <c r="AE22" s="6">
-        <v>212.79000000000002</v>
+        <v>133.60000000000002</v>
       </c>
       <c r="AF22" s="6">
-        <v>4608.8</v>
+        <v>1161.99</v>
       </c>
       <c r="AG22" s="6">
-        <v>4041.2000000000003</v>
+        <v>2003.6</v>
       </c>
       <c r="AH22" s="6"/>
       <c r="AI22" s="6">
-        <v>5024.57</v>
+        <v>7702.2599999999993</v>
       </c>
       <c r="AJ22" s="6">
-        <v>368.98</v>
+        <v>227</v>
       </c>
       <c r="AK22" s="6">
-        <v>2516.9899999999998</v>
+        <v>2320.89</v>
       </c>
       <c r="AL22" s="6">
-        <v>12186.63</v>
+        <v>11647.789999999999</v>
       </c>
       <c r="AM22" s="6">
-        <v>3288.5699999999997</v>
+        <v>2774.69</v>
       </c>
       <c r="AN22" s="6">
-        <v>3228.38</v>
+        <v>1978.97</v>
       </c>
       <c r="AO22" s="6">
-        <v>1483.88</v>
+        <v>2029.9899999999998</v>
       </c>
       <c r="AP22" s="6">
-        <v>1841.97</v>
+        <v>2412.79</v>
       </c>
       <c r="AQ22" s="6">
-        <v>1135.5700000000002</v>
+        <v>2896.7799999999997</v>
       </c>
       <c r="AR22" s="6">
-        <v>1050.99</v>
+        <v>3396.99</v>
       </c>
       <c r="AS22" s="6">
-        <v>4484</v>
+        <v>1327</v>
       </c>
       <c r="AT22" s="6">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="AU22" s="6">
-        <v>139</v>
+        <v>843</v>
       </c>
       <c r="AV22" s="6">
-        <v>432.79</v>
+        <v>1866.98</v>
       </c>
       <c r="AW22" s="6">
-        <v>1069.99</v>
+        <v>286.99</v>
       </c>
       <c r="AX22" s="6">
-        <v>763.97</v>
+        <v>5172.7</v>
       </c>
       <c r="AY22" s="6">
-        <v>4116</v>
+        <v>3729.9</v>
       </c>
       <c r="AZ22" s="6">
-        <v>3289.87</v>
-      </c>
-      <c r="BA22" s="6"/>
+        <v>12036.669999999998</v>
+      </c>
+      <c r="BA22" s="6">
+        <v>291.89</v>
+      </c>
       <c r="BB22" s="6">
-        <v>585.84</v>
+        <v>575.88</v>
       </c>
       <c r="BC22" s="6">
-        <v>754.75</v>
-      </c>
-      <c r="BD22" s="6"/>
+        <v>6805.4499999999989</v>
+      </c>
+      <c r="BD22" s="6">
+        <v>49</v>
+      </c>
       <c r="BE22" s="6">
-        <v>103.99000000000001</v>
+        <v>1591.8600000000001</v>
       </c>
       <c r="BF22" s="6"/>
       <c r="BG22" s="6">
-        <v>21183.68</v>
+        <v>3957.69</v>
       </c>
       <c r="BH22" s="6">
-        <v>7942.98</v>
+        <v>899.6</v>
       </c>
       <c r="BI22" s="6">
-        <v>5418.98</v>
+        <v>5346.9</v>
       </c>
       <c r="BJ22" s="6">
-        <v>14741.89</v>
+        <v>950</v>
       </c>
       <c r="BK22" s="6">
-        <v>11933.789999999999</v>
+        <v>13510.689999999999</v>
       </c>
       <c r="BL22" s="6">
-        <v>4887.7800000000007</v>
-      </c>
-      <c r="BM22" s="6"/>
+        <v>5819</v>
+      </c>
+      <c r="BM22" s="6">
+        <v>386.9</v>
+      </c>
       <c r="BN22" s="6">
-        <v>5996.9</v>
+        <v>7119</v>
       </c>
       <c r="BO22" s="6">
-        <v>1679.97</v>
+        <v>5503.8</v>
       </c>
       <c r="BP22" s="6">
-        <v>5701.98</v>
+        <v>285</v>
       </c>
       <c r="BQ22" s="6">
-        <v>10396.450000000001</v>
+        <v>3441.8899999999994</v>
       </c>
       <c r="BR22" s="6">
-        <v>3709.59</v>
-      </c>
-      <c r="BS22" s="6">
-        <v>49.9</v>
-      </c>
+        <v>2125.4700000000003</v>
+      </c>
+      <c r="BS22" s="6"/>
       <c r="BT22" s="6">
-        <v>3628</v>
+        <v>347.89</v>
       </c>
       <c r="BU22" s="6">
-        <v>12430.98</v>
+        <v>5865.9</v>
       </c>
       <c r="BV22" s="6">
-        <v>5850.9399999999987</v>
+        <v>233.60000000000002</v>
       </c>
       <c r="BW22" s="6">
-        <v>174.99</v>
+        <v>845.89</v>
       </c>
       <c r="BX22" s="6">
-        <v>1293.79</v>
+        <v>2152.38</v>
       </c>
       <c r="BY22" s="6">
-        <v>6147</v>
+        <v>13716.9</v>
       </c>
       <c r="BZ22" s="6">
-        <v>11911.789999999999</v>
+        <v>17080.979999999996</v>
       </c>
       <c r="CA22" s="6">
-        <v>4013.6699999999992</v>
+        <v>1092.0899999999997</v>
       </c>
       <c r="CB22" s="6">
-        <v>1267.93</v>
+        <v>1536.9</v>
       </c>
       <c r="CC22" s="6">
-        <v>1299</v>
+        <v>2139.9899999999998</v>
       </c>
       <c r="CD22" s="6">
-        <v>536.99</v>
+        <v>797.99</v>
       </c>
       <c r="CE22" s="6">
-        <v>1816.99</v>
+        <v>693.68999999999994</v>
       </c>
       <c r="CF22" s="6"/>
       <c r="CG22" s="6">
-        <v>4585.6499999999996</v>
+        <v>2034.56</v>
       </c>
       <c r="CH22" s="6">
-        <v>142.97999999999999</v>
+        <v>921.8</v>
       </c>
       <c r="CI22" s="6">
-        <v>1761.99</v>
+        <v>597</v>
       </c>
       <c r="CJ22" s="6">
-        <v>25133.469999999998</v>
+        <v>20853.099999999999</v>
       </c>
     </row>
     <row r="23" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B23" s="6">
-        <v>395</v>
+        <v>2330.0899999999997</v>
       </c>
       <c r="C23" s="6">
-        <v>1039.7</v>
-      </c>
-      <c r="D23" s="6">
-        <v>164.89000000000001</v>
-      </c>
+        <v>4312</v>
+      </c>
+      <c r="D23" s="6"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6">
-        <v>2863.8</v>
+        <v>2742.4799999999996</v>
       </c>
       <c r="G23" s="6">
-        <v>9282.8799999999992</v>
+        <v>6179.5899999999983</v>
       </c>
       <c r="H23" s="6">
-        <v>3614.59</v>
+        <v>10021.689999999999</v>
       </c>
       <c r="I23" s="6">
-        <v>6491.87</v>
+        <v>2317.75</v>
       </c>
       <c r="J23" s="6">
-        <v>5900.5999999999995</v>
-      </c>
-      <c r="K23" s="6"/>
+        <v>3437.88</v>
+      </c>
+      <c r="K23" s="6">
+        <v>1897</v>
+      </c>
       <c r="L23" s="6">
-        <v>401.78000000000003</v>
+        <v>192.9</v>
       </c>
       <c r="M23" s="6"/>
       <c r="N23" s="6">
-        <v>7407.19</v>
+        <v>224.99</v>
       </c>
       <c r="O23" s="6">
-        <v>538.9</v>
+        <v>774.99</v>
       </c>
       <c r="P23" s="6">
-        <v>1386.49</v>
+        <v>3481.3800000000006</v>
       </c>
       <c r="Q23" s="6">
-        <v>193.99</v>
+        <v>49</v>
       </c>
       <c r="R23" s="6">
-        <v>11592</v>
+        <v>12404.8</v>
       </c>
       <c r="S23" s="6">
-        <v>101.7</v>
+        <v>1016.78</v>
       </c>
       <c r="T23" s="6">
         <v>129.99</v>
       </c>
       <c r="U23" s="6">
-        <v>1160.8</v>
+        <v>103</v>
       </c>
       <c r="V23" s="6">
-        <v>1943.9</v>
+        <v>3070.9700000000003</v>
       </c>
       <c r="W23" s="6">
-        <v>9699.4599999999991</v>
+        <v>4475.7</v>
       </c>
       <c r="X23" s="6">
-        <v>3389.89</v>
+        <v>282.79000000000002</v>
       </c>
       <c r="Y23" s="6">
-        <v>4804.8999999999996</v>
+        <v>1870.6000000000001</v>
       </c>
       <c r="Z23" s="6">
-        <v>2432.8799999999997</v>
+        <v>7732.5</v>
       </c>
       <c r="AA23" s="6">
-        <v>1568</v>
+        <v>1595.98</v>
       </c>
       <c r="AB23" s="6">
-        <v>468.97</v>
-      </c>
-      <c r="AC23" s="6">
-        <v>158</v>
-      </c>
+        <v>1903.9</v>
+      </c>
+      <c r="AC23" s="6"/>
       <c r="AD23" s="6">
-        <v>1737.99</v>
+        <v>96.990000000000009</v>
       </c>
       <c r="AE23" s="6">
-        <v>164</v>
+        <v>367.99</v>
       </c>
       <c r="AF23" s="6">
-        <v>4065.69</v>
+        <v>9009.59</v>
       </c>
       <c r="AG23" s="6">
-        <v>2435.29</v>
+        <v>1474.5</v>
       </c>
       <c r="AH23" s="6"/>
       <c r="AI23" s="6">
-        <v>1656.3700000000001</v>
+        <v>6201.1799999999994</v>
       </c>
       <c r="AJ23" s="6">
-        <v>2484.9</v>
+        <v>3937.88</v>
       </c>
       <c r="AK23" s="6">
-        <v>2404.9</v>
+        <v>3487.9</v>
       </c>
       <c r="AL23" s="6">
-        <v>15583.9</v>
+        <v>8768.7900000000009</v>
       </c>
       <c r="AM23" s="6">
-        <v>1794.77</v>
+        <v>1458.08</v>
       </c>
       <c r="AN23" s="6">
-        <v>689.98</v>
+        <v>4870.8999999999996</v>
       </c>
       <c r="AO23" s="6">
-        <v>3590.9799999999996</v>
+        <v>3724.8599999999997</v>
       </c>
       <c r="AP23" s="6">
-        <v>5307.99</v>
+        <v>5604.7499999999982</v>
       </c>
       <c r="AQ23" s="6">
-        <v>4700.99</v>
+        <v>4257.9799999999996</v>
       </c>
       <c r="AR23" s="6">
-        <v>2674.0899999999997</v>
+        <v>3245.99</v>
       </c>
       <c r="AS23" s="6">
-        <v>599.9</v>
-      </c>
-      <c r="AT23" s="6"/>
+        <v>182.69000000000003</v>
+      </c>
+      <c r="AT23" s="6">
+        <v>226</v>
+      </c>
       <c r="AU23" s="6">
-        <v>2302</v>
+        <v>782.99</v>
       </c>
       <c r="AV23" s="6">
-        <v>2204.8799999999997</v>
+        <v>572.66999999999996</v>
       </c>
       <c r="AW23" s="6">
-        <v>6180.8799999999992</v>
+        <v>1708.99</v>
       </c>
       <c r="AX23" s="6">
-        <v>1649</v>
+        <v>1467</v>
       </c>
       <c r="AY23" s="6">
-        <v>3173.89</v>
+        <v>2169.98</v>
       </c>
       <c r="AZ23" s="6">
-        <v>11146.789999999999</v>
+        <v>15909</v>
       </c>
       <c r="BA23" s="6">
-        <v>317.89999999999998</v>
+        <v>1014.9</v>
       </c>
       <c r="BB23" s="6">
-        <v>1267.7900000000002</v>
+        <v>1380.97</v>
       </c>
       <c r="BC23" s="6">
-        <v>3654.2000000000003</v>
-      </c>
-      <c r="BD23" s="6"/>
+        <v>5544.8</v>
+      </c>
+      <c r="BD23" s="6">
+        <v>29</v>
+      </c>
       <c r="BE23" s="6">
-        <v>339</v>
-      </c>
-      <c r="BF23" s="6"/>
+        <v>2065.88</v>
+      </c>
+      <c r="BF23" s="6">
+        <v>899</v>
+      </c>
       <c r="BG23" s="6">
-        <v>17119.8</v>
+        <v>21190.5</v>
       </c>
       <c r="BH23" s="6">
-        <v>2491.3000000000002</v>
+        <v>2670.6</v>
       </c>
       <c r="BI23" s="6">
-        <v>926</v>
+        <v>2441.9</v>
       </c>
       <c r="BJ23" s="6">
-        <v>14106.199999999999</v>
+        <v>11724.9</v>
       </c>
       <c r="BK23" s="6">
-        <v>20776.399999999998</v>
+        <v>13426.699999999999</v>
       </c>
       <c r="BL23" s="6">
-        <v>12281.789999999999</v>
-      </c>
-      <c r="BM23" s="6">
-        <v>39</v>
-      </c>
+        <v>5726</v>
+      </c>
+      <c r="BM23" s="6"/>
       <c r="BN23" s="6">
-        <v>22823.7</v>
+        <v>22143</v>
       </c>
       <c r="BO23" s="6">
-        <v>6933.8</v>
+        <v>3718.9</v>
       </c>
       <c r="BP23" s="6">
-        <v>4401</v>
+        <v>2347.6999999999998</v>
       </c>
       <c r="BQ23" s="6">
-        <v>10416.9</v>
+        <v>14081.9</v>
       </c>
       <c r="BR23" s="6">
-        <v>2948.76</v>
+        <v>8923.8799999999992</v>
       </c>
       <c r="BS23" s="6"/>
       <c r="BT23" s="6">
-        <v>8068.8899999999994</v>
+        <v>10199.589999999998</v>
       </c>
       <c r="BU23" s="6">
-        <v>12172.9</v>
+        <v>10626.99</v>
       </c>
       <c r="BV23" s="6">
-        <v>10427</v>
+        <v>2303.9</v>
       </c>
       <c r="BW23" s="6">
-        <v>1854.78</v>
+        <v>452</v>
       </c>
       <c r="BX23" s="6">
-        <v>2731.56</v>
+        <v>3532.58</v>
       </c>
       <c r="BY23" s="6">
-        <v>5449.9</v>
+        <v>10383</v>
       </c>
       <c r="BZ23" s="6">
-        <v>36720.959999999999</v>
+        <v>16962</v>
       </c>
       <c r="CA23" s="6">
-        <v>4122.78</v>
+        <v>1901.76</v>
       </c>
       <c r="CB23" s="6">
-        <v>4872.8999999999996</v>
+        <v>7071.9</v>
       </c>
       <c r="CC23" s="6">
-        <v>4365.99</v>
+        <v>5379.79</v>
       </c>
       <c r="CD23" s="6">
-        <v>3063.87</v>
+        <v>1340.99</v>
       </c>
       <c r="CE23" s="6">
-        <v>3547.99</v>
+        <v>2352.58</v>
       </c>
       <c r="CF23" s="6"/>
       <c r="CG23" s="6">
-        <v>590.99</v>
+        <v>1714.78</v>
       </c>
       <c r="CH23" s="6">
-        <v>2030.29</v>
+        <v>10631.8</v>
       </c>
       <c r="CI23" s="6">
-        <v>276.8</v>
+        <v>2838.79</v>
       </c>
       <c r="CJ23" s="6">
-        <v>17555.359999999993</v>
+        <v>19462.690000000002</v>
       </c>
     </row>
     <row r="24" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B24" s="6">
-        <v>1199</v>
+        <v>632.79999999999995</v>
       </c>
       <c r="C24" s="6">
-        <v>1080</v>
+        <v>7463.88</v>
       </c>
       <c r="D24" s="6">
-        <v>42.9</v>
+        <v>1647.89</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6">
-        <v>8602.58</v>
+        <v>1955.48</v>
       </c>
       <c r="G24" s="6">
-        <v>6297.44</v>
+        <v>12652.89</v>
       </c>
       <c r="H24" s="6">
-        <v>4435.6899999999996</v>
+        <v>3363.78</v>
       </c>
       <c r="I24" s="6">
-        <v>3958.67</v>
+        <v>2533.9199999999996</v>
       </c>
       <c r="J24" s="6">
-        <v>1298.95</v>
+        <v>2989.77</v>
       </c>
       <c r="K24" s="6">
-        <v>5427</v>
+        <v>1742.9</v>
       </c>
       <c r="L24" s="6">
-        <v>129.99</v>
+        <v>95.89</v>
       </c>
       <c r="M24" s="6"/>
       <c r="N24" s="6">
-        <v>1226.79</v>
+        <v>1454.8</v>
       </c>
       <c r="O24" s="6">
-        <v>1062.98</v>
+        <v>1103.7</v>
       </c>
       <c r="P24" s="6">
-        <v>4100.6899999999996</v>
-      </c>
-      <c r="Q24" s="6"/>
+        <v>5346.4599999999982</v>
+      </c>
+      <c r="Q24" s="6">
+        <v>237.99</v>
+      </c>
       <c r="R24" s="6">
-        <v>11037.99</v>
+        <v>9094.8799999999992</v>
       </c>
       <c r="S24" s="6">
-        <v>150.99</v>
+        <v>710.9</v>
       </c>
       <c r="T24" s="6">
-        <v>44.99</v>
+        <v>109.9</v>
       </c>
       <c r="U24" s="6">
-        <v>6425.9900000000016</v>
+        <v>3582.8</v>
       </c>
       <c r="V24" s="6">
-        <v>1092.8</v>
+        <v>4012.7100000000005</v>
       </c>
       <c r="W24" s="6">
-        <v>2784.89</v>
+        <v>7745.09</v>
       </c>
       <c r="X24" s="6">
-        <v>462.07</v>
+        <v>1027.8900000000001</v>
       </c>
       <c r="Y24" s="6">
-        <v>1355.9</v>
+        <v>1492.78</v>
       </c>
       <c r="Z24" s="6">
-        <v>3367.7799999999997</v>
+        <v>5938.99</v>
       </c>
       <c r="AA24" s="6">
-        <v>815.99</v>
+        <v>3596</v>
       </c>
       <c r="AB24" s="6">
-        <v>597.99</v>
-      </c>
-      <c r="AC24" s="6">
-        <v>45</v>
-      </c>
+        <v>248.98000000000002</v>
+      </c>
+      <c r="AC24" s="6"/>
       <c r="AD24" s="6">
-        <v>3474.89</v>
+        <v>265.89999999999998</v>
       </c>
       <c r="AE24" s="6">
-        <v>653.89</v>
+        <v>115</v>
       </c>
       <c r="AF24" s="6">
-        <v>743.39</v>
+        <v>2405.69</v>
       </c>
       <c r="AG24" s="6">
-        <v>3281.7799999999997</v>
+        <v>1187.8900000000001</v>
       </c>
       <c r="AH24" s="6"/>
       <c r="AI24" s="6">
-        <v>5518.6399999999994</v>
+        <v>4861.9799999999996</v>
       </c>
       <c r="AJ24" s="6">
-        <v>1211.97</v>
+        <v>2566.8900000000003</v>
       </c>
       <c r="AK24" s="6">
-        <v>1124.8600000000001</v>
+        <v>363.88</v>
       </c>
       <c r="AL24" s="6">
-        <v>13978.49</v>
+        <v>7552.6899999999987</v>
       </c>
       <c r="AM24" s="6">
-        <v>5304.7699999999995</v>
+        <v>3539.7900000000004</v>
       </c>
       <c r="AN24" s="6">
-        <v>6096.6900000000005</v>
+        <v>1237.77</v>
       </c>
       <c r="AO24" s="6">
-        <v>6535.98</v>
+        <v>918.98</v>
       </c>
       <c r="AP24" s="6">
-        <v>2535.8000000000002</v>
+        <v>2130.98</v>
       </c>
       <c r="AQ24" s="6">
-        <v>1492.3</v>
+        <v>6366.8799999999992</v>
       </c>
       <c r="AR24" s="6">
-        <v>3528.5</v>
+        <v>324.89999999999998</v>
       </c>
       <c r="AS24" s="6">
-        <v>4451.99</v>
+        <v>3625.89</v>
       </c>
       <c r="AT24" s="6">
-        <v>346.99</v>
+        <v>149</v>
       </c>
       <c r="AU24" s="6">
-        <v>243.97900000000004</v>
+        <v>2411.9899999999998</v>
       </c>
       <c r="AV24" s="6">
-        <v>3687</v>
+        <v>207.9</v>
       </c>
       <c r="AW24" s="6">
-        <v>79.900000000000006</v>
+        <v>2723</v>
       </c>
       <c r="AX24" s="6">
-        <v>5453</v>
+        <v>1728</v>
       </c>
       <c r="AY24" s="6">
-        <v>2248</v>
+        <v>1568</v>
       </c>
       <c r="AZ24" s="6">
-        <v>2067.94</v>
+        <v>9979.5</v>
       </c>
       <c r="BA24" s="6">
-        <v>248</v>
+        <v>217.9</v>
       </c>
       <c r="BB24" s="6">
-        <v>1897.8899999999999</v>
+        <v>343</v>
       </c>
       <c r="BC24" s="6">
-        <v>2487.88</v>
+        <v>1762.67</v>
       </c>
       <c r="BD24" s="6">
-        <v>134.97</v>
+        <v>99.98</v>
       </c>
       <c r="BE24" s="6">
-        <v>503.96000000000004</v>
+        <v>2323.7600000000002</v>
       </c>
       <c r="BF24" s="6"/>
       <c r="BG24" s="6">
-        <v>18986.669999999998</v>
+        <v>31554.79</v>
       </c>
       <c r="BH24" s="6">
-        <v>13621</v>
+        <v>3568</v>
       </c>
       <c r="BI24" s="6">
-        <v>653.99</v>
+        <v>8457.89</v>
       </c>
       <c r="BJ24" s="6">
-        <v>13008.8</v>
+        <v>8816</v>
       </c>
       <c r="BK24" s="6">
-        <v>9492.9599999999991</v>
+        <v>22550.590000000004</v>
       </c>
       <c r="BL24" s="6">
-        <v>2598.88</v>
-      </c>
-      <c r="BM24" s="6"/>
+        <v>4016.49</v>
+      </c>
+      <c r="BM24" s="6">
+        <v>99</v>
+      </c>
       <c r="BN24" s="6">
-        <v>10407.98</v>
+        <v>20884.900000000001</v>
       </c>
       <c r="BO24" s="6">
-        <v>3449.9</v>
+        <v>2359.79</v>
       </c>
       <c r="BP24" s="6">
-        <v>3328</v>
+        <v>6561</v>
       </c>
       <c r="BQ24" s="6">
-        <v>3585</v>
+        <v>7318.9</v>
       </c>
       <c r="BR24" s="6">
-        <v>2749.4999999999995</v>
-      </c>
-      <c r="BS24" s="6">
-        <v>59.9</v>
-      </c>
+        <v>858.9699999999998</v>
+      </c>
+      <c r="BS24" s="6"/>
       <c r="BT24" s="6">
-        <v>14002.599999999999</v>
+        <v>3297.99</v>
       </c>
       <c r="BU24" s="6">
-        <v>18544.79</v>
+        <v>25747.989999999998</v>
       </c>
       <c r="BV24" s="6">
-        <v>11841.89</v>
+        <v>10859.89</v>
       </c>
       <c r="BW24" s="6">
-        <v>45</v>
+        <v>1750</v>
       </c>
       <c r="BX24" s="6">
-        <v>3994.87</v>
+        <v>2062.48</v>
       </c>
       <c r="BY24" s="6">
-        <v>4112</v>
+        <v>20231.8</v>
       </c>
       <c r="BZ24" s="6">
-        <v>4665.7</v>
+        <v>10543.89</v>
       </c>
       <c r="CA24" s="6">
-        <v>5372.65</v>
+        <v>4027.2799999999997</v>
       </c>
       <c r="CB24" s="6">
-        <v>2077.8900000000003</v>
+        <v>8922</v>
       </c>
       <c r="CC24" s="6">
-        <v>304.37</v>
+        <v>2336.9899999999998</v>
       </c>
       <c r="CD24" s="6">
-        <v>347</v>
+        <v>2005.77</v>
       </c>
       <c r="CE24" s="6">
-        <v>211.59</v>
+        <v>1771</v>
       </c>
       <c r="CF24" s="6"/>
       <c r="CG24" s="6">
-        <v>1410.8899999999999</v>
+        <v>1175.79</v>
       </c>
       <c r="CH24" s="6">
-        <v>1701.98</v>
+        <v>2344.9</v>
       </c>
       <c r="CI24" s="6">
-        <v>331.97</v>
+        <v>696</v>
       </c>
       <c r="CJ24" s="6">
-        <v>4993.9399999999996</v>
+        <v>22499.150000000005</v>
       </c>
     </row>
     <row r="25" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B25" s="6">
-        <v>503</v>
+        <v>1175.98</v>
       </c>
       <c r="C25" s="6">
-        <v>2872.9599999999991</v>
-      </c>
-      <c r="D25" s="6"/>
+        <v>2900.69</v>
+      </c>
+      <c r="D25" s="6">
+        <v>468</v>
+      </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6">
-        <v>4836.9699999999984</v>
+        <v>311.09300000000002</v>
       </c>
       <c r="G25" s="6">
-        <v>10811.29</v>
+        <v>14490.479999999998</v>
       </c>
       <c r="H25" s="6">
-        <v>5968.38</v>
+        <v>6241.1899999999987</v>
       </c>
       <c r="I25" s="6">
-        <v>5367.7699999999995</v>
+        <v>7335.79</v>
       </c>
       <c r="J25" s="6">
-        <v>1799.5</v>
+        <v>4950.37</v>
       </c>
       <c r="K25" s="6">
-        <v>1617</v>
+        <v>2398</v>
       </c>
       <c r="L25" s="6">
-        <v>661.98</v>
+        <v>89</v>
       </c>
       <c r="M25" s="6"/>
       <c r="N25" s="6">
-        <v>481.99</v>
+        <v>6238.8899999999994</v>
       </c>
       <c r="O25" s="6">
-        <v>379.7</v>
+        <v>772.88</v>
       </c>
       <c r="P25" s="6">
-        <v>1943.6899999999996</v>
+        <v>5049.8999999999996</v>
       </c>
       <c r="Q25" s="6">
-        <v>49.99</v>
+        <v>159.97</v>
       </c>
       <c r="R25" s="6">
-        <v>948</v>
+        <v>9442.8799999999992</v>
       </c>
       <c r="S25" s="6">
-        <v>692.87</v>
+        <v>576.89</v>
       </c>
       <c r="T25" s="6">
-        <v>348</v>
+        <v>487.99</v>
       </c>
       <c r="U25" s="6">
-        <v>2419.89</v>
+        <v>273.89999999999998</v>
       </c>
       <c r="V25" s="6">
-        <v>884.89</v>
+        <v>906.9</v>
       </c>
       <c r="W25" s="6">
-        <v>7386.0699999999988</v>
+        <v>3308.78</v>
       </c>
       <c r="X25" s="6">
-        <v>451.79</v>
+        <v>236.99</v>
       </c>
       <c r="Y25" s="6">
-        <v>1503.9</v>
+        <v>3634.6000000000004</v>
       </c>
       <c r="Z25" s="6">
-        <v>4185.99</v>
+        <v>3916.99</v>
       </c>
       <c r="AA25" s="6">
-        <v>2984.99</v>
+        <v>9394.99</v>
       </c>
       <c r="AB25" s="6">
-        <v>322.99</v>
+        <v>313.98</v>
       </c>
       <c r="AC25" s="6">
-        <v>688.99</v>
+        <v>129.99</v>
       </c>
       <c r="AD25" s="6">
-        <v>428.69</v>
-      </c>
-      <c r="AE25" s="6"/>
+        <v>687.99</v>
+      </c>
+      <c r="AE25" s="6">
+        <v>254</v>
+      </c>
       <c r="AF25" s="6">
-        <v>3442.89</v>
+        <v>5118.59</v>
       </c>
       <c r="AG25" s="6">
-        <v>876.59999999999991</v>
+        <v>1617.7</v>
       </c>
       <c r="AH25" s="6"/>
       <c r="AI25" s="6">
-        <v>2568.5100000000002</v>
-      </c>
-      <c r="AJ25" s="6">
-        <v>1074.5</v>
-      </c>
+        <v>7109.4400000000005</v>
+      </c>
+      <c r="AJ25" s="6"/>
       <c r="AK25" s="6">
-        <v>3720.99</v>
+        <v>4797.87</v>
       </c>
       <c r="AL25" s="6">
-        <v>8248.67</v>
+        <v>14917.869999999999</v>
       </c>
       <c r="AM25" s="6">
-        <v>1794.3700000000001</v>
+        <v>678.49</v>
       </c>
       <c r="AN25" s="6">
-        <v>1204.98</v>
+        <v>2550</v>
       </c>
       <c r="AO25" s="6">
-        <v>2335.9499999999998</v>
+        <v>4585.8900000000003</v>
       </c>
       <c r="AP25" s="6">
-        <v>3615.9799999999996</v>
+        <v>1740.8899999999999</v>
       </c>
       <c r="AQ25" s="6">
-        <v>3191.7700000000004</v>
+        <v>4619.8500000000004</v>
       </c>
       <c r="AR25" s="6">
-        <v>548.68999999999994</v>
+        <v>2305.79</v>
       </c>
       <c r="AS25" s="6">
-        <v>430.59000000000003</v>
-      </c>
-      <c r="AT25" s="6"/>
+        <v>1473.88</v>
+      </c>
+      <c r="AT25" s="6">
+        <v>35</v>
+      </c>
       <c r="AU25" s="6">
-        <v>586.88</v>
+        <v>3345.9</v>
       </c>
       <c r="AV25" s="6">
-        <v>2756</v>
+        <v>1746.99</v>
       </c>
       <c r="AW25" s="6">
-        <v>238.98000000000002</v>
+        <v>218.9</v>
       </c>
       <c r="AX25" s="6">
-        <v>3291.9799999999996</v>
+        <v>798</v>
       </c>
       <c r="AY25" s="6">
-        <v>8203.99</v>
+        <v>6704.9</v>
       </c>
       <c r="AZ25" s="6">
-        <v>6329.3899999999994</v>
+        <v>9896.7000000000007</v>
       </c>
       <c r="BA25" s="6">
-        <v>228.98000000000002</v>
+        <v>1736.89</v>
       </c>
       <c r="BB25" s="6">
-        <v>2074.8799999999997</v>
+        <v>405.99</v>
       </c>
       <c r="BC25" s="6">
-        <v>6027.2699999999986</v>
+        <v>10118.69</v>
       </c>
       <c r="BD25" s="6">
-        <v>319</v>
+        <v>59.99</v>
       </c>
       <c r="BE25" s="6">
-        <v>820</v>
+        <v>2441.87</v>
       </c>
       <c r="BF25" s="6"/>
       <c r="BG25" s="6">
-        <v>9109.4</v>
+        <v>3618.1000000000004</v>
       </c>
       <c r="BH25" s="6">
-        <v>3773.3</v>
+        <v>5870.6999999999989</v>
       </c>
       <c r="BI25" s="6">
-        <v>11620</v>
+        <v>722</v>
       </c>
       <c r="BJ25" s="6">
-        <v>4670.3899999999994</v>
+        <v>14453.9</v>
       </c>
       <c r="BK25" s="6">
-        <v>16503.399999999998</v>
+        <v>17028.900000000001</v>
       </c>
       <c r="BL25" s="6">
-        <v>5641.6</v>
+        <v>9839.7999999999993</v>
       </c>
       <c r="BM25" s="6">
-        <v>168.99</v>
+        <v>39</v>
       </c>
       <c r="BN25" s="6">
-        <v>7019</v>
+        <v>8377.7900000000009</v>
       </c>
       <c r="BO25" s="6">
-        <v>8580.9</v>
+        <v>4249.8900000000003</v>
       </c>
       <c r="BP25" s="6">
-        <v>12541.3</v>
+        <v>9705.9</v>
       </c>
       <c r="BQ25" s="6">
-        <v>14944.8</v>
+        <v>11077.5</v>
       </c>
       <c r="BR25" s="6">
-        <v>5458.99</v>
+        <v>4940.4799999999996</v>
       </c>
       <c r="BS25" s="6"/>
       <c r="BT25" s="6">
-        <v>9230.9699999999993</v>
+        <v>6144.8899999999994</v>
       </c>
       <c r="BU25" s="6">
-        <v>9220.7999999999993</v>
+        <v>6295.7000000000007</v>
       </c>
       <c r="BV25" s="6">
-        <v>2241.5</v>
+        <v>1013</v>
       </c>
       <c r="BW25" s="6">
-        <v>1566.99</v>
+        <v>298.78000000000003</v>
       </c>
       <c r="BX25" s="6">
-        <v>903.46999999999991</v>
+        <v>2549.3799999999997</v>
       </c>
       <c r="BY25" s="6">
-        <v>9082.7799999999988</v>
+        <v>12277.789999999999</v>
       </c>
       <c r="BZ25" s="6">
-        <v>21829.59</v>
+        <v>23049</v>
       </c>
       <c r="CA25" s="6">
-        <v>5089.08</v>
+        <v>6556.5599999999995</v>
       </c>
       <c r="CB25" s="6">
-        <v>8725.89</v>
+        <v>9715.9</v>
       </c>
       <c r="CC25" s="6">
-        <v>5330.869999999999</v>
+        <v>1977.99</v>
       </c>
       <c r="CD25" s="6">
-        <v>3570.8799999999997</v>
+        <v>1577.97</v>
       </c>
       <c r="CE25" s="6">
-        <v>2604.9</v>
-      </c>
-      <c r="CF25" s="6">
-        <v>79</v>
-      </c>
+        <v>1991.78</v>
+      </c>
+      <c r="CF25" s="6"/>
       <c r="CG25" s="6">
-        <v>1599.46</v>
+        <v>1465.64</v>
       </c>
       <c r="CH25" s="6">
-        <v>4115</v>
+        <v>3937.3</v>
       </c>
       <c r="CI25" s="6">
-        <v>1314.99</v>
+        <v>892.87</v>
       </c>
       <c r="CJ25" s="6">
-        <v>12940.109999999995</v>
+        <v>16749.019999999993</v>
       </c>
     </row>
     <row r="26" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B26" s="6">
-        <v>2698</v>
+        <v>395</v>
       </c>
       <c r="C26" s="6">
-        <v>1369.9</v>
+        <v>1039.7</v>
       </c>
       <c r="D26" s="6">
-        <v>1643.98</v>
+        <v>164.89000000000001</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6">
-        <v>2166.59</v>
+        <v>2863.8</v>
       </c>
       <c r="G26" s="6">
-        <v>14087.319999999996</v>
+        <v>9282.8799999999992</v>
       </c>
       <c r="H26" s="6">
-        <v>3763.49</v>
+        <v>3614.59</v>
       </c>
       <c r="I26" s="6">
-        <v>3901.8100000000004</v>
+        <v>6491.87</v>
       </c>
       <c r="J26" s="6">
-        <v>7348.869999999999</v>
-      </c>
-      <c r="K26" s="6">
-        <v>429</v>
-      </c>
+        <v>5900.6</v>
+      </c>
+      <c r="K26" s="6"/>
       <c r="L26" s="6">
-        <v>258.99</v>
+        <v>401.78000000000003</v>
       </c>
       <c r="M26" s="6"/>
       <c r="N26" s="6">
-        <v>314.89</v>
+        <v>7407.19</v>
       </c>
       <c r="O26" s="6">
-        <v>152.76999999999998</v>
+        <v>538.9</v>
       </c>
       <c r="P26" s="6">
-        <v>3583.8399999999992</v>
+        <v>1386.49</v>
       </c>
       <c r="Q26" s="6">
-        <v>368.8</v>
+        <v>193.99</v>
       </c>
       <c r="R26" s="6">
-        <v>14412.98</v>
+        <v>11592</v>
       </c>
       <c r="S26" s="6">
-        <v>139.99</v>
+        <v>101.7</v>
       </c>
       <c r="T26" s="6">
-        <v>168.98000000000002</v>
+        <v>129.99</v>
       </c>
       <c r="U26" s="6">
-        <v>6733.9000000000015</v>
+        <v>1160.8</v>
       </c>
       <c r="V26" s="6">
-        <v>902.79</v>
+        <v>1943.9</v>
       </c>
       <c r="W26" s="6">
-        <v>3138.9</v>
+        <v>9699.4599999999991</v>
       </c>
       <c r="X26" s="6">
-        <v>2151.79</v>
+        <v>3389.89</v>
       </c>
       <c r="Y26" s="6">
-        <v>121.88999999999999</v>
+        <v>4804.8999999999996</v>
       </c>
       <c r="Z26" s="6">
-        <v>3187.9700000000003</v>
+        <v>2432.8799999999997</v>
       </c>
       <c r="AA26" s="6">
-        <v>2195.98</v>
+        <v>1568</v>
       </c>
       <c r="AB26" s="6">
-        <v>499</v>
+        <v>468.97</v>
       </c>
       <c r="AC26" s="6">
-        <v>997.88</v>
+        <v>158</v>
       </c>
       <c r="AD26" s="6">
-        <v>65</v>
+        <v>1737.99</v>
       </c>
       <c r="AE26" s="6">
-        <v>1001.6899999999999</v>
+        <v>164</v>
       </c>
       <c r="AF26" s="6">
-        <v>3454.88</v>
+        <v>4065.69</v>
       </c>
       <c r="AG26" s="6">
-        <v>464.88</v>
+        <v>2435.29</v>
       </c>
       <c r="AH26" s="6"/>
       <c r="AI26" s="6">
-        <v>2136.4300000000003</v>
+        <v>1656.3700000000001</v>
       </c>
       <c r="AJ26" s="6">
-        <v>3097</v>
+        <v>2484.9</v>
       </c>
       <c r="AK26" s="6">
-        <v>2900.8399999999997</v>
+        <v>2404.9</v>
       </c>
       <c r="AL26" s="6">
-        <v>12313.759999999998</v>
+        <v>15583.9</v>
       </c>
       <c r="AM26" s="6">
-        <v>2132.9499999999998</v>
+        <v>1794.77</v>
       </c>
       <c r="AN26" s="6">
-        <v>193</v>
+        <v>689.98</v>
       </c>
       <c r="AO26" s="6">
-        <v>3184.8599999999997</v>
+        <v>3590.9799999999996</v>
       </c>
       <c r="AP26" s="6">
-        <v>1769.67</v>
+        <v>5307.99</v>
       </c>
       <c r="AQ26" s="6">
-        <v>1850.88</v>
+        <v>4700.99</v>
       </c>
       <c r="AR26" s="6">
-        <v>589.78</v>
+        <v>2674.0899999999997</v>
       </c>
       <c r="AS26" s="6">
-        <v>327.98</v>
-      </c>
-      <c r="AT26" s="6">
-        <v>178.99</v>
-      </c>
+        <v>599.9</v>
+      </c>
+      <c r="AT26" s="6"/>
       <c r="AU26" s="6">
-        <v>2048</v>
+        <v>2302</v>
       </c>
       <c r="AV26" s="6">
-        <v>4355.79</v>
+        <v>2204.8799999999997</v>
       </c>
       <c r="AW26" s="6">
-        <v>289.98</v>
+        <v>6180.8799999999992</v>
       </c>
       <c r="AX26" s="6">
-        <v>752.9</v>
+        <v>1649</v>
       </c>
       <c r="AY26" s="6">
-        <v>6126</v>
+        <v>3173.89</v>
       </c>
       <c r="AZ26" s="6">
-        <v>5163.8999999999996</v>
+        <v>11146.789999999999</v>
       </c>
       <c r="BA26" s="6">
-        <v>169</v>
+        <v>317.89999999999998</v>
       </c>
       <c r="BB26" s="6">
-        <v>554.98</v>
+        <v>1267.7900000000002</v>
       </c>
       <c r="BC26" s="6">
-        <v>6199.9</v>
+        <v>3654.2000000000003</v>
       </c>
       <c r="BD26" s="6"/>
       <c r="BE26" s="6">
-        <v>1468.8799999999999</v>
+        <v>339</v>
       </c>
       <c r="BF26" s="6"/>
       <c r="BG26" s="6">
-        <v>12109.789999999999</v>
+        <v>17119.8</v>
       </c>
       <c r="BH26" s="6">
-        <v>6098.9</v>
+        <v>2491.3000000000002</v>
       </c>
       <c r="BI26" s="6">
-        <v>1199</v>
+        <v>926</v>
       </c>
       <c r="BJ26" s="6">
-        <v>4751.99</v>
+        <v>14106.199999999999</v>
       </c>
       <c r="BK26" s="6">
-        <v>6896</v>
+        <v>20776.399999999998</v>
       </c>
       <c r="BL26" s="6">
-        <v>1418.93</v>
+        <v>12281.789999999999</v>
       </c>
       <c r="BM26" s="6">
-        <v>154</v>
+        <v>39</v>
       </c>
       <c r="BN26" s="6">
-        <v>5562.99</v>
+        <v>22823.7</v>
       </c>
       <c r="BO26" s="6">
-        <v>8500.99</v>
+        <v>6933.8</v>
       </c>
       <c r="BP26" s="6">
-        <v>6106.99</v>
+        <v>4401</v>
       </c>
       <c r="BQ26" s="6">
-        <v>6605.99</v>
+        <v>10416.9</v>
       </c>
       <c r="BR26" s="6">
-        <v>2994.42</v>
-      </c>
-      <c r="BS26" s="6">
-        <v>139.88</v>
-      </c>
+        <v>2948.76</v>
+      </c>
+      <c r="BS26" s="6"/>
       <c r="BT26" s="6">
-        <v>2809.88</v>
+        <v>8068.8899999999994</v>
       </c>
       <c r="BU26" s="6">
-        <v>23693.88</v>
+        <v>12172.9</v>
       </c>
       <c r="BV26" s="6">
-        <v>3778.59</v>
+        <v>10427</v>
       </c>
       <c r="BW26" s="6">
-        <v>669</v>
+        <v>1854.78</v>
       </c>
       <c r="BX26" s="6">
-        <v>2860.4900000000002</v>
+        <v>2731.56</v>
       </c>
       <c r="BY26" s="6">
-        <v>5348.99</v>
+        <v>5449.9</v>
       </c>
       <c r="BZ26" s="6">
-        <v>9410.7999999999993</v>
+        <v>36720.959999999999</v>
       </c>
       <c r="CA26" s="6">
-        <v>4099.54</v>
+        <v>4122.78</v>
       </c>
       <c r="CB26" s="6">
-        <v>6971.98</v>
+        <v>4872.8999999999996</v>
       </c>
       <c r="CC26" s="6">
-        <v>209.98000000000002</v>
+        <v>4365.99</v>
       </c>
       <c r="CD26" s="6">
-        <v>1464.8899999999999</v>
+        <v>3063.87</v>
       </c>
       <c r="CE26" s="6">
-        <v>1048.8900000000001</v>
+        <v>3547.99</v>
       </c>
       <c r="CF26" s="6"/>
       <c r="CG26" s="6">
-        <v>3803.6</v>
+        <v>590.99</v>
       </c>
       <c r="CH26" s="6">
-        <v>138.78</v>
+        <v>2030.29</v>
       </c>
       <c r="CI26" s="6">
-        <v>2989.27</v>
+        <v>276.8</v>
       </c>
       <c r="CJ26" s="6">
-        <v>33508.139999999992</v>
+        <v>16256.359999999995</v>
       </c>
     </row>
     <row r="27" spans="1:88" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B27" s="6">
-        <v>632.99</v>
+        <v>503</v>
       </c>
       <c r="C27" s="6">
-        <v>3146</v>
-      </c>
-      <c r="D27" s="6">
-        <v>649.9</v>
-      </c>
+        <v>2872.9599999999991</v>
+      </c>
+      <c r="D27" s="6"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6">
-        <v>2257.2800000000002</v>
+        <v>4836.9699999999984</v>
       </c>
       <c r="G27" s="6">
-        <v>6917.8</v>
+        <v>10811.29</v>
       </c>
       <c r="H27" s="6">
-        <v>6839.1599999999989</v>
+        <v>5968.3799999999992</v>
       </c>
       <c r="I27" s="6">
-        <v>4777.7199999999993</v>
+        <v>5367.7699999999995</v>
       </c>
       <c r="J27" s="6">
-        <v>2399.48</v>
-      </c>
-      <c r="K27" s="6"/>
+        <v>1799.5</v>
+      </c>
+      <c r="K27" s="6">
+        <v>1617</v>
+      </c>
       <c r="L27" s="6">
-        <v>59.39</v>
+        <v>661.98</v>
       </c>
       <c r="M27" s="6"/>
       <c r="N27" s="6">
-        <v>362.4</v>
+        <v>481.99</v>
       </c>
       <c r="O27" s="6">
-        <v>1734.98</v>
+        <v>379.7</v>
       </c>
       <c r="P27" s="6">
-        <v>1186.3800000000001</v>
+        <v>1943.6899999999996</v>
       </c>
       <c r="Q27" s="6">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="R27" s="6"/>
+        <v>49.99</v>
+      </c>
+      <c r="R27" s="6">
+        <v>948</v>
+      </c>
       <c r="S27" s="6">
-        <v>561.79999999999995</v>
+        <v>692.87</v>
       </c>
       <c r="T27" s="6">
-        <v>129.99</v>
-      </c>
-      <c r="U27" s="6"/>
+        <v>348</v>
+      </c>
+      <c r="U27" s="6">
+        <v>2419.89</v>
+      </c>
       <c r="V27" s="6">
-        <v>120.9</v>
+        <v>884.89</v>
       </c>
       <c r="W27" s="6">
-        <v>7033.87</v>
+        <v>7386.0699999999988</v>
       </c>
       <c r="X27" s="6">
-        <v>1238.9000000000001</v>
+        <v>451.79</v>
       </c>
       <c r="Y27" s="6">
-        <v>59</v>
+        <v>1503.9</v>
       </c>
       <c r="Z27" s="6">
-        <v>1393</v>
+        <v>4185.99</v>
       </c>
       <c r="AA27" s="6">
-        <v>2360</v>
+        <v>2984.99</v>
       </c>
       <c r="AB27" s="6">
-        <v>1182.8600000000001</v>
+        <v>322.99</v>
       </c>
       <c r="AC27" s="6">
-        <v>218</v>
+        <v>688.99</v>
       </c>
       <c r="AD27" s="6">
-        <v>59</v>
-      </c>
-      <c r="AE27" s="6">
-        <v>184</v>
-      </c>
+        <v>428.69</v>
+      </c>
+      <c r="AE27" s="6"/>
       <c r="AF27" s="6">
-        <v>2082.9</v>
+        <v>3442.89</v>
       </c>
       <c r="AG27" s="6">
-        <v>676.99</v>
+        <v>876.59999999999991</v>
       </c>
       <c r="AH27" s="6"/>
       <c r="AI27" s="6">
-        <v>2234.77</v>
+        <v>2568.5100000000002</v>
       </c>
       <c r="AJ27" s="6">
-        <v>2514</v>
+        <v>1074.5</v>
       </c>
       <c r="AK27" s="6">
-        <v>447.99</v>
+        <v>3720.99</v>
       </c>
       <c r="AL27" s="6">
-        <v>6653.1899999999987</v>
+        <v>8248.67</v>
       </c>
       <c r="AM27" s="6">
-        <v>3522.36</v>
+        <v>1794.3700000000001</v>
       </c>
       <c r="AN27" s="6">
-        <v>626.89</v>
+        <v>1204.98</v>
       </c>
       <c r="AO27" s="6">
-        <v>6025.98</v>
+        <v>2335.9499999999998</v>
       </c>
       <c r="AP27" s="6">
-        <v>438.78999999999996</v>
+        <v>3615.9799999999996</v>
       </c>
       <c r="AQ27" s="6">
-        <v>3982.9299999999994</v>
+        <v>3191.7700000000004</v>
       </c>
       <c r="AR27" s="6">
-        <v>79</v>
+        <v>548.69000000000005</v>
       </c>
       <c r="AS27" s="6">
-        <v>912.58999999999992</v>
-      </c>
-      <c r="AT27" s="6">
-        <v>39</v>
-      </c>
-      <c r="AU27" s="6"/>
+        <v>430.59000000000003</v>
+      </c>
+      <c r="AT27" s="6"/>
+      <c r="AU27" s="6">
+        <v>586.88</v>
+      </c>
       <c r="AV27" s="6">
-        <v>1288.8</v>
+        <v>2756</v>
       </c>
       <c r="AW27" s="6">
-        <v>408</v>
+        <v>238.98000000000002</v>
       </c>
       <c r="AX27" s="6">
-        <v>94.490000000000009</v>
+        <v>3291.9799999999996</v>
       </c>
       <c r="AY27" s="6">
-        <v>2797</v>
-      </c>
-      <c r="AZ27" s="6"/>
+        <v>8203.99</v>
+      </c>
+      <c r="AZ27" s="6">
+        <v>6329.3899999999994</v>
+      </c>
       <c r="BA27" s="6">
-        <v>179</v>
+        <v>228.98000000000002</v>
       </c>
       <c r="BB27" s="6">
-        <v>492.9</v>
+        <v>2074.8799999999997</v>
       </c>
       <c r="BC27" s="6">
-        <v>2701.5700000000006</v>
+        <v>6027.2699999999986</v>
       </c>
       <c r="BD27" s="6">
-        <v>167</v>
+        <v>319</v>
       </c>
       <c r="BE27" s="6">
-        <v>1558</v>
+        <v>820</v>
       </c>
       <c r="BF27" s="6"/>
-      <c r="BG27" s="6"/>
-      <c r="BH27" s="6"/>
-      <c r="BI27" s="6"/>
-      <c r="BJ27" s="6"/>
-      <c r="BK27" s="6"/>
-      <c r="BL27" s="6"/>
+      <c r="BG27" s="6">
+        <v>9109.4</v>
+      </c>
+      <c r="BH27" s="6">
+        <v>3773.3</v>
+      </c>
+      <c r="BI27" s="6">
+        <v>11620</v>
+      </c>
+      <c r="BJ27" s="6">
+        <v>4670.3899999999994</v>
+      </c>
+      <c r="BK27" s="6">
+        <v>16503.399999999998</v>
+      </c>
+      <c r="BL27" s="6">
+        <v>5641.6</v>
+      </c>
       <c r="BM27" s="6">
-        <v>178</v>
-      </c>
-      <c r="BN27" s="6"/>
-      <c r="BO27" s="6"/>
-      <c r="BP27" s="6"/>
-      <c r="BQ27" s="6"/>
+        <v>168.99</v>
+      </c>
+      <c r="BN27" s="6">
+        <v>7019</v>
+      </c>
+      <c r="BO27" s="6">
+        <v>8580.9</v>
+      </c>
+      <c r="BP27" s="6">
+        <v>12541.3</v>
+      </c>
+      <c r="BQ27" s="6">
+        <v>14944.8</v>
+      </c>
       <c r="BR27" s="6">
-        <v>1221.5799999999997</v>
+        <v>5458.99</v>
       </c>
       <c r="BS27" s="6"/>
       <c r="BT27" s="6">
+        <v>9230.9699999999993</v>
+      </c>
+      <c r="BU27" s="6">
+        <v>9220.7999999999993</v>
+      </c>
+      <c r="BV27" s="6">
+        <v>2241.5</v>
+      </c>
+      <c r="BW27" s="6">
+        <v>1566.99</v>
+      </c>
+      <c r="BX27" s="6">
+        <v>903.47</v>
+      </c>
+      <c r="BY27" s="6">
+        <v>9082.7799999999988</v>
+      </c>
+      <c r="BZ27" s="6">
+        <v>21829.59</v>
+      </c>
+      <c r="CA27" s="6">
+        <v>5089.08</v>
+      </c>
+      <c r="CB27" s="6">
+        <v>8725.89</v>
+      </c>
+      <c r="CC27" s="6">
+        <v>5330.869999999999</v>
+      </c>
+      <c r="CD27" s="6">
+        <v>3570.8799999999997</v>
+      </c>
+      <c r="CE27" s="6">
+        <v>2604.9</v>
+      </c>
+      <c r="CF27" s="6">
+        <v>79</v>
+      </c>
+      <c r="CG27" s="6">
+        <v>1599.46</v>
+      </c>
+      <c r="CH27" s="6">
+        <v>4115</v>
+      </c>
+      <c r="CI27" s="6">
+        <v>1314.99</v>
+      </c>
+      <c r="CJ27" s="6">
+        <v>12940.109999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:88" x14ac:dyDescent="0.35">
+      <c r="A28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="6">
+        <v>632.99</v>
+      </c>
+      <c r="C28" s="6">
+        <v>3146</v>
+      </c>
+      <c r="D28" s="6">
+        <v>649.9</v>
+      </c>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6">
+        <v>2257.2800000000002</v>
+      </c>
+      <c r="G28" s="6">
+        <v>6917.8</v>
+      </c>
+      <c r="H28" s="6">
+        <v>6839.1599999999989</v>
+      </c>
+      <c r="I28" s="6">
+        <v>4777.7199999999993</v>
+      </c>
+      <c r="J28" s="6">
+        <v>2399.48</v>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6">
+        <v>59.39</v>
+      </c>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6">
+        <v>362.4</v>
+      </c>
+      <c r="O28" s="6">
+        <v>1734.98</v>
+      </c>
+      <c r="P28" s="6">
+        <v>1186.3800000000001</v>
+      </c>
+      <c r="Q28" s="6">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6">
+        <v>561.79999999999995</v>
+      </c>
+      <c r="T28" s="6">
+        <v>129.99</v>
+      </c>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6">
+        <v>120.9</v>
+      </c>
+      <c r="W28" s="6">
+        <v>7033.87</v>
+      </c>
+      <c r="X28" s="6">
+        <v>1238.9000000000001</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>59</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>1393</v>
+      </c>
+      <c r="AA28" s="6">
+        <v>2360</v>
+      </c>
+      <c r="AB28" s="6">
+        <v>1182.8600000000001</v>
+      </c>
+      <c r="AC28" s="6">
+        <v>218</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>59</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>184</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>2082.9</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>676.99</v>
+      </c>
+      <c r="AH28" s="6"/>
+      <c r="AI28" s="6">
+        <v>2234.77</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>2514</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>447.99</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>6653.1899999999987</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>3522.36</v>
+      </c>
+      <c r="AN28" s="6">
+        <v>626.89</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>6025.98</v>
+      </c>
+      <c r="AP28" s="6">
+        <v>438.78999999999996</v>
+      </c>
+      <c r="AQ28" s="6">
+        <v>3982.9299999999994</v>
+      </c>
+      <c r="AR28" s="6">
+        <v>79</v>
+      </c>
+      <c r="AS28" s="6">
+        <v>912.58999999999992</v>
+      </c>
+      <c r="AT28" s="6">
+        <v>39</v>
+      </c>
+      <c r="AU28" s="6"/>
+      <c r="AV28" s="6">
+        <v>1288.8</v>
+      </c>
+      <c r="AW28" s="6">
+        <v>408</v>
+      </c>
+      <c r="AX28" s="6">
+        <v>94.490000000000009</v>
+      </c>
+      <c r="AY28" s="6">
+        <v>2797</v>
+      </c>
+      <c r="AZ28" s="6"/>
+      <c r="BA28" s="6">
+        <v>179</v>
+      </c>
+      <c r="BB28" s="6">
+        <v>492.9</v>
+      </c>
+      <c r="BC28" s="6">
+        <v>2701.57</v>
+      </c>
+      <c r="BD28" s="6">
+        <v>167</v>
+      </c>
+      <c r="BE28" s="6">
+        <v>1558</v>
+      </c>
+      <c r="BF28" s="6"/>
+      <c r="BG28" s="6"/>
+      <c r="BH28" s="6"/>
+      <c r="BI28" s="6"/>
+      <c r="BJ28" s="6"/>
+      <c r="BK28" s="6"/>
+      <c r="BL28" s="6"/>
+      <c r="BM28" s="6">
+        <v>178</v>
+      </c>
+      <c r="BN28" s="6"/>
+      <c r="BO28" s="6"/>
+      <c r="BP28" s="6"/>
+      <c r="BQ28" s="6"/>
+      <c r="BR28" s="6">
+        <v>1221.5799999999997</v>
+      </c>
+      <c r="BS28" s="6"/>
+      <c r="BT28" s="6">
         <v>1358.7000000000003</v>
       </c>
-      <c r="BU27" s="6"/>
-      <c r="BV27" s="6"/>
-      <c r="BW27" s="6">
+      <c r="BU28" s="6"/>
+      <c r="BV28" s="6"/>
+      <c r="BW28" s="6">
         <v>1372.9</v>
       </c>
-      <c r="BX27" s="6">
+      <c r="BX28" s="6">
         <v>3065.15</v>
       </c>
-      <c r="BY27" s="6"/>
-      <c r="BZ27" s="6"/>
-      <c r="CA27" s="6">
-        <v>5427.7899999999991</v>
-      </c>
-      <c r="CB27" s="6"/>
-      <c r="CC27" s="6">
+      <c r="BY28" s="6"/>
+      <c r="BZ28" s="6"/>
+      <c r="CA28" s="6">
+        <v>5427.79</v>
+      </c>
+      <c r="CB28" s="6"/>
+      <c r="CC28" s="6">
         <v>3427.5899999999997</v>
       </c>
-      <c r="CD27" s="6">
+      <c r="CD28" s="6">
         <v>2087</v>
       </c>
-      <c r="CE27" s="6">
+      <c r="CE28" s="6">
         <v>4467.8999999999996</v>
       </c>
-      <c r="CF27" s="6"/>
-      <c r="CG27" s="6">
+      <c r="CF28" s="6"/>
+      <c r="CG28" s="6">
         <v>1862.7800000000002</v>
       </c>
-      <c r="CH27" s="6">
+      <c r="CH28" s="6">
         <v>2659.79</v>
       </c>
-      <c r="CI27" s="6">
+      <c r="CI28" s="6">
         <v>999.90000000000009</v>
       </c>
-      <c r="CJ27" s="6"/>
-    </row>
-    <row r="28" spans="1:88" x14ac:dyDescent="0.35">
-      <c r="B28"/>
-      <c r="C28"/>
-      <c r="D28"/>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28"/>
-      <c r="H28"/>
-      <c r="I28" s="1"/>
+      <c r="CJ28" s="6"/>
     </row>
     <row r="29" spans="1:88" x14ac:dyDescent="0.35">
       <c r="B29"/>
